--- a/finance_customer.csv.xlsx
+++ b/finance_customer.csv.xlsx
@@ -8,19 +8,54 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pandas\Finance data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BA9599C-D9A1-4FDD-8E4C-58C8540AB72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3CF0C8-C512-4166-A190-319522D936ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9802DE5F-B1D8-4319-BDEA-30F1B831059A}"/>
   </bookViews>
   <sheets>
     <sheet name="finance_customer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3158" uniqueCount="720">
   <si>
     <t>customer_id</t>
   </si>
@@ -2171,13 +2206,22 @@
   </si>
   <si>
     <t>Tol_cur_bal</t>
+  </si>
+  <si>
+    <t>customer _id</t>
+  </si>
+  <si>
+    <t>Emp_title</t>
+  </si>
+  <si>
+    <t>tot_cur_bal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2308,6 +2352,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2693,7 +2743,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2711,6 +2761,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3086,7 +3137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{383771C4-FF3C-4B99-8491-974F447FF532}">
-  <dimension ref="A1:Q395"/>
+  <dimension ref="A1:W395"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -3094,19 +3145,27 @@
     <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.88671875" customWidth="1"/>
+    <col min="18" max="18" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3141,7 +3200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -3176,7 +3235,7 @@
         <v>34322</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -3211,7 +3270,7 @@
         <v>150674</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -3246,7 +3305,7 @@
         <v>281735</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -3281,7 +3340,7 @@
         <v>379132</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -3324,11 +3383,12 @@
       <c r="P6" s="7" t="s">
         <v>715</v>
       </c>
-      <c r="Q6" s="7" t="s">
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -3367,19 +3427,20 @@
         <v>38335069.949000001</v>
       </c>
       <c r="O7" s="8">
-        <f t="shared" ref="O7:Q7" si="0">SUM(F1:F394)</f>
+        <f t="shared" ref="O7" si="0">SUM(F1:F394)</f>
         <v>3110000</v>
       </c>
       <c r="P7" s="8">
         <f>SUM(J1:J394)</f>
         <v>3202883</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8">
         <f>SUM(K1:K394)</f>
         <v>32568773</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -3414,7 +3475,7 @@
         <v>408091</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -3449,7 +3510,7 @@
         <v>24448</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -3484,7 +3545,7 @@
         <v>30491</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
@@ -3519,7 +3580,7 @@
         <v>5927</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -3554,7 +3615,7 @@
         <v>96087</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -3589,7 +3650,7 @@
         <v>40264</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>48</v>
       </c>
@@ -3624,7 +3685,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
@@ -3659,7 +3720,7 @@
         <v>16656</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>52</v>
       </c>
@@ -3694,7 +3755,7 @@
         <v>37575</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>54</v>
       </c>
@@ -3728,8 +3789,41 @@
       <c r="K17" s="2">
         <v>142362</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M17" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="U17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="V17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="W17" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
@@ -3763,8 +3857,42 @@
       <c r="K18" s="2">
         <v>76641</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="N18" s="2" t="str" cm="1">
+        <f t="array" ref="N18:W18">_xlfn.XLOOKUP(M18,A2:A394,B2:K394,"not found",0)</f>
+        <v>Mechanical</v>
+      </c>
+      <c r="O18" s="2" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P18" s="2" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>49000</v>
+      </c>
+      <c r="R18" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="S18" s="2" t="str">
+        <v>Source Verified</v>
+      </c>
+      <c r="T18" s="2" t="str">
+        <v>109xx</v>
+      </c>
+      <c r="U18" s="2" t="str">
+        <v>NY</v>
+      </c>
+      <c r="V18" s="2">
+        <v>2192</v>
+      </c>
+      <c r="W18" s="2">
+        <v>19731</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>57</v>
       </c>
@@ -3798,8 +3926,42 @@
       <c r="K19" s="2">
         <v>69267</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N19" s="2" t="str" cm="1">
+        <f t="array" ref="N19:W19">_xlfn.XLOOKUP(M19,A3:A395,B3:K395,"not found",0)</f>
+        <v>Corrections Officer</v>
+      </c>
+      <c r="O19" s="2" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P19" s="2" t="str">
+        <v>Mortgage</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>74000</v>
+      </c>
+      <c r="R19" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="S19" s="2" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="T19" s="2" t="str">
+        <v>107xx</v>
+      </c>
+      <c r="U19" s="2" t="str">
+        <v>NY</v>
+      </c>
+      <c r="V19" s="2">
+        <v>47824</v>
+      </c>
+      <c r="W19" s="2">
+        <v>382595</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
@@ -3833,8 +3995,42 @@
       <c r="K20" s="2">
         <v>7013</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N20" s="2" t="str" cm="1">
+        <f t="array" ref="N20:W20">_xlfn.XLOOKUP(M20,A4:A396,B4:K396,"not found",0)</f>
+        <v xml:space="preserve">Claims Adjuster </v>
+      </c>
+      <c r="O20" s="2" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P20" s="2" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>38000</v>
+      </c>
+      <c r="R20" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="S20" s="2" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="T20" s="2" t="str">
+        <v>109xx</v>
+      </c>
+      <c r="U20" s="2" t="str">
+        <v>NY</v>
+      </c>
+      <c r="V20" s="2">
+        <v>1381</v>
+      </c>
+      <c r="W20" s="2">
+        <v>19340</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>61</v>
       </c>
@@ -3868,8 +4064,42 @@
       <c r="K21" s="2">
         <v>28818</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M21" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="N21" s="2" t="str" cm="1">
+        <f t="array" ref="N21:W21">_xlfn.XLOOKUP(M21,A5:A397,B5:K397,"not found",0)</f>
+        <v>Csr</v>
+      </c>
+      <c r="O21" s="2" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P21" s="2" t="str">
+        <v>Mortgage</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>65000</v>
+      </c>
+      <c r="R21" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="S21" s="2" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="T21" s="2" t="str">
+        <v>109xx</v>
+      </c>
+      <c r="U21" s="2" t="str">
+        <v>NY</v>
+      </c>
+      <c r="V21" s="2">
+        <v>20384</v>
+      </c>
+      <c r="W21" s="2">
+        <v>448449</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>62</v>
       </c>
@@ -3903,8 +4133,42 @@
       <c r="K22" s="2">
         <v>36059</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N22" s="2" t="str" cm="1">
+        <f t="array" ref="N22:W22">_xlfn.XLOOKUP(M22,A6:A398,B6:K398,"not found",0)</f>
+        <v>Application Developer</v>
+      </c>
+      <c r="O22" s="2" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P22" s="2" t="str">
+        <v>Mortgage</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>135000</v>
+      </c>
+      <c r="R22" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="S22" s="2" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="T22" s="2" t="str">
+        <v>109xx</v>
+      </c>
+      <c r="U22" s="2" t="str">
+        <v>NY</v>
+      </c>
+      <c r="V22" s="2">
+        <v>35562</v>
+      </c>
+      <c r="W22" s="2">
+        <v>355619</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>64</v>
       </c>
@@ -3938,8 +4202,42 @@
       <c r="K23" s="2">
         <v>382595</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M23" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N23" s="2" t="str" cm="1">
+        <f t="array" ref="N23:W23">_xlfn.XLOOKUP(M23,A7:A399,B7:K399,"not found",0)</f>
+        <v>None</v>
+      </c>
+      <c r="O23" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="P23" s="2" t="str">
+        <v>Mortgage</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>52800</v>
+      </c>
+      <c r="R23" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="S23" s="2" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="T23" s="2" t="str">
+        <v>480xx</v>
+      </c>
+      <c r="U23" s="2" t="str">
+        <v>MI</v>
+      </c>
+      <c r="V23" s="2">
+        <v>21029</v>
+      </c>
+      <c r="W23" s="2">
+        <v>105146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>66</v>
       </c>
@@ -3973,8 +4271,42 @@
       <c r="K24" s="2">
         <v>28413</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M24" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="N24" s="2" t="str" cm="1">
+        <f t="array" ref="N24:W24">_xlfn.XLOOKUP(M24,A8:A400,B8:K400,"not found",0)</f>
+        <v>National Client Space Manager</v>
+      </c>
+      <c r="O24" s="2" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P24" s="2" t="str">
+        <v>Mortgage</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>86000</v>
+      </c>
+      <c r="R24" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="S24" s="2" t="str">
+        <v>Source Verified</v>
+      </c>
+      <c r="T24" s="2" t="str">
+        <v>109xx</v>
+      </c>
+      <c r="U24" s="2" t="str">
+        <v>NY</v>
+      </c>
+      <c r="V24" s="2">
+        <v>19868</v>
+      </c>
+      <c r="W24" s="2">
+        <v>298017</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>68</v>
       </c>
@@ -4008,8 +4340,42 @@
       <c r="K25" s="2">
         <v>40630</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M25" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N25" s="2" t="str" cm="1">
+        <f t="array" ref="N25:W25">_xlfn.XLOOKUP(M25,A9:A401,B9:K401,"not found",0)</f>
+        <v xml:space="preserve">School Psychologist </v>
+      </c>
+      <c r="O25" s="2" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P25" s="2" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>90000</v>
+      </c>
+      <c r="R25" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="S25" s="2" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="T25" s="2" t="str">
+        <v>109xx</v>
+      </c>
+      <c r="U25" s="2" t="str">
+        <v>NY</v>
+      </c>
+      <c r="V25" s="2">
+        <v>11132</v>
+      </c>
+      <c r="W25" s="2">
+        <v>144718</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>70</v>
       </c>
@@ -4043,8 +4409,42 @@
       <c r="K26" s="2">
         <v>111366</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N26" s="2" t="str" cm="1">
+        <f t="array" ref="N26:W26">_xlfn.XLOOKUP(M26,A10:A402,B10:K402,"not found",0)</f>
+        <v>Teacher</v>
+      </c>
+      <c r="O26" s="2" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P26" s="2" t="str">
+        <v>Mortgage</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>96000</v>
+      </c>
+      <c r="R26" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="S26" s="2" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="T26" s="2" t="str">
+        <v>109xx</v>
+      </c>
+      <c r="U26" s="2" t="str">
+        <v>NY</v>
+      </c>
+      <c r="V26" s="2">
+        <v>54834</v>
+      </c>
+      <c r="W26" s="2">
+        <v>383838</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>72</v>
       </c>
@@ -4079,7 +4479,7 @@
         <v>28747</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>74</v>
       </c>
@@ -4114,7 +4514,7 @@
         <v>20751</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>75</v>
       </c>
@@ -4149,7 +4549,7 @@
         <v>204961</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>77</v>
       </c>
@@ -4184,7 +4584,7 @@
         <v>40001</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>79</v>
       </c>
@@ -4219,7 +4619,7 @@
         <v>8562</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>81</v>
       </c>
@@ -16926,7 +17326,7 @@
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E395">
-        <f t="shared" ref="C395:I395" si="1">SUM(E1:E394)</f>
+        <f t="shared" ref="E395:F395" si="1">SUM(E1:E394)</f>
         <v>38335069.949000001</v>
       </c>
       <c r="F395">
@@ -16943,6 +17343,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/finance_customer.csv.xlsx
+++ b/finance_customer.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pandas\Finance data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3CF0C8-C512-4166-A190-319522D936ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951CAE8F-3B5F-4BAF-B38C-39CDBFF05ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9802DE5F-B1D8-4319-BDEA-30F1B831059A}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3158" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="740">
   <si>
     <t>customer_id</t>
   </si>
@@ -2215,6 +2215,66 @@
   </si>
   <si>
     <t>tot_cur_bal</t>
+  </si>
+  <si>
+    <t>3nonenonenonenone</t>
+  </si>
+  <si>
+    <t>23nonenonenonenone</t>
+  </si>
+  <si>
+    <t>124nonenonenone</t>
+  </si>
+  <si>
+    <t>92nonenonenone</t>
+  </si>
+  <si>
+    <t>74nonenonenone</t>
+  </si>
+  <si>
+    <t>165nonenonenone</t>
+  </si>
+  <si>
+    <t>16nonenonenonenone</t>
+  </si>
+  <si>
+    <t>139nonenonenone</t>
+  </si>
+  <si>
+    <t>95nonenonenone</t>
+  </si>
+  <si>
+    <t>24nonenonenonenone</t>
+  </si>
+  <si>
+    <t>13nonenonenonenone</t>
+  </si>
+  <si>
+    <t>159nonenonenone</t>
+  </si>
+  <si>
+    <t>19nonenonenonenone</t>
+  </si>
+  <si>
+    <t>67nonenonenone</t>
+  </si>
+  <si>
+    <t>15nonenonenonenone</t>
+  </si>
+  <si>
+    <t>253nonenonenone</t>
+  </si>
+  <si>
+    <t>132nonenonenone</t>
+  </si>
+  <si>
+    <t>2nonenonenonenonenone</t>
+  </si>
+  <si>
+    <t>175nonenonenone</t>
+  </si>
+  <si>
+    <t>185nonenonenone</t>
   </si>
 </sst>
 </file>
@@ -2743,7 +2803,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2762,6 +2822,15 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3146,26 +3215,26 @@
     <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="8" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" style="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.88671875" customWidth="1"/>
-    <col min="18" max="18" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3187,10 +3256,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -3200,7 +3269,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -3219,13 +3288,13 @@
       <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="11" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="2">
@@ -3235,7 +3304,7 @@
         <v>34322</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -3254,13 +3323,13 @@
       <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="11" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="2">
@@ -3270,7 +3339,7 @@
         <v>150674</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -3289,13 +3358,13 @@
       <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="11" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="2">
@@ -3305,7 +3374,7 @@
         <v>281735</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -3321,16 +3390,16 @@
       <c r="E5" s="2">
         <v>75000</v>
       </c>
-      <c r="F5" s="4">
-        <v>120000</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="11" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="2">
@@ -3340,7 +3409,7 @@
         <v>379132</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -3359,13 +3428,13 @@
       <c r="F6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J6" s="2">
@@ -3383,12 +3452,11 @@
       <c r="P6" s="7" t="s">
         <v>715</v>
       </c>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7" t="s">
+      <c r="Q6" s="7" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -3407,13 +3475,13 @@
       <c r="F7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="2">
@@ -3428,19 +3496,18 @@
       </c>
       <c r="O7" s="8">
         <f t="shared" ref="O7" si="0">SUM(F1:F394)</f>
-        <v>3110000</v>
+        <v>0</v>
       </c>
       <c r="P7" s="8">
         <f>SUM(J1:J394)</f>
         <v>3202883</v>
       </c>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8">
-        <f>SUM(K1:K394)</f>
-        <v>32568773</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q7" s="8">
+        <f>SUM(J1:J394)</f>
+        <v>3202883</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -3459,13 +3526,13 @@
       <c r="F8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J8" s="2">
@@ -3475,7 +3542,7 @@
         <v>408091</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -3494,13 +3561,13 @@
       <c r="F9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="2">
@@ -3510,7 +3577,7 @@
         <v>24448</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -3529,13 +3596,13 @@
       <c r="F10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J10" s="2">
@@ -3545,7 +3612,7 @@
         <v>30491</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
@@ -3564,13 +3631,13 @@
       <c r="F11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J11" s="2">
@@ -3580,7 +3647,7 @@
         <v>5927</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -3599,13 +3666,13 @@
       <c r="F12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J12" s="2">
@@ -3615,7 +3682,7 @@
         <v>96087</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -3634,13 +3701,13 @@
       <c r="F13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J13" s="2">
@@ -3650,7 +3717,7 @@
         <v>40264</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>48</v>
       </c>
@@ -3669,13 +3736,13 @@
       <c r="F14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J14" s="2">
@@ -3685,7 +3752,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
@@ -3704,13 +3771,13 @@
       <c r="F15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J15" s="2">
@@ -3720,7 +3787,7 @@
         <v>16656</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>52</v>
       </c>
@@ -3739,13 +3806,13 @@
       <c r="F16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J16" s="2">
@@ -3774,13 +3841,13 @@
       <c r="F17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J17" s="2">
@@ -3842,13 +3909,13 @@
       <c r="F18" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J18" s="2">
@@ -3911,13 +3978,13 @@
       <c r="F19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J19" s="2">
@@ -3980,13 +4047,13 @@
       <c r="F20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J20" s="2">
@@ -4049,13 +4116,13 @@
       <c r="F21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J21" s="2">
@@ -4118,13 +4185,13 @@
       <c r="F22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J22" s="2">
@@ -4187,13 +4254,13 @@
       <c r="F23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J23" s="2">
@@ -4256,13 +4323,13 @@
       <c r="F24" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J24" s="2">
@@ -4325,13 +4392,13 @@
       <c r="F25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J25" s="2">
@@ -4394,13 +4461,13 @@
       <c r="F26" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J26" s="2">
@@ -4463,13 +4530,13 @@
       <c r="F27" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J27" s="2">
@@ -4498,13 +4565,13 @@
       <c r="F28" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I28" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J28" s="2">
@@ -4533,13 +4600,13 @@
       <c r="F29" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="I29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J29" s="2">
@@ -4568,13 +4635,13 @@
       <c r="F30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="I30" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J30" s="2">
@@ -4603,13 +4670,13 @@
       <c r="F31" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J31" s="2">
@@ -4638,13 +4705,13 @@
       <c r="F32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J32" s="2">
@@ -4654,7 +4721,7 @@
         <v>8189</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>83</v>
       </c>
@@ -4673,13 +4740,13 @@
       <c r="F33" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J33" s="2">
@@ -4689,7 +4756,7 @@
         <v>134654</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
@@ -4708,13 +4775,13 @@
       <c r="F34" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J34" s="2">
@@ -4724,7 +4791,7 @@
         <v>20389</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>86</v>
       </c>
@@ -4743,13 +4810,13 @@
       <c r="F35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J35" s="2">
@@ -4759,7 +4826,7 @@
         <v>335106</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>88</v>
       </c>
@@ -4778,13 +4845,13 @@
       <c r="F36" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="I36" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J36" s="2">
@@ -4794,7 +4861,7 @@
         <v>15673</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>91</v>
       </c>
@@ -4813,13 +4880,13 @@
       <c r="F37" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J37" s="2">
@@ -4829,7 +4896,7 @@
         <v>20828</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>93</v>
       </c>
@@ -4848,13 +4915,13 @@
       <c r="F38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I38" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J38" s="2">
@@ -4864,7 +4931,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>95</v>
       </c>
@@ -4880,16 +4947,16 @@
       <c r="E39" s="2">
         <v>9000</v>
       </c>
-      <c r="F39" s="4">
-        <v>30000</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="F39" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J39" s="2">
@@ -4899,7 +4966,7 @@
         <v>71976</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>96</v>
       </c>
@@ -4918,13 +4985,13 @@
       <c r="F40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="I40" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J40" s="2">
@@ -4934,7 +5001,7 @@
         <v>14107</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>98</v>
       </c>
@@ -4953,13 +5020,13 @@
       <c r="F41" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="H41" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="I41" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J41" s="2">
@@ -4968,8 +5035,9 @@
       <c r="K41" s="2">
         <v>251895</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="R41" s="7"/>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>100</v>
       </c>
@@ -4988,13 +5056,13 @@
       <c r="F42" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="I42" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J42" s="2">
@@ -5004,7 +5072,7 @@
         <v>18082</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>102</v>
       </c>
@@ -5023,13 +5091,13 @@
       <c r="F43" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="I43" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J43" s="2">
@@ -5039,7 +5107,7 @@
         <v>21200</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>104</v>
       </c>
@@ -5058,13 +5126,13 @@
       <c r="F44" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H44" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="I44" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J44" s="2">
@@ -5074,7 +5142,7 @@
         <v>80289</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>107</v>
       </c>
@@ -5093,13 +5161,13 @@
       <c r="F45" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="11" t="s">
         <v>109</v>
       </c>
       <c r="J45" s="2">
@@ -5109,7 +5177,7 @@
         <v>230115</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>110</v>
       </c>
@@ -5128,13 +5196,13 @@
       <c r="F46" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H46" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="I46" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J46" s="2">
@@ -5144,7 +5212,7 @@
         <v>31172</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>112</v>
       </c>
@@ -5163,13 +5231,13 @@
       <c r="F47" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H47" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I47" s="2" t="s">
+      <c r="I47" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J47" s="2">
@@ -5179,7 +5247,7 @@
         <v>229656</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>114</v>
       </c>
@@ -5198,13 +5266,13 @@
       <c r="F48" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="H48" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I48" s="2" t="s">
+      <c r="I48" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J48" s="2">
@@ -5233,13 +5301,13 @@
       <c r="F49" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="H49" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="I49" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J49" s="2">
@@ -5268,13 +5336,13 @@
       <c r="F50" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H50" s="2" t="s">
+      <c r="H50" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I50" s="2" t="s">
+      <c r="I50" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J50" s="2">
@@ -5300,16 +5368,16 @@
       <c r="E51" s="2">
         <v>90000</v>
       </c>
-      <c r="F51" s="4">
-        <v>230000</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="F51" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H51" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="I51" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J51" s="2">
@@ -5338,13 +5406,13 @@
       <c r="F52" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I52" s="2" t="s">
+      <c r="I52" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J52" s="2">
@@ -5373,13 +5441,13 @@
       <c r="F53" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H53" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I53" s="2" t="s">
+      <c r="I53" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J53" s="2">
@@ -5408,13 +5476,13 @@
       <c r="F54" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I54" s="2" t="s">
+      <c r="I54" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J54" s="2">
@@ -5443,13 +5511,13 @@
       <c r="F55" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I55" s="2" t="s">
+      <c r="I55" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J55" s="2">
@@ -5478,13 +5546,13 @@
       <c r="F56" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="I56" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J56" s="2">
@@ -5513,13 +5581,13 @@
       <c r="F57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I57" s="2" t="s">
+      <c r="I57" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J57" s="2">
@@ -5548,13 +5616,13 @@
       <c r="F58" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I58" s="2" t="s">
+      <c r="I58" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J58" s="2">
@@ -5583,13 +5651,13 @@
       <c r="F59" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="H59" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I59" s="2" t="s">
+      <c r="I59" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J59" s="2">
@@ -5618,13 +5686,13 @@
       <c r="F60" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H60" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I60" s="2" t="s">
+      <c r="I60" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J60" s="2">
@@ -5653,13 +5721,13 @@
       <c r="F61" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H61" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="I61" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J61" s="2">
@@ -5688,13 +5756,13 @@
       <c r="F62" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G62" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="H62" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I62" s="2" t="s">
+      <c r="I62" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J62" s="2">
@@ -5723,13 +5791,13 @@
       <c r="F63" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="H63" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I63" s="2" t="s">
+      <c r="I63" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J63" s="2">
@@ -5758,13 +5826,13 @@
       <c r="F64" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G64" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="H64" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I64" s="2" t="s">
+      <c r="I64" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J64" s="2">
@@ -5793,13 +5861,13 @@
       <c r="F65" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="H65" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I65" s="2" t="s">
+      <c r="I65" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J65" s="2">
@@ -5828,13 +5896,13 @@
       <c r="F66" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H66" s="2" t="s">
+      <c r="H66" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I66" s="2" t="s">
+      <c r="I66" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J66" s="2">
@@ -5863,13 +5931,13 @@
       <c r="F67" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H67" s="2" t="s">
+      <c r="H67" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I67" s="2" t="s">
+      <c r="I67" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J67" s="2">
@@ -5898,13 +5966,13 @@
       <c r="F68" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="G68" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H68" s="2" t="s">
+      <c r="H68" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I68" s="2" t="s">
+      <c r="I68" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J68" s="2">
@@ -5933,13 +6001,13 @@
       <c r="F69" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="H69" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I69" s="2" t="s">
+      <c r="I69" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J69" s="2">
@@ -5968,13 +6036,13 @@
       <c r="F70" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H70" s="2" t="s">
+      <c r="H70" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I70" s="2" t="s">
+      <c r="I70" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J70" s="2">
@@ -6003,13 +6071,13 @@
       <c r="F71" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="H71" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I71" s="2" t="s">
+      <c r="I71" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J71" s="2">
@@ -6038,13 +6106,13 @@
       <c r="F72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="G72" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H72" s="2" t="s">
+      <c r="H72" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I72" s="2" t="s">
+      <c r="I72" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J72" s="2">
@@ -6073,13 +6141,13 @@
       <c r="F73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H73" s="2" t="s">
+      <c r="H73" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I73" s="2" t="s">
+      <c r="I73" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J73" s="2">
@@ -6108,13 +6176,13 @@
       <c r="F74" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H74" s="2" t="s">
+      <c r="H74" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I74" s="2" t="s">
+      <c r="I74" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J74" s="2">
@@ -6143,13 +6211,13 @@
       <c r="F75" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H75" s="2" t="s">
+      <c r="H75" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I75" s="2" t="s">
+      <c r="I75" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J75" s="2">
@@ -6178,13 +6246,13 @@
       <c r="F76" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="H76" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I76" s="2" t="s">
+      <c r="I76" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J76" s="2">
@@ -6213,13 +6281,13 @@
       <c r="F77" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="H77" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I77" s="2" t="s">
+      <c r="I77" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J77" s="2">
@@ -6248,13 +6316,13 @@
       <c r="F78" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H78" s="2" t="s">
+      <c r="H78" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I78" s="2" t="s">
+      <c r="I78" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J78" s="2">
@@ -6280,16 +6348,16 @@
       <c r="E79" s="2">
         <v>62000</v>
       </c>
-      <c r="F79" s="4">
-        <v>124000</v>
-      </c>
-      <c r="G79" s="2" t="s">
+      <c r="F79" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="H79" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I79" s="2" t="s">
+      <c r="I79" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J79" s="2">
@@ -6318,13 +6386,13 @@
       <c r="F80" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H80" s="2" t="s">
+      <c r="H80" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I80" s="2" t="s">
+      <c r="I80" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J80" s="2">
@@ -6353,13 +6421,13 @@
       <c r="F81" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="H81" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I81" s="2" t="s">
+      <c r="I81" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J81" s="2">
@@ -6388,13 +6456,13 @@
       <c r="F82" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="H82" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I82" s="2" t="s">
+      <c r="I82" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J82" s="2">
@@ -6420,16 +6488,16 @@
       <c r="E83" s="2">
         <v>60000</v>
       </c>
-      <c r="F83" s="4">
-        <v>92000</v>
-      </c>
-      <c r="G83" s="2" t="s">
+      <c r="F83" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H83" s="2" t="s">
+      <c r="H83" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I83" s="2" t="s">
+      <c r="I83" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J83" s="2">
@@ -6458,13 +6526,13 @@
       <c r="F84" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H84" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I84" s="2" t="s">
+      <c r="I84" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J84" s="2">
@@ -6493,13 +6561,13 @@
       <c r="F85" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G85" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="H85" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I85" s="2" t="s">
+      <c r="I85" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J85" s="2">
@@ -6528,13 +6596,13 @@
       <c r="F86" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H86" s="2" t="s">
+      <c r="H86" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="I86" s="2" t="s">
+      <c r="I86" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J86" s="2">
@@ -6563,13 +6631,13 @@
       <c r="F87" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H87" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I87" s="2" t="s">
+      <c r="I87" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J87" s="2">
@@ -6598,13 +6666,13 @@
       <c r="F88" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G88" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="H88" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I88" s="2" t="s">
+      <c r="I88" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J88" s="2">
@@ -6630,16 +6698,16 @@
       <c r="E89" s="2">
         <v>48000</v>
       </c>
-      <c r="F89" s="4">
-        <v>74000</v>
-      </c>
-      <c r="G89" s="2" t="s">
+      <c r="F89" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="G89" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H89" s="2" t="s">
+      <c r="H89" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I89" s="2" t="s">
+      <c r="I89" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J89" s="2">
@@ -6668,13 +6736,13 @@
       <c r="F90" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G90" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H90" s="2" t="s">
+      <c r="H90" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I90" s="2" t="s">
+      <c r="I90" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J90" s="2">
@@ -6703,13 +6771,13 @@
       <c r="F91" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H91" s="2" t="s">
+      <c r="H91" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I91" s="2" t="s">
+      <c r="I91" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J91" s="2">
@@ -6738,13 +6806,13 @@
       <c r="F92" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G92" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H92" s="2" t="s">
+      <c r="H92" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I92" s="2" t="s">
+      <c r="I92" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J92" s="2">
@@ -6773,13 +6841,13 @@
       <c r="F93" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="G93" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="H93" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I93" s="2" t="s">
+      <c r="I93" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J93" s="2">
@@ -6808,13 +6876,13 @@
       <c r="F94" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G94" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H94" s="2" t="s">
+      <c r="H94" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I94" s="2" t="s">
+      <c r="I94" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J94" s="2">
@@ -6843,13 +6911,13 @@
       <c r="F95" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G95" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H95" s="2" t="s">
+      <c r="H95" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I95" s="2" t="s">
+      <c r="I95" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J95" s="2">
@@ -6878,13 +6946,13 @@
       <c r="F96" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="G96" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H96" s="2" t="s">
+      <c r="H96" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I96" s="2" t="s">
+      <c r="I96" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J96" s="2">
@@ -6913,13 +6981,13 @@
       <c r="F97" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="G97" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H97" s="2" t="s">
+      <c r="H97" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I97" s="2" t="s">
+      <c r="I97" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J97" s="2">
@@ -6948,13 +7016,13 @@
       <c r="F98" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G98" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H98" s="2" t="s">
+      <c r="H98" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I98" s="2" t="s">
+      <c r="I98" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J98" s="2">
@@ -6983,13 +7051,13 @@
       <c r="F99" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="G99" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H99" s="2" t="s">
+      <c r="H99" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I99" s="2" t="s">
+      <c r="I99" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J99" s="2">
@@ -7015,16 +7083,16 @@
       <c r="E100" s="2">
         <v>55000</v>
       </c>
-      <c r="F100" s="4">
-        <v>165000</v>
-      </c>
-      <c r="G100" s="2" t="s">
+      <c r="F100" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H100" s="2" t="s">
+      <c r="H100" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I100" s="2" t="s">
+      <c r="I100" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J100" s="2">
@@ -7053,13 +7121,13 @@
       <c r="F101" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="G101" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H101" s="2" t="s">
+      <c r="H101" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I101" s="2" t="s">
+      <c r="I101" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J101" s="2">
@@ -7088,13 +7156,13 @@
       <c r="F102" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G102" s="2" t="s">
+      <c r="G102" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H102" s="2" t="s">
+      <c r="H102" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I102" s="2" t="s">
+      <c r="I102" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J102" s="2">
@@ -7123,13 +7191,13 @@
       <c r="F103" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G103" s="2" t="s">
+      <c r="G103" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H103" s="2" t="s">
+      <c r="H103" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I103" s="2" t="s">
+      <c r="I103" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J103" s="2">
@@ -7158,13 +7226,13 @@
       <c r="F104" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G104" s="2" t="s">
+      <c r="G104" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H104" s="2" t="s">
+      <c r="H104" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I104" s="2" t="s">
+      <c r="I104" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J104" s="2">
@@ -7190,16 +7258,16 @@
       <c r="E105" s="2">
         <v>16000</v>
       </c>
-      <c r="F105" s="4">
-        <v>160000</v>
-      </c>
-      <c r="G105" s="2" t="s">
+      <c r="F105" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="G105" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="H105" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I105" s="2" t="s">
+      <c r="I105" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J105" s="2">
@@ -7228,13 +7296,13 @@
       <c r="F106" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G106" s="2" t="s">
+      <c r="G106" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="H106" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I106" s="2" t="s">
+      <c r="I106" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J106" s="2">
@@ -7263,13 +7331,13 @@
       <c r="F107" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="G107" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="H107" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I107" s="2" t="s">
+      <c r="I107" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J107" s="2">
@@ -7298,13 +7366,13 @@
       <c r="F108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="G108" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H108" s="2" t="s">
+      <c r="H108" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I108" s="2" t="s">
+      <c r="I108" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J108" s="2">
@@ -7333,13 +7401,13 @@
       <c r="F109" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G109" s="2" t="s">
+      <c r="G109" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H109" s="2" t="s">
+      <c r="H109" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I109" s="2" t="s">
+      <c r="I109" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J109" s="2">
@@ -7368,13 +7436,13 @@
       <c r="F110" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="G110" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H110" s="2" t="s">
+      <c r="H110" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I110" s="2" t="s">
+      <c r="I110" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J110" s="2">
@@ -7403,13 +7471,13 @@
       <c r="F111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G111" s="2" t="s">
+      <c r="G111" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H111" s="2" t="s">
+      <c r="H111" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I111" s="2" t="s">
+      <c r="I111" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J111" s="2">
@@ -7438,13 +7506,13 @@
       <c r="F112" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="G112" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H112" s="2" t="s">
+      <c r="H112" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I112" s="2" t="s">
+      <c r="I112" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J112" s="2">
@@ -7473,13 +7541,13 @@
       <c r="F113" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="G113" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H113" s="2" t="s">
+      <c r="H113" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I113" s="2" t="s">
+      <c r="I113" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J113" s="2">
@@ -7508,13 +7576,13 @@
       <c r="F114" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G114" s="2" t="s">
+      <c r="G114" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H114" s="2" t="s">
+      <c r="H114" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I114" s="2" t="s">
+      <c r="I114" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J114" s="2">
@@ -7543,13 +7611,13 @@
       <c r="F115" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G115" s="2" t="s">
+      <c r="G115" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H115" s="2" t="s">
+      <c r="H115" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I115" s="2" t="s">
+      <c r="I115" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J115" s="2">
@@ -7575,16 +7643,16 @@
       <c r="E116" s="2">
         <v>45000</v>
       </c>
-      <c r="F116" s="4">
-        <v>139000</v>
-      </c>
-      <c r="G116" s="2" t="s">
+      <c r="F116" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="G116" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="H116" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I116" s="2" t="s">
+      <c r="I116" s="11" t="s">
         <v>26</v>
       </c>
       <c r="J116" s="2">
@@ -7613,13 +7681,13 @@
       <c r="F117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G117" s="2" t="s">
+      <c r="G117" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H117" s="2" t="s">
+      <c r="H117" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I117" s="2" t="s">
+      <c r="I117" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J117" s="2">
@@ -7648,13 +7716,13 @@
       <c r="F118" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="G118" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H118" s="2" t="s">
+      <c r="H118" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I118" s="2" t="s">
+      <c r="I118" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J118" s="2">
@@ -7683,13 +7751,13 @@
       <c r="F119" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="G119" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H119" s="2" t="s">
+      <c r="H119" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I119" s="2" t="s">
+      <c r="I119" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J119" s="2">
@@ -7718,13 +7786,13 @@
       <c r="F120" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G120" s="2" t="s">
+      <c r="G120" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H120" s="2" t="s">
+      <c r="H120" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I120" s="2" t="s">
+      <c r="I120" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J120" s="2">
@@ -7753,13 +7821,13 @@
       <c r="F121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G121" s="2" t="s">
+      <c r="G121" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H121" s="2" t="s">
+      <c r="H121" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I121" s="2" t="s">
+      <c r="I121" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J121" s="2">
@@ -7788,13 +7856,13 @@
       <c r="F122" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G122" s="2" t="s">
+      <c r="G122" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H122" s="2" t="s">
+      <c r="H122" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I122" s="2" t="s">
+      <c r="I122" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J122" s="2">
@@ -7823,13 +7891,13 @@
       <c r="F123" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G123" s="2" t="s">
+      <c r="G123" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H123" s="2" t="s">
+      <c r="H123" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I123" s="2" t="s">
+      <c r="I123" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J123" s="2">
@@ -7858,13 +7926,13 @@
       <c r="F124" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G124" s="2" t="s">
+      <c r="G124" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="H124" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I124" s="2" t="s">
+      <c r="I124" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J124" s="2">
@@ -7893,13 +7961,13 @@
       <c r="F125" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G125" s="2" t="s">
+      <c r="G125" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H125" s="2" t="s">
+      <c r="H125" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I125" s="2" t="s">
+      <c r="I125" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J125" s="2">
@@ -7928,13 +7996,13 @@
       <c r="F126" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G126" s="2" t="s">
+      <c r="G126" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H126" s="2" t="s">
+      <c r="H126" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I126" s="2" t="s">
+      <c r="I126" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J126" s="2">
@@ -7963,13 +8031,13 @@
       <c r="F127" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G127" s="2" t="s">
+      <c r="G127" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H127" s="2" t="s">
+      <c r="H127" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I127" s="2" t="s">
+      <c r="I127" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J127" s="2">
@@ -7998,13 +8066,13 @@
       <c r="F128" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G128" s="2" t="s">
+      <c r="G128" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H128" s="2" t="s">
+      <c r="H128" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I128" s="2" t="s">
+      <c r="I128" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J128" s="2">
@@ -8033,13 +8101,13 @@
       <c r="F129" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G129" s="2" t="s">
+      <c r="G129" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H129" s="2" t="s">
+      <c r="H129" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I129" s="2" t="s">
+      <c r="I129" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J129" s="2">
@@ -8068,13 +8136,13 @@
       <c r="F130" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G130" s="2" t="s">
+      <c r="G130" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H130" s="2" t="s">
+      <c r="H130" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I130" s="2" t="s">
+      <c r="I130" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J130" s="2">
@@ -8103,13 +8171,13 @@
       <c r="F131" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G131" s="2" t="s">
+      <c r="G131" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H131" s="2" t="s">
+      <c r="H131" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I131" s="2" t="s">
+      <c r="I131" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J131" s="2">
@@ -8138,13 +8206,13 @@
       <c r="F132" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G132" s="2" t="s">
+      <c r="G132" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H132" s="2" t="s">
+      <c r="H132" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I132" s="2" t="s">
+      <c r="I132" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J132" s="2">
@@ -8173,13 +8241,13 @@
       <c r="F133" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="G133" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H133" s="2" t="s">
+      <c r="H133" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I133" s="2" t="s">
+      <c r="I133" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J133" s="2">
@@ -8205,16 +8273,16 @@
       <c r="E134" s="2">
         <v>55000</v>
       </c>
-      <c r="F134" s="4">
-        <v>95000</v>
-      </c>
-      <c r="G134" s="2" t="s">
+      <c r="F134" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="G134" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H134" s="2" t="s">
+      <c r="H134" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I134" s="2" t="s">
+      <c r="I134" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J134" s="2">
@@ -8243,13 +8311,13 @@
       <c r="F135" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G135" s="2" t="s">
+      <c r="G135" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H135" s="2" t="s">
+      <c r="H135" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I135" s="2" t="s">
+      <c r="I135" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J135" s="2">
@@ -8278,13 +8346,13 @@
       <c r="F136" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G136" s="2" t="s">
+      <c r="G136" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H136" s="2" t="s">
+      <c r="H136" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I136" s="2" t="s">
+      <c r="I136" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J136" s="2">
@@ -8313,13 +8381,13 @@
       <c r="F137" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G137" s="2" t="s">
+      <c r="G137" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H137" s="2" t="s">
+      <c r="H137" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I137" s="2" t="s">
+      <c r="I137" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J137" s="2">
@@ -8348,13 +8416,13 @@
       <c r="F138" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G138" s="2" t="s">
+      <c r="G138" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H138" s="2" t="s">
+      <c r="H138" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I138" s="2" t="s">
+      <c r="I138" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J138" s="2">
@@ -8383,13 +8451,13 @@
       <c r="F139" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G139" s="2" t="s">
+      <c r="G139" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H139" s="2" t="s">
+      <c r="H139" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I139" s="2" t="s">
+      <c r="I139" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J139" s="2">
@@ -8418,13 +8486,13 @@
       <c r="F140" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="G140" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H140" s="2" t="s">
+      <c r="H140" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I140" s="2" t="s">
+      <c r="I140" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J140" s="2">
@@ -8453,13 +8521,13 @@
       <c r="F141" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G141" s="2" t="s">
+      <c r="G141" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H141" s="2" t="s">
+      <c r="H141" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I141" s="2" t="s">
+      <c r="I141" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J141" s="2">
@@ -8488,13 +8556,13 @@
       <c r="F142" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G142" s="2" t="s">
+      <c r="G142" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H142" s="2" t="s">
+      <c r="H142" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I142" s="2" t="s">
+      <c r="I142" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J142" s="2">
@@ -8523,13 +8591,13 @@
       <c r="F143" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G143" s="2" t="s">
+      <c r="G143" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H143" s="2" t="s">
+      <c r="H143" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="I143" s="2" t="s">
+      <c r="I143" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J143" s="2">
@@ -8558,13 +8626,13 @@
       <c r="F144" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G144" s="2" t="s">
+      <c r="G144" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H144" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I144" s="2" t="s">
+      <c r="H144" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I144" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J144" s="2">
@@ -8593,13 +8661,13 @@
       <c r="F145" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G145" s="2" t="s">
+      <c r="G145" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H145" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I145" s="2" t="s">
+      <c r="H145" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I145" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J145" s="2">
@@ -8628,13 +8696,13 @@
       <c r="F146" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G146" s="2" t="s">
+      <c r="G146" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H146" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I146" s="2" t="s">
+      <c r="H146" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I146" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J146" s="2">
@@ -8663,13 +8731,13 @@
       <c r="F147" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G147" s="2" t="s">
+      <c r="G147" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H147" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I147" s="2" t="s">
+      <c r="H147" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I147" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J147" s="2">
@@ -8698,13 +8766,13 @@
       <c r="F148" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G148" s="2" t="s">
+      <c r="G148" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H148" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I148" s="2" t="s">
+      <c r="H148" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I148" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J148" s="2">
@@ -8733,13 +8801,13 @@
       <c r="F149" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G149" s="2" t="s">
+      <c r="G149" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H149" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I149" s="2" t="s">
+      <c r="H149" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I149" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J149" s="2">
@@ -8768,13 +8836,13 @@
       <c r="F150" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G150" s="2" t="s">
+      <c r="G150" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H150" s="2" t="s">
+      <c r="H150" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I150" s="2" t="s">
+      <c r="I150" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J150" s="2">
@@ -8803,13 +8871,13 @@
       <c r="F151" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G151" s="2" t="s">
+      <c r="G151" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H151" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I151" s="2" t="s">
+      <c r="H151" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I151" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J151" s="2">
@@ -8838,13 +8906,13 @@
       <c r="F152" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="G152" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H152" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I152" s="2" t="s">
+      <c r="H152" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I152" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J152" s="2">
@@ -8873,13 +8941,13 @@
       <c r="F153" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="G153" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H153" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I153" s="2" t="s">
+      <c r="H153" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I153" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J153" s="2">
@@ -8908,13 +8976,13 @@
       <c r="F154" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G154" s="2" t="s">
+      <c r="G154" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H154" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I154" s="2" t="s">
+      <c r="H154" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I154" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J154" s="2">
@@ -8943,13 +9011,13 @@
       <c r="F155" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G155" s="2" t="s">
+      <c r="G155" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H155" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I155" s="2" t="s">
+      <c r="H155" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I155" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J155" s="2">
@@ -8978,13 +9046,13 @@
       <c r="F156" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="G156" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H156" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I156" s="2" t="s">
+      <c r="H156" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I156" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J156" s="2">
@@ -9013,13 +9081,13 @@
       <c r="F157" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G157" s="2" t="s">
+      <c r="G157" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H157" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I157" s="2" t="s">
+      <c r="H157" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I157" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J157" s="2">
@@ -9048,13 +9116,13 @@
       <c r="F158" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G158" s="2" t="s">
+      <c r="G158" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H158" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I158" s="2" t="s">
+      <c r="H158" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I158" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J158" s="2">
@@ -9083,13 +9151,13 @@
       <c r="F159" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G159" s="2" t="s">
+      <c r="G159" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H159" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I159" s="2" t="s">
+      <c r="H159" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I159" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J159" s="2">
@@ -9118,13 +9186,13 @@
       <c r="F160" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G160" s="2" t="s">
+      <c r="G160" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H160" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I160" s="2" t="s">
+      <c r="H160" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I160" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J160" s="2">
@@ -9153,13 +9221,13 @@
       <c r="F161" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G161" s="2" t="s">
+      <c r="G161" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H161" s="2" t="s">
+      <c r="H161" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I161" s="2" t="s">
+      <c r="I161" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J161" s="2">
@@ -9188,13 +9256,13 @@
       <c r="F162" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G162" s="2" t="s">
+      <c r="G162" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H162" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I162" s="2" t="s">
+      <c r="H162" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I162" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J162" s="2">
@@ -9223,13 +9291,13 @@
       <c r="F163" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G163" s="2" t="s">
+      <c r="G163" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H163" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I163" s="2" t="s">
+      <c r="H163" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I163" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J163" s="2">
@@ -9258,13 +9326,13 @@
       <c r="F164" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G164" s="2" t="s">
+      <c r="G164" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H164" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I164" s="2" t="s">
+      <c r="H164" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I164" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J164" s="2">
@@ -9293,13 +9361,13 @@
       <c r="F165" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G165" s="2" t="s">
+      <c r="G165" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H165" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I165" s="2" t="s">
+      <c r="H165" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I165" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J165" s="2">
@@ -9328,13 +9396,13 @@
       <c r="F166" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="G166" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H166" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I166" s="2" t="s">
+      <c r="H166" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I166" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J166" s="2">
@@ -9363,13 +9431,13 @@
       <c r="F167" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G167" s="2" t="s">
+      <c r="G167" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H167" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I167" s="2" t="s">
+      <c r="H167" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I167" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J167" s="2">
@@ -9398,13 +9466,13 @@
       <c r="F168" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G168" s="2" t="s">
+      <c r="G168" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H168" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I168" s="2" t="s">
+      <c r="H168" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I168" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J168" s="2">
@@ -9433,13 +9501,13 @@
       <c r="F169" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G169" s="2" t="s">
+      <c r="G169" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H169" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I169" s="2" t="s">
+      <c r="H169" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I169" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J169" s="2">
@@ -9468,13 +9536,13 @@
       <c r="F170" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G170" s="2" t="s">
+      <c r="G170" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H170" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I170" s="2" t="s">
+      <c r="H170" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I170" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J170" s="2">
@@ -9503,13 +9571,13 @@
       <c r="F171" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G171" s="2" t="s">
+      <c r="G171" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H171" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I171" s="2" t="s">
+      <c r="H171" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I171" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J171" s="2">
@@ -9538,13 +9606,13 @@
       <c r="F172" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G172" s="2" t="s">
+      <c r="G172" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H172" s="2" t="s">
+      <c r="H172" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I172" s="2" t="s">
+      <c r="I172" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J172" s="2">
@@ -9573,13 +9641,13 @@
       <c r="F173" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G173" s="2" t="s">
+      <c r="G173" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H173" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I173" s="2" t="s">
+      <c r="H173" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I173" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J173" s="2">
@@ -9608,13 +9676,13 @@
       <c r="F174" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G174" s="2" t="s">
+      <c r="G174" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H174" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I174" s="2" t="s">
+      <c r="H174" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I174" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J174" s="2">
@@ -9643,13 +9711,13 @@
       <c r="F175" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G175" s="2" t="s">
+      <c r="G175" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H175" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I175" s="2" t="s">
+      <c r="H175" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I175" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J175" s="2">
@@ -9678,13 +9746,13 @@
       <c r="F176" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G176" s="2" t="s">
+      <c r="G176" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H176" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I176" s="2" t="s">
+      <c r="H176" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I176" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J176" s="2">
@@ -9713,13 +9781,13 @@
       <c r="F177" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G177" s="2" t="s">
+      <c r="G177" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H177" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I177" s="2" t="s">
+      <c r="H177" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I177" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J177" s="2">
@@ -9748,13 +9816,13 @@
       <c r="F178" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G178" s="2" t="s">
+      <c r="G178" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H178" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I178" s="2" t="s">
+      <c r="H178" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I178" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J178" s="2">
@@ -9783,13 +9851,13 @@
       <c r="F179" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G179" s="2" t="s">
+      <c r="G179" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H179" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I179" s="2" t="s">
+      <c r="H179" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I179" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J179" s="2">
@@ -9818,13 +9886,13 @@
       <c r="F180" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G180" s="2" t="s">
+      <c r="G180" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H180" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I180" s="2" t="s">
+      <c r="H180" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I180" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J180" s="2">
@@ -9853,13 +9921,13 @@
       <c r="F181" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G181" s="2" t="s">
+      <c r="G181" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H181" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I181" s="2" t="s">
+      <c r="H181" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I181" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J181" s="2">
@@ -9888,13 +9956,13 @@
       <c r="F182" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G182" s="2" t="s">
+      <c r="G182" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H182" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I182" s="2" t="s">
+      <c r="H182" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I182" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J182" s="2">
@@ -9923,13 +9991,13 @@
       <c r="F183" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G183" s="2" t="s">
+      <c r="G183" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H183" s="2" t="s">
+      <c r="H183" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I183" s="2" t="s">
+      <c r="I183" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J183" s="2">
@@ -9958,13 +10026,13 @@
       <c r="F184" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G184" s="2" t="s">
+      <c r="G184" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H184" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I184" s="2" t="s">
+      <c r="H184" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I184" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J184" s="2">
@@ -9993,13 +10061,13 @@
       <c r="F185" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G185" s="2" t="s">
+      <c r="G185" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H185" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I185" s="2" t="s">
+      <c r="H185" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I185" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J185" s="2">
@@ -10028,13 +10096,13 @@
       <c r="F186" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G186" s="2" t="s">
+      <c r="G186" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H186" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I186" s="2" t="s">
+      <c r="H186" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I186" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J186" s="2">
@@ -10063,13 +10131,13 @@
       <c r="F187" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G187" s="2" t="s">
+      <c r="G187" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H187" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I187" s="2" t="s">
+      <c r="H187" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I187" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J187" s="2">
@@ -10098,13 +10166,13 @@
       <c r="F188" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G188" s="2" t="s">
+      <c r="G188" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H188" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I188" s="2" t="s">
+      <c r="H188" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I188" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J188" s="2">
@@ -10133,13 +10201,13 @@
       <c r="F189" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G189" s="2" t="s">
+      <c r="G189" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H189" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I189" s="2" t="s">
+      <c r="H189" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I189" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J189" s="2">
@@ -10168,13 +10236,13 @@
       <c r="F190" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G190" s="2" t="s">
+      <c r="G190" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H190" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I190" s="2" t="s">
+      <c r="H190" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I190" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J190" s="2">
@@ -10203,13 +10271,13 @@
       <c r="F191" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G191" s="2" t="s">
+      <c r="G191" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H191" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I191" s="2" t="s">
+      <c r="H191" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I191" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J191" s="2">
@@ -10238,13 +10306,13 @@
       <c r="F192" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G192" s="2" t="s">
+      <c r="G192" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H192" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I192" s="2" t="s">
+      <c r="H192" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I192" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J192" s="2">
@@ -10273,13 +10341,13 @@
       <c r="F193" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G193" s="2" t="s">
+      <c r="G193" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H193" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I193" s="2" t="s">
+      <c r="H193" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I193" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J193" s="2">
@@ -10308,13 +10376,13 @@
       <c r="F194" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G194" s="2" t="s">
+      <c r="G194" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H194" s="2" t="s">
+      <c r="H194" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I194" s="2" t="s">
+      <c r="I194" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J194" s="2">
@@ -10343,13 +10411,13 @@
       <c r="F195" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G195" s="2" t="s">
+      <c r="G195" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H195" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I195" s="2" t="s">
+      <c r="H195" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I195" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J195" s="2">
@@ -10378,13 +10446,13 @@
       <c r="F196" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G196" s="2" t="s">
+      <c r="G196" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H196" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I196" s="2" t="s">
+      <c r="H196" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I196" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J196" s="2">
@@ -10413,13 +10481,13 @@
       <c r="F197" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G197" s="2" t="s">
+      <c r="G197" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H197" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I197" s="2" t="s">
+      <c r="H197" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I197" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J197" s="2">
@@ -10448,13 +10516,13 @@
       <c r="F198" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G198" s="2" t="s">
+      <c r="G198" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H198" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I198" s="2" t="s">
+      <c r="H198" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I198" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J198" s="2">
@@ -10483,13 +10551,13 @@
       <c r="F199" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G199" s="2" t="s">
+      <c r="G199" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H199" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I199" s="2" t="s">
+      <c r="H199" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I199" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J199" s="2">
@@ -10518,13 +10586,13 @@
       <c r="F200" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G200" s="2" t="s">
+      <c r="G200" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H200" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I200" s="2" t="s">
+      <c r="H200" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I200" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J200" s="2">
@@ -10553,13 +10621,13 @@
       <c r="F201" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G201" s="2" t="s">
+      <c r="G201" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H201" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I201" s="2" t="s">
+      <c r="H201" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I201" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J201" s="2">
@@ -10588,13 +10656,13 @@
       <c r="F202" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G202" s="2" t="s">
+      <c r="G202" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H202" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I202" s="2" t="s">
+      <c r="H202" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I202" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J202" s="2">
@@ -10623,13 +10691,13 @@
       <c r="F203" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G203" s="2" t="s">
+      <c r="G203" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H203" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I203" s="2" t="s">
+      <c r="H203" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I203" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J203" s="2">
@@ -10658,13 +10726,13 @@
       <c r="F204" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G204" s="2" t="s">
+      <c r="G204" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H204" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I204" s="2" t="s">
+      <c r="H204" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I204" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J204" s="2">
@@ -10693,13 +10761,13 @@
       <c r="F205" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G205" s="2" t="s">
+      <c r="G205" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H205" s="2" t="s">
+      <c r="H205" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I205" s="2" t="s">
+      <c r="I205" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J205" s="2">
@@ -10728,13 +10796,13 @@
       <c r="F206" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G206" s="2" t="s">
+      <c r="G206" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H206" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I206" s="2" t="s">
+      <c r="H206" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I206" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J206" s="2">
@@ -10763,13 +10831,13 @@
       <c r="F207" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G207" s="2" t="s">
+      <c r="G207" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H207" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I207" s="2" t="s">
+      <c r="H207" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I207" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J207" s="2">
@@ -10798,13 +10866,13 @@
       <c r="F208" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G208" s="2" t="s">
+      <c r="G208" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H208" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I208" s="2" t="s">
+      <c r="H208" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I208" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J208" s="2">
@@ -10833,13 +10901,13 @@
       <c r="F209" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G209" s="2" t="s">
+      <c r="G209" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H209" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I209" s="2" t="s">
+      <c r="H209" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I209" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J209" s="2">
@@ -10868,13 +10936,13 @@
       <c r="F210" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G210" s="2" t="s">
+      <c r="G210" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H210" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I210" s="2" t="s">
+      <c r="H210" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I210" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J210" s="2">
@@ -10903,13 +10971,13 @@
       <c r="F211" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G211" s="2" t="s">
+      <c r="G211" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H211" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I211" s="2" t="s">
+      <c r="H211" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I211" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J211" s="2">
@@ -10938,13 +11006,13 @@
       <c r="F212" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G212" s="2" t="s">
+      <c r="G212" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H212" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I212" s="2" t="s">
+      <c r="H212" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I212" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J212" s="2">
@@ -10973,13 +11041,13 @@
       <c r="F213" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G213" s="2" t="s">
+      <c r="G213" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H213" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I213" s="2" t="s">
+      <c r="H213" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I213" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J213" s="2">
@@ -11008,13 +11076,13 @@
       <c r="F214" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G214" s="2" t="s">
+      <c r="G214" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H214" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I214" s="2" t="s">
+      <c r="H214" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I214" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J214" s="2">
@@ -11043,13 +11111,13 @@
       <c r="F215" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G215" s="2" t="s">
+      <c r="G215" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H215" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I215" s="2" t="s">
+      <c r="H215" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I215" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J215" s="2">
@@ -11078,13 +11146,13 @@
       <c r="F216" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G216" s="2" t="s">
+      <c r="G216" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H216" s="2" t="s">
+      <c r="H216" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I216" s="2" t="s">
+      <c r="I216" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J216" s="2">
@@ -11113,13 +11181,13 @@
       <c r="F217" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G217" s="2" t="s">
+      <c r="G217" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H217" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I217" s="2" t="s">
+      <c r="H217" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I217" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J217" s="2">
@@ -11148,13 +11216,13 @@
       <c r="F218" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G218" s="2" t="s">
+      <c r="G218" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H218" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I218" s="2" t="s">
+      <c r="H218" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I218" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J218" s="2">
@@ -11183,13 +11251,13 @@
       <c r="F219" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G219" s="2" t="s">
+      <c r="G219" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H219" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I219" s="2" t="s">
+      <c r="H219" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I219" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J219" s="2">
@@ -11218,13 +11286,13 @@
       <c r="F220" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G220" s="2" t="s">
+      <c r="G220" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H220" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I220" s="2" t="s">
+      <c r="H220" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I220" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J220" s="2">
@@ -11253,13 +11321,13 @@
       <c r="F221" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G221" s="2" t="s">
+      <c r="G221" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H221" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I221" s="2" t="s">
+      <c r="H221" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I221" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J221" s="2">
@@ -11288,13 +11356,13 @@
       <c r="F222" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G222" s="2" t="s">
+      <c r="G222" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H222" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I222" s="2" t="s">
+      <c r="H222" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I222" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J222" s="2">
@@ -11320,16 +11388,16 @@
       <c r="E223" s="2">
         <v>120000</v>
       </c>
-      <c r="F223" s="4">
-        <v>240000</v>
-      </c>
-      <c r="G223" s="2" t="s">
+      <c r="F223" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="G223" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H223" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I223" s="2" t="s">
+      <c r="H223" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I223" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J223" s="2">
@@ -11358,13 +11426,13 @@
       <c r="F224" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G224" s="2" t="s">
+      <c r="G224" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H224" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I224" s="2" t="s">
+      <c r="H224" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I224" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J224" s="2">
@@ -11393,13 +11461,13 @@
       <c r="F225" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G225" s="2" t="s">
+      <c r="G225" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H225" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I225" s="2" t="s">
+      <c r="H225" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I225" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J225" s="2">
@@ -11428,13 +11496,13 @@
       <c r="F226" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G226" s="2" t="s">
+      <c r="G226" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H226" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I226" s="2" t="s">
+      <c r="H226" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I226" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J226" s="2">
@@ -11463,13 +11531,13 @@
       <c r="F227" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G227" s="2" t="s">
+      <c r="G227" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H227" s="2" t="s">
+      <c r="H227" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I227" s="2" t="s">
+      <c r="I227" s="11" t="s">
         <v>26</v>
       </c>
       <c r="J227" s="2">
@@ -11498,13 +11566,13 @@
       <c r="F228" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G228" s="2" t="s">
+      <c r="G228" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H228" s="2" t="s">
+      <c r="H228" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I228" s="2" t="s">
+      <c r="I228" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J228" s="2">
@@ -11530,16 +11598,16 @@
       <c r="E229" s="2">
         <v>55000</v>
       </c>
-      <c r="F229" s="4">
-        <v>130000</v>
-      </c>
-      <c r="G229" s="2" t="s">
+      <c r="F229" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="G229" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H229" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I229" s="2" t="s">
+      <c r="H229" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I229" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J229" s="2">
@@ -11568,13 +11636,13 @@
       <c r="F230" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G230" s="2" t="s">
+      <c r="G230" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H230" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I230" s="2" t="s">
+      <c r="H230" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I230" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J230" s="2">
@@ -11603,13 +11671,13 @@
       <c r="F231" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G231" s="2" t="s">
+      <c r="G231" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H231" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I231" s="2" t="s">
+      <c r="H231" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I231" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J231" s="2">
@@ -11638,13 +11706,13 @@
       <c r="F232" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G232" s="2" t="s">
+      <c r="G232" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H232" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I232" s="2" t="s">
+      <c r="H232" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I232" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J232" s="2">
@@ -11673,13 +11741,13 @@
       <c r="F233" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G233" s="2" t="s">
+      <c r="G233" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H233" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I233" s="2" t="s">
+      <c r="H233" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I233" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J233" s="2">
@@ -11708,13 +11776,13 @@
       <c r="F234" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G234" s="2" t="s">
+      <c r="G234" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H234" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I234" s="2" t="s">
+      <c r="H234" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I234" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J234" s="2">
@@ -11743,13 +11811,13 @@
       <c r="F235" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G235" s="2" t="s">
+      <c r="G235" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H235" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I235" s="2" t="s">
+      <c r="H235" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I235" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J235" s="2">
@@ -11778,13 +11846,13 @@
       <c r="F236" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G236" s="2" t="s">
+      <c r="G236" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H236" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I236" s="2" t="s">
+      <c r="H236" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I236" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J236" s="2">
@@ -11810,16 +11878,16 @@
       <c r="E237" s="2">
         <v>82000</v>
       </c>
-      <c r="F237" s="4">
-        <v>159000</v>
-      </c>
-      <c r="G237" s="2" t="s">
+      <c r="F237" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="G237" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H237" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I237" s="2" t="s">
+      <c r="H237" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I237" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J237" s="2">
@@ -11848,13 +11916,13 @@
       <c r="F238" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G238" s="2" t="s">
+      <c r="G238" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H238" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I238" s="2" t="s">
+      <c r="H238" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I238" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J238" s="2">
@@ -11883,13 +11951,13 @@
       <c r="F239" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G239" s="2" t="s">
+      <c r="G239" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H239" s="2" t="s">
+      <c r="H239" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I239" s="2" t="s">
+      <c r="I239" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J239" s="2">
@@ -11918,13 +11986,13 @@
       <c r="F240" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G240" s="2" t="s">
+      <c r="G240" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H240" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I240" s="2" t="s">
+      <c r="H240" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I240" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J240" s="2">
@@ -11953,13 +12021,13 @@
       <c r="F241" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G241" s="2" t="s">
+      <c r="G241" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H241" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I241" s="2" t="s">
+      <c r="H241" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I241" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J241" s="2">
@@ -11988,13 +12056,13 @@
       <c r="F242" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G242" s="2" t="s">
+      <c r="G242" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H242" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I242" s="2" t="s">
+      <c r="H242" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I242" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J242" s="2">
@@ -12023,13 +12091,13 @@
       <c r="F243" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G243" s="2" t="s">
+      <c r="G243" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H243" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I243" s="2" t="s">
+      <c r="H243" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I243" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J243" s="2">
@@ -12058,13 +12126,13 @@
       <c r="F244" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G244" s="2" t="s">
+      <c r="G244" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H244" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I244" s="2" t="s">
+      <c r="H244" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I244" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J244" s="2">
@@ -12093,13 +12161,13 @@
       <c r="F245" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G245" s="2" t="s">
+      <c r="G245" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H245" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I245" s="2" t="s">
+      <c r="H245" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I245" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J245" s="2">
@@ -12128,13 +12196,13 @@
       <c r="F246" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G246" s="2" t="s">
+      <c r="G246" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H246" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I246" s="2" t="s">
+      <c r="H246" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I246" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J246" s="2">
@@ -12160,16 +12228,16 @@
       <c r="E247" s="2">
         <v>60000</v>
       </c>
-      <c r="F247" s="4">
-        <v>190000</v>
-      </c>
-      <c r="G247" s="2" t="s">
+      <c r="F247" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="G247" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H247" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I247" s="2" t="s">
+      <c r="H247" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I247" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J247" s="2">
@@ -12198,13 +12266,13 @@
       <c r="F248" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G248" s="2" t="s">
+      <c r="G248" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H248" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I248" s="2" t="s">
+      <c r="H248" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I248" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J248" s="2">
@@ -12233,13 +12301,13 @@
       <c r="F249" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G249" s="2" t="s">
+      <c r="G249" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H249" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I249" s="2" t="s">
+      <c r="H249" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I249" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J249" s="2">
@@ -12265,16 +12333,16 @@
       <c r="E250" s="2">
         <v>33500</v>
       </c>
-      <c r="F250" s="4">
-        <v>67000</v>
-      </c>
-      <c r="G250" s="2" t="s">
+      <c r="F250" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="G250" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H250" s="2" t="s">
+      <c r="H250" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I250" s="2" t="s">
+      <c r="I250" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J250" s="2">
@@ -12303,13 +12371,13 @@
       <c r="F251" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G251" s="2" t="s">
+      <c r="G251" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H251" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I251" s="2" t="s">
+      <c r="H251" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I251" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J251" s="2">
@@ -12338,13 +12406,13 @@
       <c r="F252" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G252" s="2" t="s">
+      <c r="G252" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H252" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I252" s="2" t="s">
+      <c r="H252" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I252" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J252" s="2">
@@ -12373,13 +12441,13 @@
       <c r="F253" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G253" s="2" t="s">
+      <c r="G253" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H253" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I253" s="2" t="s">
+      <c r="H253" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I253" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J253" s="2">
@@ -12408,13 +12476,13 @@
       <c r="F254" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G254" s="2" t="s">
+      <c r="G254" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H254" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I254" s="2" t="s">
+      <c r="H254" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I254" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J254" s="2">
@@ -12443,13 +12511,13 @@
       <c r="F255" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G255" s="2" t="s">
+      <c r="G255" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H255" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I255" s="2" t="s">
+      <c r="H255" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I255" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J255" s="2">
@@ -12478,13 +12546,13 @@
       <c r="F256" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G256" s="2" t="s">
+      <c r="G256" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H256" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I256" s="2" t="s">
+      <c r="H256" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I256" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J256" s="2">
@@ -12513,13 +12581,13 @@
       <c r="F257" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G257" s="2" t="s">
+      <c r="G257" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H257" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I257" s="2" t="s">
+      <c r="H257" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I257" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J257" s="2">
@@ -12548,13 +12616,13 @@
       <c r="F258" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G258" s="2" t="s">
+      <c r="G258" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H258" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I258" s="2" t="s">
+      <c r="H258" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I258" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J258" s="2">
@@ -12583,13 +12651,13 @@
       <c r="F259" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G259" s="2" t="s">
+      <c r="G259" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H259" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I259" s="2" t="s">
+      <c r="H259" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I259" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J259" s="2">
@@ -12618,13 +12686,13 @@
       <c r="F260" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G260" s="2" t="s">
+      <c r="G260" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H260" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I260" s="2" t="s">
+      <c r="H260" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I260" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J260" s="2">
@@ -12653,13 +12721,13 @@
       <c r="F261" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G261" s="2" t="s">
+      <c r="G261" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H261" s="2" t="s">
+      <c r="H261" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I261" s="2" t="s">
+      <c r="I261" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J261" s="2">
@@ -12688,13 +12756,13 @@
       <c r="F262" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G262" s="2" t="s">
+      <c r="G262" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H262" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I262" s="2" t="s">
+      <c r="H262" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I262" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J262" s="2">
@@ -12723,13 +12791,13 @@
       <c r="F263" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G263" s="2" t="s">
+      <c r="G263" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H263" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I263" s="2" t="s">
+      <c r="H263" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I263" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J263" s="2">
@@ -12758,13 +12826,13 @@
       <c r="F264" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G264" s="2" t="s">
+      <c r="G264" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H264" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I264" s="2" t="s">
+      <c r="H264" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I264" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J264" s="2">
@@ -12793,13 +12861,13 @@
       <c r="F265" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G265" s="2" t="s">
+      <c r="G265" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H265" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I265" s="2" t="s">
+      <c r="H265" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I265" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J265" s="2">
@@ -12828,13 +12896,13 @@
       <c r="F266" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G266" s="2" t="s">
+      <c r="G266" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H266" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I266" s="2" t="s">
+      <c r="H266" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I266" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J266" s="2">
@@ -12863,13 +12931,13 @@
       <c r="F267" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G267" s="2" t="s">
+      <c r="G267" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H267" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I267" s="2" t="s">
+      <c r="H267" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I267" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J267" s="2">
@@ -12898,13 +12966,13 @@
       <c r="F268" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G268" s="2" t="s">
+      <c r="G268" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H268" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I268" s="2" t="s">
+      <c r="H268" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I268" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J268" s="2">
@@ -12933,13 +13001,13 @@
       <c r="F269" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G269" s="2" t="s">
+      <c r="G269" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H269" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I269" s="2" t="s">
+      <c r="H269" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I269" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J269" s="2">
@@ -12968,13 +13036,13 @@
       <c r="F270" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G270" s="2" t="s">
+      <c r="G270" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H270" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I270" s="2" t="s">
+      <c r="H270" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I270" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J270" s="2">
@@ -13003,13 +13071,13 @@
       <c r="F271" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G271" s="2" t="s">
+      <c r="G271" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H271" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I271" s="2" t="s">
+      <c r="H271" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I271" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J271" s="2">
@@ -13038,13 +13106,13 @@
       <c r="F272" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G272" s="2" t="s">
+      <c r="G272" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H272" s="2" t="s">
+      <c r="H272" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I272" s="2" t="s">
+      <c r="I272" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J272" s="2">
@@ -13073,13 +13141,13 @@
       <c r="F273" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G273" s="2" t="s">
+      <c r="G273" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H273" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I273" s="2" t="s">
+      <c r="H273" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I273" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J273" s="2">
@@ -13108,13 +13176,13 @@
       <c r="F274" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G274" s="2" t="s">
+      <c r="G274" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H274" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I274" s="2" t="s">
+      <c r="H274" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I274" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J274" s="2">
@@ -13143,13 +13211,13 @@
       <c r="F275" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G275" s="2" t="s">
+      <c r="G275" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H275" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I275" s="2" t="s">
+      <c r="H275" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I275" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J275" s="2">
@@ -13178,13 +13246,13 @@
       <c r="F276" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G276" s="2" t="s">
+      <c r="G276" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H276" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I276" s="2" t="s">
+      <c r="H276" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I276" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J276" s="2">
@@ -13213,13 +13281,13 @@
       <c r="F277" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G277" s="2" t="s">
+      <c r="G277" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H277" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I277" s="2" t="s">
+      <c r="H277" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I277" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J277" s="2">
@@ -13248,13 +13316,13 @@
       <c r="F278" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G278" s="2" t="s">
+      <c r="G278" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H278" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I278" s="2" t="s">
+      <c r="H278" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I278" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J278" s="2">
@@ -13283,13 +13351,13 @@
       <c r="F279" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G279" s="2" t="s">
+      <c r="G279" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H279" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I279" s="2" t="s">
+      <c r="H279" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I279" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J279" s="2">
@@ -13318,13 +13386,13 @@
       <c r="F280" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G280" s="2" t="s">
+      <c r="G280" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H280" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I280" s="2" t="s">
+      <c r="H280" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I280" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J280" s="2">
@@ -13353,13 +13421,13 @@
       <c r="F281" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G281" s="2" t="s">
+      <c r="G281" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H281" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I281" s="2" t="s">
+      <c r="H281" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I281" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J281" s="2">
@@ -13388,13 +13456,13 @@
       <c r="F282" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G282" s="2" t="s">
+      <c r="G282" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H282" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I282" s="2" t="s">
+      <c r="H282" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I282" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J282" s="2">
@@ -13420,16 +13488,16 @@
       <c r="E283" s="2">
         <v>20000</v>
       </c>
-      <c r="F283" s="4">
-        <v>150000</v>
-      </c>
-      <c r="G283" s="2" t="s">
+      <c r="F283" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="G283" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H283" s="2" t="s">
+      <c r="H283" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I283" s="2" t="s">
+      <c r="I283" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J283" s="2">
@@ -13458,13 +13526,13 @@
       <c r="F284" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G284" s="2" t="s">
+      <c r="G284" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H284" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I284" s="2" t="s">
+      <c r="H284" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I284" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J284" s="2">
@@ -13493,13 +13561,13 @@
       <c r="F285" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G285" s="2" t="s">
+      <c r="G285" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H285" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I285" s="2" t="s">
+      <c r="H285" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I285" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J285" s="2">
@@ -13528,13 +13596,13 @@
       <c r="F286" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G286" s="2" t="s">
+      <c r="G286" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H286" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I286" s="2" t="s">
+      <c r="H286" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I286" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J286" s="2">
@@ -13563,13 +13631,13 @@
       <c r="F287" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G287" s="2" t="s">
+      <c r="G287" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H287" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I287" s="2" t="s">
+      <c r="H287" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I287" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J287" s="2">
@@ -13598,13 +13666,13 @@
       <c r="F288" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G288" s="2" t="s">
+      <c r="G288" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H288" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I288" s="2" t="s">
+      <c r="H288" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I288" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J288" s="2">
@@ -13633,13 +13701,13 @@
       <c r="F289" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G289" s="2" t="s">
+      <c r="G289" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H289" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I289" s="2" t="s">
+      <c r="H289" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I289" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J289" s="2">
@@ -13668,13 +13736,13 @@
       <c r="F290" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G290" s="2" t="s">
+      <c r="G290" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H290" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I290" s="2" t="s">
+      <c r="H290" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I290" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J290" s="2">
@@ -13703,13 +13771,13 @@
       <c r="F291" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G291" s="2" t="s">
+      <c r="G291" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H291" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I291" s="2" t="s">
+      <c r="H291" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I291" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J291" s="2">
@@ -13735,16 +13803,16 @@
       <c r="E292" s="2">
         <v>165000</v>
       </c>
-      <c r="F292" s="4">
-        <v>253000</v>
-      </c>
-      <c r="G292" s="2" t="s">
+      <c r="F292" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="G292" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H292" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I292" s="2" t="s">
+      <c r="H292" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I292" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J292" s="2">
@@ -13773,13 +13841,13 @@
       <c r="F293" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G293" s="2" t="s">
+      <c r="G293" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H293" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I293" s="2" t="s">
+      <c r="H293" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I293" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J293" s="2">
@@ -13808,13 +13876,13 @@
       <c r="F294" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G294" s="2" t="s">
+      <c r="G294" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H294" s="2" t="s">
+      <c r="H294" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I294" s="2" t="s">
+      <c r="I294" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J294" s="2">
@@ -13843,13 +13911,13 @@
       <c r="F295" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G295" s="2" t="s">
+      <c r="G295" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H295" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I295" s="2" t="s">
+      <c r="H295" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I295" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J295" s="2">
@@ -13878,13 +13946,13 @@
       <c r="F296" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G296" s="2" t="s">
+      <c r="G296" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H296" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I296" s="2" t="s">
+      <c r="H296" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I296" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J296" s="2">
@@ -13913,13 +13981,13 @@
       <c r="F297" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G297" s="2" t="s">
+      <c r="G297" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H297" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I297" s="2" t="s">
+      <c r="H297" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I297" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J297" s="2">
@@ -13948,13 +14016,13 @@
       <c r="F298" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G298" s="2" t="s">
+      <c r="G298" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H298" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I298" s="2" t="s">
+      <c r="H298" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I298" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J298" s="2">
@@ -13983,13 +14051,13 @@
       <c r="F299" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G299" s="2" t="s">
+      <c r="G299" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H299" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I299" s="2" t="s">
+      <c r="H299" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I299" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J299" s="2">
@@ -14018,13 +14086,13 @@
       <c r="F300" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G300" s="2" t="s">
+      <c r="G300" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H300" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I300" s="2" t="s">
+      <c r="H300" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I300" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J300" s="2">
@@ -14053,13 +14121,13 @@
       <c r="F301" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G301" s="2" t="s">
+      <c r="G301" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H301" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I301" s="2" t="s">
+      <c r="H301" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I301" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J301" s="2">
@@ -14088,13 +14156,13 @@
       <c r="F302" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G302" s="2" t="s">
+      <c r="G302" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H302" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I302" s="2" t="s">
+      <c r="H302" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I302" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J302" s="2">
@@ -14123,13 +14191,13 @@
       <c r="F303" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G303" s="2" t="s">
+      <c r="G303" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H303" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I303" s="2" t="s">
+      <c r="H303" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I303" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J303" s="2">
@@ -14158,13 +14226,13 @@
       <c r="F304" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G304" s="2" t="s">
+      <c r="G304" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H304" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I304" s="2" t="s">
+      <c r="H304" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I304" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J304" s="2">
@@ -14193,13 +14261,13 @@
       <c r="F305" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G305" s="2" t="s">
+      <c r="G305" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H305" s="2" t="s">
+      <c r="H305" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I305" s="2" t="s">
+      <c r="I305" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J305" s="2">
@@ -14228,13 +14296,13 @@
       <c r="F306" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G306" s="2" t="s">
+      <c r="G306" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H306" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I306" s="2" t="s">
+      <c r="H306" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I306" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J306" s="2">
@@ -14263,13 +14331,13 @@
       <c r="F307" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G307" s="2" t="s">
+      <c r="G307" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H307" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I307" s="2" t="s">
+      <c r="H307" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I307" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J307" s="2">
@@ -14298,13 +14366,13 @@
       <c r="F308" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G308" s="2" t="s">
+      <c r="G308" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H308" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I308" s="2" t="s">
+      <c r="H308" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I308" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J308" s="2">
@@ -14333,13 +14401,13 @@
       <c r="F309" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G309" s="2" t="s">
+      <c r="G309" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H309" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I309" s="2" t="s">
+      <c r="H309" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I309" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J309" s="2">
@@ -14368,13 +14436,13 @@
       <c r="F310" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G310" s="2" t="s">
+      <c r="G310" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H310" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I310" s="2" t="s">
+      <c r="H310" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I310" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J310" s="2">
@@ -14403,13 +14471,13 @@
       <c r="F311" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G311" s="2" t="s">
+      <c r="G311" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H311" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I311" s="2" t="s">
+      <c r="H311" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I311" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J311" s="2">
@@ -14438,13 +14506,13 @@
       <c r="F312" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G312" s="2" t="s">
+      <c r="G312" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H312" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I312" s="2" t="s">
+      <c r="H312" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I312" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J312" s="2">
@@ -14473,13 +14541,13 @@
       <c r="F313" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G313" s="2" t="s">
+      <c r="G313" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H313" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I313" s="2" t="s">
+      <c r="H313" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I313" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J313" s="2">
@@ -14508,13 +14576,13 @@
       <c r="F314" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G314" s="2" t="s">
+      <c r="G314" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H314" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I314" s="2" t="s">
+      <c r="H314" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I314" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J314" s="2">
@@ -14543,13 +14611,13 @@
       <c r="F315" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G315" s="2" t="s">
+      <c r="G315" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H315" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I315" s="2" t="s">
+      <c r="H315" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I315" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J315" s="2">
@@ -14575,16 +14643,16 @@
       <c r="E316" s="2">
         <v>42000</v>
       </c>
-      <c r="F316" s="4">
-        <v>132000</v>
-      </c>
-      <c r="G316" s="2" t="s">
+      <c r="F316" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="G316" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H316" s="2" t="s">
+      <c r="H316" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I316" s="2" t="s">
+      <c r="I316" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J316" s="2">
@@ -14613,13 +14681,13 @@
       <c r="F317" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G317" s="2" t="s">
+      <c r="G317" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H317" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I317" s="2" t="s">
+      <c r="H317" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I317" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J317" s="2">
@@ -14648,13 +14716,13 @@
       <c r="F318" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G318" s="2" t="s">
+      <c r="G318" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H318" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I318" s="2" t="s">
+      <c r="H318" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I318" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J318" s="2">
@@ -14683,13 +14751,13 @@
       <c r="F319" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G319" s="2" t="s">
+      <c r="G319" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H319" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I319" s="2" t="s">
+      <c r="H319" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I319" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J319" s="2">
@@ -14718,13 +14786,13 @@
       <c r="F320" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G320" s="2" t="s">
+      <c r="G320" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H320" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I320" s="2" t="s">
+      <c r="H320" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I320" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J320" s="2">
@@ -14753,13 +14821,13 @@
       <c r="F321" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G321" s="2" t="s">
+      <c r="G321" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H321" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I321" s="2" t="s">
+      <c r="H321" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I321" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J321" s="2">
@@ -14788,13 +14856,13 @@
       <c r="F322" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G322" s="2" t="s">
+      <c r="G322" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H322" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I322" s="2" t="s">
+      <c r="H322" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I322" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J322" s="2">
@@ -14823,13 +14891,13 @@
       <c r="F323" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G323" s="2" t="s">
+      <c r="G323" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H323" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I323" s="2" t="s">
+      <c r="H323" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I323" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J323" s="2">
@@ -14858,13 +14926,13 @@
       <c r="F324" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G324" s="2" t="s">
+      <c r="G324" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H324" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I324" s="2" t="s">
+      <c r="H324" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I324" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J324" s="2">
@@ -14893,13 +14961,13 @@
       <c r="F325" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G325" s="2" t="s">
+      <c r="G325" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H325" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I325" s="2" t="s">
+      <c r="H325" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I325" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J325" s="2">
@@ -14928,13 +14996,13 @@
       <c r="F326" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G326" s="2" t="s">
+      <c r="G326" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H326" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I326" s="2" t="s">
+      <c r="H326" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I326" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J326" s="2">
@@ -14963,13 +15031,13 @@
       <c r="F327" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G327" s="2" t="s">
+      <c r="G327" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H327" s="2" t="s">
+      <c r="H327" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I327" s="2" t="s">
+      <c r="I327" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J327" s="2">
@@ -14998,13 +15066,13 @@
       <c r="F328" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G328" s="2" t="s">
+      <c r="G328" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H328" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I328" s="2" t="s">
+      <c r="H328" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I328" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J328" s="2">
@@ -15033,13 +15101,13 @@
       <c r="F329" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G329" s="2" t="s">
+      <c r="G329" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H329" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I329" s="2" t="s">
+      <c r="H329" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I329" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J329" s="2">
@@ -15068,13 +15136,13 @@
       <c r="F330" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G330" s="2" t="s">
+      <c r="G330" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H330" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I330" s="2" t="s">
+      <c r="H330" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I330" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J330" s="2">
@@ -15103,13 +15171,13 @@
       <c r="F331" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G331" s="2" t="s">
+      <c r="G331" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H331" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I331" s="2" t="s">
+      <c r="H331" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I331" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J331" s="2">
@@ -15138,13 +15206,13 @@
       <c r="F332" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G332" s="2" t="s">
+      <c r="G332" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H332" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I332" s="2" t="s">
+      <c r="H332" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I332" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J332" s="2">
@@ -15173,13 +15241,13 @@
       <c r="F333" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G333" s="2" t="s">
+      <c r="G333" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H333" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I333" s="2" t="s">
+      <c r="H333" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I333" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J333" s="2">
@@ -15208,13 +15276,13 @@
       <c r="F334" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G334" s="2" t="s">
+      <c r="G334" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H334" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I334" s="2" t="s">
+      <c r="H334" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I334" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J334" s="2">
@@ -15243,13 +15311,13 @@
       <c r="F335" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G335" s="2" t="s">
+      <c r="G335" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H335" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I335" s="2" t="s">
+      <c r="H335" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I335" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J335" s="2">
@@ -15278,13 +15346,13 @@
       <c r="F336" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G336" s="2" t="s">
+      <c r="G336" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H336" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I336" s="2" t="s">
+      <c r="H336" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I336" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J336" s="2">
@@ -15313,13 +15381,13 @@
       <c r="F337" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G337" s="2" t="s">
+      <c r="G337" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H337" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I337" s="2" t="s">
+      <c r="H337" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I337" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J337" s="2">
@@ -15348,13 +15416,13 @@
       <c r="F338" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G338" s="2" t="s">
+      <c r="G338" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H338" s="2" t="s">
+      <c r="H338" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I338" s="2" t="s">
+      <c r="I338" s="11" t="s">
         <v>26</v>
       </c>
       <c r="J338" s="2">
@@ -15383,13 +15451,13 @@
       <c r="F339" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G339" s="2" t="s">
+      <c r="G339" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H339" s="2" t="s">
+      <c r="H339" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I339" s="2" t="s">
+      <c r="I339" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J339" s="2">
@@ -15418,13 +15486,13 @@
       <c r="F340" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G340" s="2" t="s">
+      <c r="G340" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H340" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I340" s="2" t="s">
+      <c r="H340" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I340" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J340" s="2">
@@ -15453,13 +15521,13 @@
       <c r="F341" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G341" s="2" t="s">
+      <c r="G341" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H341" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I341" s="2" t="s">
+      <c r="H341" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I341" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J341" s="2">
@@ -15488,13 +15556,13 @@
       <c r="F342" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G342" s="2" t="s">
+      <c r="G342" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H342" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I342" s="2" t="s">
+      <c r="H342" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I342" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J342" s="2">
@@ -15523,13 +15591,13 @@
       <c r="F343" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G343" s="2" t="s">
+      <c r="G343" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H343" s="2" t="s">
+      <c r="H343" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I343" s="2" t="s">
+      <c r="I343" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J343" s="2">
@@ -15558,13 +15626,13 @@
       <c r="F344" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G344" s="2" t="s">
+      <c r="G344" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H344" s="2" t="s">
+      <c r="H344" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I344" s="2" t="s">
+      <c r="I344" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J344" s="2">
@@ -15593,13 +15661,13 @@
       <c r="F345" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G345" s="2" t="s">
+      <c r="G345" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H345" s="2" t="s">
+      <c r="H345" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I345" s="2" t="s">
+      <c r="I345" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J345" s="2">
@@ -15628,13 +15696,13 @@
       <c r="F346" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G346" s="2" t="s">
+      <c r="G346" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H346" s="2" t="s">
+      <c r="H346" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I346" s="2" t="s">
+      <c r="I346" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J346" s="2">
@@ -15663,13 +15731,13 @@
       <c r="F347" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G347" s="2" t="s">
+      <c r="G347" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H347" s="2" t="s">
+      <c r="H347" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I347" s="2" t="s">
+      <c r="I347" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J347" s="2">
@@ -15698,13 +15766,13 @@
       <c r="F348" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G348" s="2" t="s">
+      <c r="G348" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H348" s="2" t="s">
+      <c r="H348" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I348" s="2" t="s">
+      <c r="I348" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J348" s="2">
@@ -15733,13 +15801,13 @@
       <c r="F349" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G349" s="2" t="s">
+      <c r="G349" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H349" s="2" t="s">
+      <c r="H349" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I349" s="2" t="s">
+      <c r="I349" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J349" s="2">
@@ -15768,13 +15836,13 @@
       <c r="F350" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G350" s="2" t="s">
+      <c r="G350" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H350" s="2" t="s">
+      <c r="H350" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I350" s="2" t="s">
+      <c r="I350" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J350" s="2">
@@ -15803,13 +15871,13 @@
       <c r="F351" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G351" s="2" t="s">
+      <c r="G351" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H351" s="2" t="s">
+      <c r="H351" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I351" s="2" t="s">
+      <c r="I351" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J351" s="2">
@@ -15838,13 +15906,13 @@
       <c r="F352" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G352" s="2" t="s">
+      <c r="G352" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H352" s="2" t="s">
+      <c r="H352" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I352" s="2" t="s">
+      <c r="I352" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J352" s="2">
@@ -15873,13 +15941,13 @@
       <c r="F353" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G353" s="2" t="s">
+      <c r="G353" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H353" s="2" t="s">
+      <c r="H353" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I353" s="2" t="s">
+      <c r="I353" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J353" s="2">
@@ -15908,13 +15976,13 @@
       <c r="F354" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G354" s="2" t="s">
+      <c r="G354" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H354" s="2" t="s">
+      <c r="H354" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I354" s="2" t="s">
+      <c r="I354" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J354" s="2">
@@ -15943,13 +16011,13 @@
       <c r="F355" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G355" s="2" t="s">
+      <c r="G355" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H355" s="2" t="s">
+      <c r="H355" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I355" s="2" t="s">
+      <c r="I355" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J355" s="2">
@@ -15978,13 +16046,13 @@
       <c r="F356" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G356" s="2" t="s">
+      <c r="G356" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H356" s="2" t="s">
+      <c r="H356" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I356" s="2" t="s">
+      <c r="I356" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J356" s="2">
@@ -16013,13 +16081,13 @@
       <c r="F357" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G357" s="2" t="s">
+      <c r="G357" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H357" s="2" t="s">
+      <c r="H357" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I357" s="2" t="s">
+      <c r="I357" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J357" s="2">
@@ -16048,13 +16116,13 @@
       <c r="F358" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G358" s="2" t="s">
+      <c r="G358" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H358" s="2" t="s">
+      <c r="H358" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I358" s="2" t="s">
+      <c r="I358" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J358" s="2">
@@ -16083,13 +16151,13 @@
       <c r="F359" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G359" s="2" t="s">
+      <c r="G359" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H359" s="2" t="s">
+      <c r="H359" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I359" s="2" t="s">
+      <c r="I359" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J359" s="2">
@@ -16118,13 +16186,13 @@
       <c r="F360" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G360" s="2" t="s">
+      <c r="G360" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H360" s="2" t="s">
+      <c r="H360" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I360" s="2" t="s">
+      <c r="I360" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J360" s="2">
@@ -16150,16 +16218,16 @@
       <c r="E361" s="2">
         <v>100000</v>
       </c>
-      <c r="F361" s="4">
-        <v>200000</v>
-      </c>
-      <c r="G361" s="2" t="s">
+      <c r="F361" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="G361" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H361" s="2" t="s">
+      <c r="H361" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I361" s="2" t="s">
+      <c r="I361" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J361" s="2">
@@ -16185,16 +16253,16 @@
       <c r="E362" s="2">
         <v>75000</v>
       </c>
-      <c r="F362" s="4">
-        <v>175000</v>
-      </c>
-      <c r="G362" s="2" t="s">
+      <c r="F362" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="G362" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H362" s="2" t="s">
+      <c r="H362" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I362" s="2" t="s">
+      <c r="I362" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J362" s="2">
@@ -16223,13 +16291,13 @@
       <c r="F363" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G363" s="2" t="s">
+      <c r="G363" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H363" s="2" t="s">
+      <c r="H363" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I363" s="2" t="s">
+      <c r="I363" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J363" s="2">
@@ -16255,16 +16323,16 @@
       <c r="E364" s="2">
         <v>90000</v>
       </c>
-      <c r="F364" s="4">
-        <v>185000</v>
-      </c>
-      <c r="G364" s="2" t="s">
+      <c r="F364" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="G364" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H364" s="2" t="s">
+      <c r="H364" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I364" s="2" t="s">
+      <c r="I364" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J364" s="2">
@@ -16293,13 +16361,13 @@
       <c r="F365" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G365" s="2" t="s">
+      <c r="G365" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H365" s="2" t="s">
+      <c r="H365" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I365" s="2" t="s">
+      <c r="I365" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J365" s="2">
@@ -16328,13 +16396,13 @@
       <c r="F366" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G366" s="2" t="s">
+      <c r="G366" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H366" s="2" t="s">
+      <c r="H366" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I366" s="2" t="s">
+      <c r="I366" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J366" s="2">
@@ -16363,13 +16431,13 @@
       <c r="F367" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G367" s="2" t="s">
+      <c r="G367" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H367" s="2" t="s">
+      <c r="H367" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I367" s="2" t="s">
+      <c r="I367" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J367" s="2">
@@ -16398,13 +16466,13 @@
       <c r="F368" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G368" s="2" t="s">
+      <c r="G368" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H368" s="2" t="s">
+      <c r="H368" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I368" s="2" t="s">
+      <c r="I368" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J368" s="2">
@@ -16433,13 +16501,13 @@
       <c r="F369" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G369" s="2" t="s">
+      <c r="G369" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H369" s="2" t="s">
+      <c r="H369" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I369" s="2" t="s">
+      <c r="I369" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J369" s="2">
@@ -16468,13 +16536,13 @@
       <c r="F370" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G370" s="2" t="s">
+      <c r="G370" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H370" s="2" t="s">
+      <c r="H370" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I370" s="2" t="s">
+      <c r="I370" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J370" s="2">
@@ -16503,13 +16571,13 @@
       <c r="F371" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G371" s="2" t="s">
+      <c r="G371" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H371" s="2" t="s">
+      <c r="H371" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I371" s="2" t="s">
+      <c r="I371" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J371" s="2">
@@ -16538,13 +16606,13 @@
       <c r="F372" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G372" s="2" t="s">
+      <c r="G372" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H372" s="2" t="s">
+      <c r="H372" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I372" s="2" t="s">
+      <c r="I372" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J372" s="2">
@@ -16573,13 +16641,13 @@
       <c r="F373" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G373" s="2" t="s">
+      <c r="G373" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H373" s="2" t="s">
+      <c r="H373" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I373" s="2" t="s">
+      <c r="I373" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J373" s="2">
@@ -16608,13 +16676,13 @@
       <c r="F374" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G374" s="2" t="s">
+      <c r="G374" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H374" s="2" t="s">
+      <c r="H374" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I374" s="2" t="s">
+      <c r="I374" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J374" s="2">
@@ -16643,13 +16711,13 @@
       <c r="F375" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G375" s="2" t="s">
+      <c r="G375" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H375" s="2" t="s">
+      <c r="H375" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I375" s="2" t="s">
+      <c r="I375" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J375" s="2">
@@ -16678,13 +16746,13 @@
       <c r="F376" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G376" s="2" t="s">
+      <c r="G376" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H376" s="2" t="s">
+      <c r="H376" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I376" s="2" t="s">
+      <c r="I376" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J376" s="2">
@@ -16713,13 +16781,13 @@
       <c r="F377" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G377" s="2" t="s">
+      <c r="G377" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H377" s="2" t="s">
+      <c r="H377" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I377" s="2" t="s">
+      <c r="I377" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J377" s="2">
@@ -16748,13 +16816,13 @@
       <c r="F378" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G378" s="2" t="s">
+      <c r="G378" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H378" s="2" t="s">
+      <c r="H378" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I378" s="2" t="s">
+      <c r="I378" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J378" s="2">
@@ -16783,13 +16851,13 @@
       <c r="F379" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G379" s="2" t="s">
+      <c r="G379" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H379" s="2" t="s">
+      <c r="H379" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I379" s="2" t="s">
+      <c r="I379" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J379" s="2">
@@ -16818,13 +16886,13 @@
       <c r="F380" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G380" s="2" t="s">
+      <c r="G380" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H380" s="2" t="s">
+      <c r="H380" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I380" s="2" t="s">
+      <c r="I380" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J380" s="2">
@@ -16853,13 +16921,13 @@
       <c r="F381" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G381" s="2" t="s">
+      <c r="G381" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H381" s="2" t="s">
+      <c r="H381" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I381" s="2" t="s">
+      <c r="I381" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J381" s="2">
@@ -16888,13 +16956,13 @@
       <c r="F382" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G382" s="2" t="s">
+      <c r="G382" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H382" s="2" t="s">
+      <c r="H382" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I382" s="2" t="s">
+      <c r="I382" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J382" s="2">
@@ -16923,13 +16991,13 @@
       <c r="F383" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G383" s="2" t="s">
+      <c r="G383" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H383" s="2" t="s">
+      <c r="H383" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I383" s="2" t="s">
+      <c r="I383" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J383" s="2">
@@ -16958,13 +17026,13 @@
       <c r="F384" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G384" s="2" t="s">
+      <c r="G384" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H384" s="2" t="s">
+      <c r="H384" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I384" s="2" t="s">
+      <c r="I384" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J384" s="2">
@@ -16993,13 +17061,13 @@
       <c r="F385" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G385" s="2" t="s">
+      <c r="G385" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H385" s="2" t="s">
+      <c r="H385" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I385" s="2" t="s">
+      <c r="I385" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J385" s="2">
@@ -17028,13 +17096,13 @@
       <c r="F386" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G386" s="2" t="s">
+      <c r="G386" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H386" s="2" t="s">
+      <c r="H386" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I386" s="2" t="s">
+      <c r="I386" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J386" s="2">
@@ -17063,13 +17131,13 @@
       <c r="F387" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G387" s="2" t="s">
+      <c r="G387" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H387" s="2" t="s">
+      <c r="H387" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I387" s="2" t="s">
+      <c r="I387" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J387" s="2">
@@ -17098,13 +17166,13 @@
       <c r="F388" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G388" s="2" t="s">
+      <c r="G388" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H388" s="2" t="s">
+      <c r="H388" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I388" s="2" t="s">
+      <c r="I388" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J388" s="2">
@@ -17133,13 +17201,13 @@
       <c r="F389" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G389" s="2" t="s">
+      <c r="G389" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H389" s="2" t="s">
+      <c r="H389" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I389" s="2" t="s">
+      <c r="I389" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J389" s="2">
@@ -17168,13 +17236,13 @@
       <c r="F390" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G390" s="2" t="s">
+      <c r="G390" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H390" s="2" t="s">
+      <c r="H390" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I390" s="2" t="s">
+      <c r="I390" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J390" s="2">
@@ -17203,13 +17271,13 @@
       <c r="F391" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G391" s="2" t="s">
+      <c r="G391" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H391" s="2" t="s">
+      <c r="H391" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I391" s="2" t="s">
+      <c r="I391" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J391" s="2">
@@ -17238,13 +17306,13 @@
       <c r="F392" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G392" s="2" t="s">
+      <c r="G392" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H392" s="2" t="s">
+      <c r="H392" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I392" s="2" t="s">
+      <c r="I392" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J392" s="2">
@@ -17273,13 +17341,13 @@
       <c r="F393" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G393" s="2" t="s">
+      <c r="G393" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H393" s="2" t="s">
+      <c r="H393" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I393" s="2" t="s">
+      <c r="I393" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J393" s="2">
@@ -17308,13 +17376,13 @@
       <c r="F394" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G394" s="2" t="s">
+      <c r="G394" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H394" s="2" t="s">
+      <c r="H394" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I394" s="2" t="s">
+      <c r="I394" s="11" t="s">
         <v>29</v>
       </c>
       <c r="J394" s="2">
@@ -17331,8 +17399,9 @@
       </c>
       <c r="F395">
         <f t="shared" si="1"/>
-        <v>3110000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G395"/>
       <c r="J395">
         <f>SUM(J1:J394)</f>
         <v>3202883</v>

--- a/finance_customer.csv.xlsx
+++ b/finance_customer.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pandas\Finance data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EB5F83-4362-4F58-8C1D-379F32A09359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360E1F00-DA61-4D04-882F-0C9FC0165B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9802DE5F-B1D8-4319-BDEA-30F1B831059A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9802DE5F-B1D8-4319-BDEA-30F1B831059A}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot Table" sheetId="2" r:id="rId1"/>

--- a/finance_customer.csv.xlsx
+++ b/finance_customer.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pandas\Finance data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360E1F00-DA61-4D04-882F-0C9FC0165B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDB26D0-D1ED-44CF-8F45-3A983E145812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9802DE5F-B1D8-4319-BDEA-30F1B831059A}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
-    <pivotCache cacheId="14" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3513" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3515" uniqueCount="747">
   <si>
     <t>customer_id</t>
   </si>
@@ -2222,12 +2222,6 @@
     <t>tot_cur_bal</t>
   </si>
   <si>
-    <t>3nonenonenonenone</t>
-  </si>
-  <si>
-    <t>23nonenonenonenone</t>
-  </si>
-  <si>
     <t>124nonenonenone</t>
   </si>
   <si>
@@ -2252,9 +2246,6 @@
     <t>24nonenonenonenone</t>
   </si>
   <si>
-    <t>13nonenonenonenone</t>
-  </si>
-  <si>
     <t>159nonenonenone</t>
   </si>
   <si>
@@ -2304,6 +2295,12 @@
   </si>
   <si>
     <t>Count of home_ownership</t>
+  </si>
+  <si>
+    <t>2none</t>
+  </si>
+  <si>
+    <t>1none</t>
   </si>
 </sst>
 </file>
@@ -2867,10 +2864,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -14373,107 +14372,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA328EE9-D6A1-4564-A98F-EB239F495583}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A14:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="14">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="6" item="2" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of home_ownership" fld="3" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1BEB0EC-1B93-46CD-AF9B-F4264EF3619B}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1BEB0EC-1B93-46CD-AF9B-F4264EF3619B}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H11:I297" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -15669,8 +15568,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4257A7A8-6D2C-4CF7-952A-0B876954193D}" name="PivotTable2" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4257A7A8-6D2C-4CF7-952A-0B876954193D}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E4:F8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -15740,8 +15639,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D0CA5600-92BA-45FE-80B4-8C71AE4E87C6}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D0CA5600-92BA-45FE-80B4-8C71AE4E87C6}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -16199,6 +16098,106 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA328EE9-D6A1-4564-A98F-EB239F495583}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A14:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" item="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of home_ownership" fld="3" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -16529,7 +16528,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>3</v>
       </c>
       <c r="F2" t="s">
@@ -16537,2462 +16536,2462 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
-        <v>741</v>
+      <c r="A3" s="14" t="s">
+        <v>738</v>
       </c>
       <c r="B3" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>697</v>
+      </c>
+      <c r="B4">
+        <v>22000</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>738</v>
+      </c>
+      <c r="F4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>15215456.32</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>3509473.5079999999</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>19588140.120999999</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>739</v>
+      </c>
+      <c r="B8">
+        <v>38335069.949000001</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>739</v>
+      </c>
+      <c r="F8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>697</v>
-      </c>
-      <c r="B4" s="14">
-        <v>22000</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>741</v>
-      </c>
-      <c r="F4" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="14">
-        <v>15215456.32</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="14">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="14">
-        <v>3509473.5079999999</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="14">
-        <v>19588140.120999999</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="14">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="14" t="s">
+        <v>738</v>
+      </c>
+      <c r="I11" t="s">
         <v>742</v>
       </c>
-      <c r="B8" s="14">
-        <v>38335069.949000001</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>742</v>
-      </c>
-      <c r="F8" s="14">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H11" s="15" t="s">
-        <v>741</v>
-      </c>
-      <c r="I11" t="s">
-        <v>745</v>
-      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12">
         <v>203282</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13">
         <v>1025</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="14" t="s">
+        <v>738</v>
+      </c>
+      <c r="B14" t="s">
+        <v>744</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="I14">
+        <v>272053</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="I15">
+        <v>23872</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>635</v>
+      </c>
+      <c r="I16">
+        <v>7330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="I17">
+        <v>24721</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="I18">
+        <v>41018</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>612</v>
+      </c>
+      <c r="I19">
+        <v>21482</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="I20">
+        <v>24433</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="B21">
+        <v>38</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I21">
+        <v>31172</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22">
+        <v>10003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
+        <v>11</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="I23">
+        <v>43449</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="I24">
+        <v>355619</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
+        <v>739</v>
+      </c>
+      <c r="B25">
+        <v>91</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="I25">
+        <v>45641</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="I26">
+        <v>64932</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="I27">
+        <v>12708</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="I28">
+        <v>21410</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="I29">
+        <v>16834</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="I30">
+        <v>172937</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="I31">
+        <v>39346</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="I32">
+        <v>167438</v>
+      </c>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="I33">
+        <v>30011</v>
+      </c>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="I34">
+        <v>31757</v>
+      </c>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="I35">
+        <v>15697</v>
+      </c>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="I36">
+        <v>19641</v>
+      </c>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="15" t="s">
+        <v>689</v>
+      </c>
+      <c r="I37">
+        <v>178933</v>
+      </c>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="I38">
+        <v>24547</v>
+      </c>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I39">
+        <v>23284</v>
+      </c>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="I40">
+        <v>21474</v>
+      </c>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="I41">
+        <v>51972</v>
+      </c>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="I42">
+        <v>23784</v>
+      </c>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="I43">
+        <v>35653</v>
+      </c>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="I44">
+        <v>294858</v>
+      </c>
+    </row>
+    <row r="45" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H45" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45">
+        <v>31779</v>
+      </c>
+    </row>
+    <row r="46" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H46" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="I46">
+        <v>229656</v>
+      </c>
+    </row>
+    <row r="47" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H47" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="I47">
+        <v>95236</v>
+      </c>
+    </row>
+    <row r="48" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H48" s="15" t="s">
+        <v>622</v>
+      </c>
+      <c r="I48">
+        <v>93602</v>
+      </c>
+    </row>
+    <row r="49" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H49" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="I49">
+        <v>44276</v>
+      </c>
+    </row>
+    <row r="50" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H50" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="I50">
+        <v>9273</v>
+      </c>
+    </row>
+    <row r="51" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H51" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="I51">
+        <v>3757</v>
+      </c>
+    </row>
+    <row r="52" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H52" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="I52">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="53" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H53" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I53">
+        <v>222346</v>
+      </c>
+    </row>
+    <row r="54" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H54" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="I54">
+        <v>8634</v>
+      </c>
+    </row>
+    <row r="55" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H55" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="I55">
+        <v>20052</v>
+      </c>
+    </row>
+    <row r="56" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H56" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="I56">
+        <v>29277</v>
+      </c>
+    </row>
+    <row r="57" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H57" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="I57">
+        <v>44536</v>
+      </c>
+    </row>
+    <row r="58" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H58" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="I58">
+        <v>59604</v>
+      </c>
+    </row>
+    <row r="59" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H59" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="I59">
+        <v>26721</v>
+      </c>
+    </row>
+    <row r="60" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H60" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="I60">
+        <v>6954</v>
+      </c>
+    </row>
+    <row r="61" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H61" s="15" t="s">
+        <v>617</v>
+      </c>
+      <c r="I61">
+        <v>113227</v>
+      </c>
+    </row>
+    <row r="62" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H62" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="I62">
+        <v>19340</v>
+      </c>
+    </row>
+    <row r="63" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H63" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="I63">
+        <v>40373</v>
+      </c>
+    </row>
+    <row r="64" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H64" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="I64">
+        <v>13286</v>
+      </c>
+    </row>
+    <row r="65" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H65" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="I65">
+        <v>34785</v>
+      </c>
+    </row>
+    <row r="66" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H66" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="I66">
+        <v>43959</v>
+      </c>
+    </row>
+    <row r="67" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H67" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="I67">
+        <v>27823</v>
+      </c>
+    </row>
+    <row r="68" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H68" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="I68">
+        <v>22766</v>
+      </c>
+    </row>
+    <row r="69" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H69" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="I69">
+        <v>12683</v>
+      </c>
+    </row>
+    <row r="70" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H70" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="I70">
+        <v>11424</v>
+      </c>
+    </row>
+    <row r="71" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H71" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="I71">
+        <v>49537</v>
+      </c>
+    </row>
+    <row r="72" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H72" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="I72">
+        <v>45699</v>
+      </c>
+    </row>
+    <row r="73" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H73" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="I73">
+        <v>9765</v>
+      </c>
+    </row>
+    <row r="74" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H74" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="I74">
+        <v>36059</v>
+      </c>
+    </row>
+    <row r="75" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H75" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="I75">
+        <v>17181</v>
+      </c>
+    </row>
+    <row r="76" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H76" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="I76">
+        <v>382595</v>
+      </c>
+    </row>
+    <row r="77" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H77" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="I77">
+        <v>21130</v>
+      </c>
+    </row>
+    <row r="78" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H78" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="I78">
+        <v>101756</v>
+      </c>
+    </row>
+    <row r="79" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H79" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="I79">
+        <v>7911</v>
+      </c>
+    </row>
+    <row r="80" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H80" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="I80">
+        <v>8147</v>
+      </c>
+    </row>
+    <row r="81" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H81" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="I81">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="82" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H82" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I82">
+        <v>448449</v>
+      </c>
+    </row>
+    <row r="83" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H83" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I83">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="84" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H84" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="I84">
+        <v>5193</v>
+      </c>
+    </row>
+    <row r="85" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H85" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="I85">
+        <v>7332</v>
+      </c>
+    </row>
+    <row r="86" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H86" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="I86">
+        <v>12120</v>
+      </c>
+    </row>
+    <row r="87" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H87" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="I87">
+        <v>28167</v>
+      </c>
+    </row>
+    <row r="88" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H88" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="I88">
+        <v>251895</v>
+      </c>
+    </row>
+    <row r="89" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H89" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="I89">
+        <v>199941</v>
+      </c>
+    </row>
+    <row r="90" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H90" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="I90">
+        <v>79658</v>
+      </c>
+    </row>
+    <row r="91" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H91" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I91">
+        <v>96087</v>
+      </c>
+    </row>
+    <row r="92" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H92" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I92">
+        <v>662883</v>
+      </c>
+    </row>
+    <row r="93" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H93" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="I93">
+        <v>13899</v>
+      </c>
+    </row>
+    <row r="94" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H94" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="I94">
+        <v>67597</v>
+      </c>
+    </row>
+    <row r="95" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H95" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I95">
+        <v>111366</v>
+      </c>
+    </row>
+    <row r="96" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H96" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="I96">
+        <v>25241</v>
+      </c>
+    </row>
+    <row r="97" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H97" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I97">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="98" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H98" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="I98">
+        <v>231599</v>
+      </c>
+    </row>
+    <row r="99" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H99" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="I99">
+        <v>42576</v>
+      </c>
+    </row>
+    <row r="100" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H100" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I100">
+        <v>160490</v>
+      </c>
+    </row>
+    <row r="101" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H101" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="I101">
+        <v>134982</v>
+      </c>
+    </row>
+    <row r="102" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H102" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="I102">
+        <v>101603</v>
+      </c>
+    </row>
+    <row r="103" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H103" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I103">
+        <v>5714</v>
+      </c>
+    </row>
+    <row r="104" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H104" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="I104">
+        <v>22759</v>
+      </c>
+    </row>
+    <row r="105" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H105" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="I105">
+        <v>3643</v>
+      </c>
+    </row>
+    <row r="106" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H106" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="I106">
+        <v>38081</v>
+      </c>
+    </row>
+    <row r="107" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H107" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="I107">
+        <v>6182</v>
+      </c>
+    </row>
+    <row r="108" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H108" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="I108">
+        <v>10505</v>
+      </c>
+    </row>
+    <row r="109" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H109" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="I109">
+        <v>98484</v>
+      </c>
+    </row>
+    <row r="110" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H110" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="I110">
+        <v>34932</v>
+      </c>
+    </row>
+    <row r="111" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H111" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="I111">
+        <v>74374</v>
+      </c>
+    </row>
+    <row r="112" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H112" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="I112">
+        <v>4261</v>
+      </c>
+    </row>
+    <row r="113" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H113" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="I113">
+        <v>54338</v>
+      </c>
+    </row>
+    <row r="114" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H114" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="I114">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="115" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H115" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="I115">
+        <v>33661</v>
+      </c>
+    </row>
+    <row r="116" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H116" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="I116">
+        <v>30802</v>
+      </c>
+    </row>
+    <row r="117" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H117" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I117">
+        <v>5927</v>
+      </c>
+    </row>
+    <row r="118" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H118" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="I118">
+        <v>32575</v>
+      </c>
+    </row>
+    <row r="119" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H119" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="I119">
+        <v>13643</v>
+      </c>
+    </row>
+    <row r="120" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H120" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="I120">
+        <v>32792</v>
+      </c>
+    </row>
+    <row r="121" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H121" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="I121">
+        <v>19553</v>
+      </c>
+    </row>
+    <row r="122" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H122" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="I122">
+        <v>15577</v>
+      </c>
+    </row>
+    <row r="123" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H123" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I123">
+        <v>231826</v>
+      </c>
+    </row>
+    <row r="124" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H124" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="I124">
+        <v>51298</v>
+      </c>
+    </row>
+    <row r="125" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H125" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="I125">
+        <v>3305</v>
+      </c>
+    </row>
+    <row r="126" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H126" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="I126">
+        <v>13881</v>
+      </c>
+    </row>
+    <row r="127" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H127" s="15" t="s">
+        <v>693</v>
+      </c>
+      <c r="I127">
+        <v>43946</v>
+      </c>
+    </row>
+    <row r="128" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H128" s="15" t="s">
+        <v>639</v>
+      </c>
+      <c r="I128">
+        <v>11784</v>
+      </c>
+    </row>
+    <row r="129" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H129" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="I129">
+        <v>104255</v>
+      </c>
+    </row>
+    <row r="130" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H130" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="I130">
+        <v>47617</v>
+      </c>
+    </row>
+    <row r="131" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H131" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="I131">
+        <v>5134</v>
+      </c>
+    </row>
+    <row r="132" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H132" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="I132">
+        <v>13408</v>
+      </c>
+    </row>
+    <row r="133" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H133" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="I133">
+        <v>3359</v>
+      </c>
+    </row>
+    <row r="134" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H134" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="I134">
+        <v>12077</v>
+      </c>
+    </row>
+    <row r="135" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H135" s="15" t="s">
+        <v>679</v>
+      </c>
+      <c r="I135">
+        <v>48062</v>
+      </c>
+    </row>
+    <row r="136" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H136" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I136">
+        <v>30491</v>
+      </c>
+    </row>
+    <row r="137" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H137" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="I137">
+        <v>8126</v>
+      </c>
+    </row>
+    <row r="138" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H138" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="I138">
+        <v>18082</v>
+      </c>
+    </row>
+    <row r="139" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H139" s="15" t="s">
+        <v>575</v>
+      </c>
+      <c r="I139">
+        <v>439090</v>
+      </c>
+    </row>
+    <row r="140" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H140" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="I140">
+        <v>21569</v>
+      </c>
+    </row>
+    <row r="141" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H141" s="15" t="s">
+        <v>631</v>
+      </c>
+      <c r="I141">
+        <v>34338</v>
+      </c>
+    </row>
+    <row r="142" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H142" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="I142">
+        <v>138650</v>
+      </c>
+    </row>
+    <row r="143" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H143" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="I143">
+        <v>54330</v>
+      </c>
+    </row>
+    <row r="144" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H144" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="I144">
+        <v>10215</v>
+      </c>
+    </row>
+    <row r="145" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H145" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="I145">
+        <v>559430</v>
+      </c>
+    </row>
+    <row r="146" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H146" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="I146">
+        <v>17147</v>
+      </c>
+    </row>
+    <row r="147" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H147" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I147">
+        <v>40264</v>
+      </c>
+    </row>
+    <row r="148" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H148" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="I148">
+        <v>42366</v>
+      </c>
+    </row>
+    <row r="149" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H149" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="I149">
+        <v>379401</v>
+      </c>
+    </row>
+    <row r="150" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H150" s="15" t="s">
+        <v>691</v>
+      </c>
+      <c r="I150">
+        <v>4856</v>
+      </c>
+    </row>
+    <row r="151" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H151" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="I151">
+        <v>15673</v>
+      </c>
+    </row>
+    <row r="152" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H152" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="I152">
+        <v>5925</v>
+      </c>
+    </row>
+    <row r="153" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H153" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="I153">
+        <v>28389</v>
+      </c>
+    </row>
+    <row r="154" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H154" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="I154">
+        <v>16361</v>
+      </c>
+    </row>
+    <row r="155" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H155" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="I155">
+        <v>43330</v>
+      </c>
+    </row>
+    <row r="156" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H156" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="I156">
+        <v>71674</v>
+      </c>
+    </row>
+    <row r="157" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H157" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="I157">
+        <v>420337</v>
+      </c>
+    </row>
+    <row r="158" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H158" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I158">
+        <v>335106</v>
+      </c>
+    </row>
+    <row r="159" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H159" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="I159">
+        <v>101847</v>
+      </c>
+    </row>
+    <row r="160" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H160" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I160">
+        <v>20021</v>
+      </c>
+    </row>
+    <row r="161" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H161" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="I161">
+        <v>24805</v>
+      </c>
+    </row>
+    <row r="162" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H162" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I162">
+        <v>28747</v>
+      </c>
+    </row>
+    <row r="163" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H163" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="I163">
+        <v>25439</v>
+      </c>
+    </row>
+    <row r="164" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H164" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="I164">
+        <v>18632</v>
+      </c>
+    </row>
+    <row r="165" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H165" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I165">
+        <v>360610</v>
+      </c>
+    </row>
+    <row r="166" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H166" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I166">
+        <v>8189</v>
+      </c>
+    </row>
+    <row r="167" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H167" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I167">
+        <v>7013</v>
+      </c>
+    </row>
+    <row r="168" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H168" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="I168">
+        <v>56188</v>
+      </c>
+    </row>
+    <row r="169" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H169" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="I169">
+        <v>27336</v>
+      </c>
+    </row>
+    <row r="170" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H170" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="I170">
+        <v>15883</v>
+      </c>
+    </row>
+    <row r="171" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H171" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="I171">
+        <v>19731</v>
+      </c>
+    </row>
+    <row r="172" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H172" s="15" t="s">
+        <v>530</v>
+      </c>
+      <c r="I172">
+        <v>25441</v>
+      </c>
+    </row>
+    <row r="173" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H173" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="I173">
+        <v>13288</v>
+      </c>
+    </row>
+    <row r="174" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H174" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="I174">
+        <v>188896</v>
+      </c>
+    </row>
+    <row r="175" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H175" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="I175">
+        <v>33801</v>
+      </c>
+    </row>
+    <row r="176" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H176" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="I176">
+        <v>19860</v>
+      </c>
+    </row>
+    <row r="177" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H177" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="I177">
+        <v>126928</v>
+      </c>
+    </row>
+    <row r="178" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H178" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I178">
+        <v>298017</v>
+      </c>
+    </row>
+    <row r="179" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H179" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="I179">
+        <v>48329</v>
+      </c>
+    </row>
+    <row r="180" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H180" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I180">
+        <v>4418497</v>
+      </c>
+    </row>
+    <row r="181" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H181" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I181">
+        <v>487770</v>
+      </c>
+    </row>
+    <row r="182" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H182" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="I182">
+        <v>149289</v>
+      </c>
+    </row>
+    <row r="183" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H183" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I183">
+        <v>174650</v>
+      </c>
+    </row>
+    <row r="184" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H184" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="I184">
+        <v>39119</v>
+      </c>
+    </row>
+    <row r="185" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H185" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="I185">
+        <v>52119</v>
+      </c>
+    </row>
+    <row r="186" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H186" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I186">
+        <v>14107</v>
+      </c>
+    </row>
+    <row r="187" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H187" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="I187">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="188" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H188" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="I188">
+        <v>13165</v>
+      </c>
+    </row>
+    <row r="189" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H189" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I189">
+        <v>43958</v>
+      </c>
+    </row>
+    <row r="190" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H190" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="I190">
+        <v>17189</v>
+      </c>
+    </row>
+    <row r="191" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H191" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="I191">
+        <v>28388</v>
+      </c>
+    </row>
+    <row r="192" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H192" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="I192">
+        <v>34259</v>
+      </c>
+    </row>
+    <row r="193" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H193" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="I193">
+        <v>12299</v>
+      </c>
+    </row>
+    <row r="194" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H194" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="I194">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="195" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H195" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="I195">
+        <v>266948</v>
+      </c>
+    </row>
+    <row r="196" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H196" s="15" t="s">
+        <v>711</v>
+      </c>
+      <c r="I196">
+        <v>383200</v>
+      </c>
+    </row>
+    <row r="197" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H197" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="I197">
+        <v>415151</v>
+      </c>
+    </row>
+    <row r="198" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H198" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="I198">
+        <v>17325</v>
+      </c>
+    </row>
+    <row r="199" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H199" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="I199">
+        <v>42695</v>
+      </c>
+    </row>
+    <row r="200" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H200" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="I200">
+        <v>14054</v>
+      </c>
+    </row>
+    <row r="201" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H201" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="I201">
+        <v>7058</v>
+      </c>
+    </row>
+    <row r="202" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H202" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="I202">
+        <v>354700</v>
+      </c>
+    </row>
+    <row r="203" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H203" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I203">
+        <v>69267</v>
+      </c>
+    </row>
+    <row r="204" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H204" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="I204">
+        <v>14445</v>
+      </c>
+    </row>
+    <row r="205" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H205" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="I205">
+        <v>50320</v>
+      </c>
+    </row>
+    <row r="206" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H206" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="I206">
+        <v>39638</v>
+      </c>
+    </row>
+    <row r="207" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H207" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="I207">
+        <v>94249</v>
+      </c>
+    </row>
+    <row r="208" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H208" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="I208">
+        <v>17935</v>
+      </c>
+    </row>
+    <row r="209" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H209" s="15" t="s">
+        <v>666</v>
+      </c>
+      <c r="I209">
+        <v>25548</v>
+      </c>
+    </row>
+    <row r="210" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H210" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="I210">
+        <v>43428</v>
+      </c>
+    </row>
+    <row r="211" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H211" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="I211">
+        <v>119151</v>
+      </c>
+    </row>
+    <row r="212" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H212" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I212">
+        <v>230115</v>
+      </c>
+    </row>
+    <row r="213" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H213" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="I213">
+        <v>50230</v>
+      </c>
+    </row>
+    <row r="214" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H214" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="I214">
+        <v>35045</v>
+      </c>
+    </row>
+    <row r="215" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H215" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="I215">
+        <v>214342</v>
+      </c>
+    </row>
+    <row r="216" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H216" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I216">
+        <v>408091</v>
+      </c>
+    </row>
+    <row r="217" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H217" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="I217">
+        <v>621764</v>
+      </c>
+    </row>
+    <row r="218" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H218" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="I218">
+        <v>8562</v>
+      </c>
+    </row>
+    <row r="219" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H219" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="I219">
+        <v>152627</v>
+      </c>
+    </row>
+    <row r="220" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H220" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="I220">
+        <v>541824</v>
+      </c>
+    </row>
+    <row r="221" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H221" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="I221">
+        <v>150717</v>
+      </c>
+    </row>
+    <row r="222" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H222" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="I222">
+        <v>54114</v>
+      </c>
+    </row>
+    <row r="223" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H223" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="I223">
+        <v>56057</v>
+      </c>
+    </row>
+    <row r="224" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H224" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="I224">
+        <v>52255</v>
+      </c>
+    </row>
+    <row r="225" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H225" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="I225">
+        <v>44672</v>
+      </c>
+    </row>
+    <row r="226" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H226" s="15" t="s">
+        <v>672</v>
+      </c>
+      <c r="I226">
+        <v>11959</v>
+      </c>
+    </row>
+    <row r="227" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H227" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="I227">
+        <v>18472</v>
+      </c>
+    </row>
+    <row r="228" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H228" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="I228">
+        <v>9648</v>
+      </c>
+    </row>
+    <row r="229" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H229" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I229">
+        <v>323115</v>
+      </c>
+    </row>
+    <row r="230" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H230" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I230">
+        <v>366256</v>
+      </c>
+    </row>
+    <row r="231" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H231" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="I231">
+        <v>29452</v>
+      </c>
+    </row>
+    <row r="232" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H232" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I232">
+        <v>28413</v>
+      </c>
+    </row>
+    <row r="233" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H233" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="I233">
+        <v>203136</v>
+      </c>
+    </row>
+    <row r="234" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H234" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="I234">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="235" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H235" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="I235">
+        <v>13704</v>
+      </c>
+    </row>
+    <row r="236" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H236" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="I236">
+        <v>56938</v>
+      </c>
+    </row>
+    <row r="237" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H237" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="I237">
+        <v>10099</v>
+      </c>
+    </row>
+    <row r="238" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H238" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="I238">
+        <v>144718</v>
+      </c>
+    </row>
+    <row r="239" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H239" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="I239">
+        <v>270906</v>
+      </c>
+    </row>
+    <row r="240" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H240" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="I240">
+        <v>11709</v>
+      </c>
+    </row>
+    <row r="241" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H241" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="I241">
+        <v>22946</v>
+      </c>
+    </row>
+    <row r="242" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H242" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="I242">
+        <v>614223</v>
+      </c>
+    </row>
+    <row r="243" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H243" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="I243">
+        <v>59511</v>
+      </c>
+    </row>
+    <row r="244" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H244" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="I244">
+        <v>11968</v>
+      </c>
+    </row>
+    <row r="245" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H245" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="I245">
+        <v>355614</v>
+      </c>
+    </row>
+    <row r="246" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H246" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="I246">
+        <v>20374</v>
+      </c>
+    </row>
+    <row r="247" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H247" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="I247">
+        <v>33807</v>
+      </c>
+    </row>
+    <row r="248" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H248" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="I248">
+        <v>86888</v>
+      </c>
+    </row>
+    <row r="249" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H249" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="I249">
+        <v>10210</v>
+      </c>
+    </row>
+    <row r="250" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H250" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="I250">
+        <v>27518</v>
+      </c>
+    </row>
+    <row r="251" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H251" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="I251">
+        <v>20748</v>
+      </c>
+    </row>
+    <row r="252" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H252" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="I252">
+        <v>13521</v>
+      </c>
+    </row>
+    <row r="253" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H253" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="I253">
+        <v>17744</v>
+      </c>
+    </row>
+    <row r="254" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H254" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="I254">
+        <v>23340</v>
+      </c>
+    </row>
+    <row r="255" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H255" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="I255">
+        <v>212372</v>
+      </c>
+    </row>
+    <row r="256" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H256" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="I256">
+        <v>559220</v>
+      </c>
+    </row>
+    <row r="257" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H257" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="I257">
+        <v>225198</v>
+      </c>
+    </row>
+    <row r="258" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H258" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="I258">
+        <v>26761</v>
+      </c>
+    </row>
+    <row r="259" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H259" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="I259">
+        <v>17403</v>
+      </c>
+    </row>
+    <row r="260" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H260" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="I260">
+        <v>237155</v>
+      </c>
+    </row>
+    <row r="261" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H261" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="I261">
+        <v>35838</v>
+      </c>
+    </row>
+    <row r="262" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H262" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="I262">
+        <v>55756</v>
+      </c>
+    </row>
+    <row r="263" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H263" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="I263">
+        <v>21783</v>
+      </c>
+    </row>
+    <row r="264" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H264" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I264">
+        <v>40630</v>
+      </c>
+    </row>
+    <row r="265" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H265" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="I265">
+        <v>73967</v>
+      </c>
+    </row>
+    <row r="266" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H266" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="I266">
+        <v>5499</v>
+      </c>
+    </row>
+    <row r="267" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H267" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="I267">
+        <v>6680</v>
+      </c>
+    </row>
+    <row r="268" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H268" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="I268">
+        <v>6040</v>
+      </c>
+    </row>
+    <row r="269" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H269" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="I269">
+        <v>37575</v>
+      </c>
+    </row>
+    <row r="270" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H270" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="I270">
+        <v>30213</v>
+      </c>
+    </row>
+    <row r="271" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H271" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="I271">
+        <v>343514</v>
+      </c>
+    </row>
+    <row r="272" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H272" s="15" t="s">
+        <v>599</v>
+      </c>
+      <c r="I272">
+        <v>442114</v>
+      </c>
+    </row>
+    <row r="273" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H273" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="I273">
+        <v>70671</v>
+      </c>
+    </row>
+    <row r="274" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H274" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="I274">
+        <v>38035</v>
+      </c>
+    </row>
+    <row r="275" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H275" s="15" t="s">
+        <v>579</v>
+      </c>
+      <c r="I275">
+        <v>10481</v>
+      </c>
+    </row>
+    <row r="276" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H276" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="I276">
+        <v>1675988</v>
+      </c>
+    </row>
+    <row r="277" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H277" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="I277">
+        <v>41019</v>
+      </c>
+    </row>
+    <row r="278" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H278" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="I278">
+        <v>9339</v>
+      </c>
+    </row>
+    <row r="279" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H279" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="I279">
+        <v>142744</v>
+      </c>
+    </row>
+    <row r="280" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H280" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="I280">
+        <v>16566</v>
+      </c>
+    </row>
+    <row r="281" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H281" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="I281">
+        <v>66897</v>
+      </c>
+    </row>
+    <row r="282" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H282" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="I282">
+        <v>18716</v>
+      </c>
+    </row>
+    <row r="283" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H283" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="I283">
+        <v>79181</v>
+      </c>
+    </row>
+    <row r="284" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H284" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="I284">
+        <v>14406</v>
+      </c>
+    </row>
+    <row r="285" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H285" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="I285">
+        <v>3737</v>
+      </c>
+    </row>
+    <row r="286" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H286" s="15" t="s">
+        <v>708</v>
+      </c>
+      <c r="I286">
+        <v>246805</v>
+      </c>
+    </row>
+    <row r="287" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H287" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="I287">
+        <v>6667</v>
+      </c>
+    </row>
+    <row r="288" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H288" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="I288">
+        <v>1015979</v>
+      </c>
+    </row>
+    <row r="289" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H289" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="I289">
+        <v>1224740</v>
+      </c>
+    </row>
+    <row r="290" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H290" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="I290">
+        <v>14945</v>
+      </c>
+    </row>
+    <row r="291" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H291" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="I291">
+        <v>118282</v>
+      </c>
+    </row>
+    <row r="292" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H292" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="I292">
+        <v>21200</v>
+      </c>
+    </row>
+    <row r="293" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H293" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="I293">
+        <v>27049</v>
+      </c>
+    </row>
+    <row r="294" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H294" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="I294">
+        <v>38516</v>
+      </c>
+    </row>
+    <row r="295" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H295" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="I295">
+        <v>20046</v>
+      </c>
+    </row>
+    <row r="296" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H296" s="15" t="s">
         <v>741</v>
       </c>
-      <c r="B14" t="s">
-        <v>747</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>594</v>
-      </c>
-      <c r="I14" s="14">
-        <v>272053</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="I15" s="14">
-        <v>23872</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="14">
-        <v>3</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>635</v>
-      </c>
-      <c r="I16" s="14">
-        <v>7330</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="14">
-        <v>9</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="I17" s="14">
-        <v>24721</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="14">
-        <v>6</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>446</v>
-      </c>
-      <c r="I18" s="14">
-        <v>41018</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B19" s="14">
-        <v>2</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>612</v>
-      </c>
-      <c r="I19" s="14">
-        <v>21482</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="B20" s="14">
-        <v>7</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>487</v>
-      </c>
-      <c r="I20" s="14">
-        <v>24433</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="B21" s="14">
-        <v>38</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="I21" s="14">
-        <v>31172</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
-        <v>628</v>
-      </c>
-      <c r="B22" s="14">
-        <v>5</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="I22" s="14">
-        <v>10003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="14">
-        <v>11</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="I23" s="14">
-        <v>43449</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="B24" s="14">
-        <v>9</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="I24" s="14">
-        <v>355619</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
-        <v>742</v>
-      </c>
-      <c r="B25" s="14">
-        <v>91</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>677</v>
-      </c>
-      <c r="I25" s="14">
-        <v>45641</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H26" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="I26" s="14">
-        <v>64932</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="16" t="s">
-        <v>540</v>
-      </c>
-      <c r="I27" s="14">
-        <v>12708</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="I28" s="14">
-        <v>21410</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="I29" s="14">
-        <v>16834</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="I30" s="14">
-        <v>172937</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="16" t="s">
-        <v>457</v>
-      </c>
-      <c r="I31" s="14">
-        <v>39346</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H32" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="I32" s="14">
-        <v>167438</v>
-      </c>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="I33" s="14">
-        <v>30011</v>
-      </c>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="16" t="s">
-        <v>462</v>
-      </c>
-      <c r="I34" s="14">
-        <v>31757</v>
-      </c>
-    </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H35" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="I35" s="14">
-        <v>15697</v>
-      </c>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="16" t="s">
-        <v>702</v>
-      </c>
-      <c r="I36" s="14">
-        <v>19641</v>
-      </c>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="16" t="s">
-        <v>689</v>
-      </c>
-      <c r="I37" s="14">
-        <v>178933</v>
-      </c>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="I38" s="14">
-        <v>24547</v>
-      </c>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="I39" s="14">
-        <v>23284</v>
-      </c>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="I40" s="14">
-        <v>21474</v>
-      </c>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="16" t="s">
-        <v>674</v>
-      </c>
-      <c r="I41" s="14">
-        <v>51972</v>
-      </c>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="I42" s="14">
-        <v>23784</v>
-      </c>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="16" t="s">
-        <v>437</v>
-      </c>
-      <c r="I43" s="14">
-        <v>35653</v>
-      </c>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="16" t="s">
-        <v>470</v>
-      </c>
-      <c r="I44" s="14">
-        <v>294858</v>
-      </c>
-    </row>
-    <row r="45" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H45" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="I45" s="14">
-        <v>31779</v>
-      </c>
-    </row>
-    <row r="46" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H46" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="I46" s="14">
-        <v>229656</v>
-      </c>
-    </row>
-    <row r="47" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H47" s="16" t="s">
-        <v>483</v>
-      </c>
-      <c r="I47" s="14">
-        <v>95236</v>
-      </c>
-    </row>
-    <row r="48" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H48" s="16" t="s">
-        <v>622</v>
-      </c>
-      <c r="I48" s="14">
-        <v>93602</v>
-      </c>
-    </row>
-    <row r="49" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H49" s="16" t="s">
-        <v>412</v>
-      </c>
-      <c r="I49" s="14">
-        <v>44276</v>
-      </c>
-    </row>
-    <row r="50" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H50" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="I50" s="14">
-        <v>9273</v>
-      </c>
-    </row>
-    <row r="51" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H51" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="I51" s="14">
-        <v>3757</v>
-      </c>
-    </row>
-    <row r="52" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H52" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="I52" s="14">
-        <v>3914</v>
-      </c>
-    </row>
-    <row r="53" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H53" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I53" s="14">
-        <v>222346</v>
-      </c>
-    </row>
-    <row r="54" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H54" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="I54" s="14">
-        <v>8634</v>
-      </c>
-    </row>
-    <row r="55" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H55" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="I55" s="14">
-        <v>20052</v>
-      </c>
-    </row>
-    <row r="56" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H56" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="I56" s="14">
-        <v>29277</v>
-      </c>
-    </row>
-    <row r="57" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H57" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="I57" s="14">
-        <v>44536</v>
-      </c>
-    </row>
-    <row r="58" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H58" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="I58" s="14">
-        <v>59604</v>
-      </c>
-    </row>
-    <row r="59" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H59" s="16" t="s">
-        <v>555</v>
-      </c>
-      <c r="I59" s="14">
-        <v>26721</v>
-      </c>
-    </row>
-    <row r="60" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H60" s="16" t="s">
-        <v>652</v>
-      </c>
-      <c r="I60" s="14">
-        <v>6954</v>
-      </c>
-    </row>
-    <row r="61" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H61" s="16" t="s">
-        <v>617</v>
-      </c>
-      <c r="I61" s="14">
-        <v>113227</v>
-      </c>
-    </row>
-    <row r="62" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H62" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="I62" s="14">
-        <v>19340</v>
-      </c>
-    </row>
-    <row r="63" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H63" s="16" t="s">
-        <v>364</v>
-      </c>
-      <c r="I63" s="14">
-        <v>40373</v>
-      </c>
-    </row>
-    <row r="64" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H64" s="16" t="s">
-        <v>516</v>
-      </c>
-      <c r="I64" s="14">
-        <v>13286</v>
-      </c>
-    </row>
-    <row r="65" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H65" s="16" t="s">
-        <v>615</v>
-      </c>
-      <c r="I65" s="14">
-        <v>34785</v>
-      </c>
-    </row>
-    <row r="66" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H66" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="I66" s="14">
-        <v>43959</v>
-      </c>
-    </row>
-    <row r="67" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H67" s="16" t="s">
-        <v>648</v>
-      </c>
-      <c r="I67" s="14">
-        <v>27823</v>
-      </c>
-    </row>
-    <row r="68" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H68" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="I68" s="14">
-        <v>22766</v>
-      </c>
-    </row>
-    <row r="69" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H69" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="I69" s="14">
-        <v>12683</v>
-      </c>
-    </row>
-    <row r="70" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H70" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="I70" s="14">
-        <v>11424</v>
-      </c>
-    </row>
-    <row r="71" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H71" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="I71" s="14">
-        <v>49537</v>
-      </c>
-    </row>
-    <row r="72" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H72" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="I72" s="14">
-        <v>45699</v>
-      </c>
-    </row>
-    <row r="73" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H73" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="I73" s="14">
-        <v>9765</v>
-      </c>
-    </row>
-    <row r="74" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H74" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I74" s="14">
-        <v>36059</v>
-      </c>
-    </row>
-    <row r="75" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H75" s="16" t="s">
-        <v>592</v>
-      </c>
-      <c r="I75" s="14">
-        <v>17181</v>
-      </c>
-    </row>
-    <row r="76" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H76" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="I76" s="14">
-        <v>382595</v>
-      </c>
-    </row>
-    <row r="77" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H77" s="16" t="s">
-        <v>610</v>
-      </c>
-      <c r="I77" s="14">
-        <v>21130</v>
-      </c>
-    </row>
-    <row r="78" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H78" s="16" t="s">
-        <v>362</v>
-      </c>
-      <c r="I78" s="14">
-        <v>101756</v>
-      </c>
-    </row>
-    <row r="79" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H79" s="16" t="s">
-        <v>398</v>
-      </c>
-      <c r="I79" s="14">
-        <v>7911</v>
-      </c>
-    </row>
-    <row r="80" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H80" s="16" t="s">
-        <v>566</v>
-      </c>
-      <c r="I80" s="14">
-        <v>8147</v>
-      </c>
-    </row>
-    <row r="81" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H81" s="16" t="s">
-        <v>536</v>
-      </c>
-      <c r="I81" s="14">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="82" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H82" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="I82" s="14">
-        <v>448449</v>
-      </c>
-    </row>
-    <row r="83" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H83" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="I83" s="14">
-        <v>40001</v>
-      </c>
-    </row>
-    <row r="84" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H84" s="16" t="s">
-        <v>656</v>
-      </c>
-      <c r="I84" s="14">
-        <v>5193</v>
-      </c>
-    </row>
-    <row r="85" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H85" s="16" t="s">
-        <v>644</v>
-      </c>
-      <c r="I85" s="14">
-        <v>7332</v>
-      </c>
-    </row>
-    <row r="86" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H86" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="I86" s="14">
-        <v>12120</v>
-      </c>
-    </row>
-    <row r="87" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H87" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="I87" s="14">
-        <v>28167</v>
-      </c>
-    </row>
-    <row r="88" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H88" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="I88" s="14">
-        <v>251895</v>
-      </c>
-    </row>
-    <row r="89" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H89" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="I89" s="14">
-        <v>199941</v>
-      </c>
-    </row>
-    <row r="90" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H90" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="I90" s="14">
-        <v>79658</v>
-      </c>
-    </row>
-    <row r="91" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H91" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="I91" s="14">
-        <v>96087</v>
-      </c>
-    </row>
-    <row r="92" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H92" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="I92" s="14">
-        <v>662883</v>
-      </c>
-    </row>
-    <row r="93" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H93" s="16" t="s">
-        <v>561</v>
-      </c>
-      <c r="I93" s="14">
-        <v>13899</v>
-      </c>
-    </row>
-    <row r="94" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H94" s="16" t="s">
-        <v>532</v>
-      </c>
-      <c r="I94" s="14">
-        <v>67597</v>
-      </c>
-    </row>
-    <row r="95" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H95" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="I95" s="14">
-        <v>111366</v>
-      </c>
-    </row>
-    <row r="96" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H96" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="I96" s="14">
-        <v>25241</v>
-      </c>
-    </row>
-    <row r="97" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H97" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="I97" s="14">
-        <v>6538</v>
-      </c>
-    </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H98" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="I98" s="14">
-        <v>231599</v>
-      </c>
-    </row>
-    <row r="99" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H99" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="I99" s="14">
-        <v>42576</v>
-      </c>
-    </row>
-    <row r="100" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H100" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I100" s="14">
-        <v>160490</v>
-      </c>
-    </row>
-    <row r="101" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H101" s="16" t="s">
-        <v>633</v>
-      </c>
-      <c r="I101" s="14">
-        <v>134982</v>
-      </c>
-    </row>
-    <row r="102" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H102" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="I102" s="14">
-        <v>101603</v>
-      </c>
-    </row>
-    <row r="103" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H103" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I103" s="14">
-        <v>5714</v>
-      </c>
-    </row>
-    <row r="104" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H104" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="I104" s="14">
-        <v>22759</v>
-      </c>
-    </row>
-    <row r="105" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H105" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="I105" s="14">
-        <v>3643</v>
-      </c>
-    </row>
-    <row r="106" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H106" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="I106" s="14">
-        <v>38081</v>
-      </c>
-    </row>
-    <row r="107" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H107" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="I107" s="14">
-        <v>6182</v>
-      </c>
-    </row>
-    <row r="108" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H108" s="16" t="s">
-        <v>706</v>
-      </c>
-      <c r="I108" s="14">
-        <v>10505</v>
-      </c>
-    </row>
-    <row r="109" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H109" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="I109" s="14">
-        <v>98484</v>
-      </c>
-    </row>
-    <row r="110" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H110" s="16" t="s">
-        <v>347</v>
-      </c>
-      <c r="I110" s="14">
-        <v>34932</v>
-      </c>
-    </row>
-    <row r="111" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H111" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="I111" s="14">
-        <v>74374</v>
-      </c>
-    </row>
-    <row r="112" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H112" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="I112" s="14">
-        <v>4261</v>
-      </c>
-    </row>
-    <row r="113" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H113" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="I113" s="14">
-        <v>54338</v>
-      </c>
-    </row>
-    <row r="114" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H114" s="16" t="s">
-        <v>670</v>
-      </c>
-      <c r="I114" s="14">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="115" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H115" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="I115" s="14">
-        <v>33661</v>
-      </c>
-    </row>
-    <row r="116" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H116" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="I116" s="14">
-        <v>30802</v>
-      </c>
-    </row>
-    <row r="117" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H117" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I117" s="14">
-        <v>5927</v>
-      </c>
-    </row>
-    <row r="118" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H118" s="16" t="s">
-        <v>518</v>
-      </c>
-      <c r="I118" s="14">
-        <v>32575</v>
-      </c>
-    </row>
-    <row r="119" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H119" s="16" t="s">
-        <v>384</v>
-      </c>
-      <c r="I119" s="14">
-        <v>13643</v>
-      </c>
-    </row>
-    <row r="120" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H120" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="I120" s="14">
-        <v>32792</v>
-      </c>
-    </row>
-    <row r="121" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H121" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="I121" s="14">
-        <v>19553</v>
-      </c>
-    </row>
-    <row r="122" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H122" s="16" t="s">
-        <v>534</v>
-      </c>
-      <c r="I122" s="14">
-        <v>15577</v>
-      </c>
-    </row>
-    <row r="123" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H123" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I123" s="14">
-        <v>231826</v>
-      </c>
-    </row>
-    <row r="124" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H124" s="16" t="s">
-        <v>637</v>
-      </c>
-      <c r="I124" s="14">
-        <v>51298</v>
-      </c>
-    </row>
-    <row r="125" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H125" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="I125" s="14">
-        <v>3305</v>
-      </c>
-    </row>
-    <row r="126" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H126" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="I126" s="14">
-        <v>13881</v>
-      </c>
-    </row>
-    <row r="127" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H127" s="16" t="s">
-        <v>693</v>
-      </c>
-      <c r="I127" s="14">
-        <v>43946</v>
-      </c>
-    </row>
-    <row r="128" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H128" s="16" t="s">
-        <v>639</v>
-      </c>
-      <c r="I128" s="14">
-        <v>11784</v>
-      </c>
-    </row>
-    <row r="129" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H129" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="I129" s="14">
-        <v>104255</v>
-      </c>
-    </row>
-    <row r="130" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H130" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="I130" s="14">
-        <v>47617</v>
-      </c>
-    </row>
-    <row r="131" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H131" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="I131" s="14">
-        <v>5134</v>
-      </c>
-    </row>
-    <row r="132" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H132" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="I132" s="14">
-        <v>13408</v>
-      </c>
-    </row>
-    <row r="133" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H133" s="16" t="s">
-        <v>650</v>
-      </c>
-      <c r="I133" s="14">
-        <v>3359</v>
-      </c>
-    </row>
-    <row r="134" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H134" s="16" t="s">
-        <v>450</v>
-      </c>
-      <c r="I134" s="14">
-        <v>12077</v>
-      </c>
-    </row>
-    <row r="135" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H135" s="16" t="s">
-        <v>679</v>
-      </c>
-      <c r="I135" s="14">
-        <v>48062</v>
-      </c>
-    </row>
-    <row r="136" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H136" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="I136" s="14">
-        <v>30491</v>
-      </c>
-    </row>
-    <row r="137" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H137" s="16" t="s">
-        <v>490</v>
-      </c>
-      <c r="I137" s="14">
-        <v>8126</v>
-      </c>
-    </row>
-    <row r="138" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H138" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I138" s="14">
-        <v>18082</v>
-      </c>
-    </row>
-    <row r="139" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H139" s="16" t="s">
-        <v>575</v>
-      </c>
-      <c r="I139" s="14">
-        <v>439090</v>
-      </c>
-    </row>
-    <row r="140" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H140" s="16" t="s">
-        <v>495</v>
-      </c>
-      <c r="I140" s="14">
-        <v>21569</v>
-      </c>
-    </row>
-    <row r="141" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H141" s="16" t="s">
-        <v>631</v>
-      </c>
-      <c r="I141" s="14">
-        <v>34338</v>
-      </c>
-    </row>
-    <row r="142" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H142" s="16" t="s">
-        <v>501</v>
-      </c>
-      <c r="I142" s="14">
-        <v>138650</v>
-      </c>
-    </row>
-    <row r="143" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H143" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="I143" s="14">
-        <v>54330</v>
-      </c>
-    </row>
-    <row r="144" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H144" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="I144" s="14">
-        <v>10215</v>
-      </c>
-    </row>
-    <row r="145" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H145" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="I145" s="14">
-        <v>559430</v>
-      </c>
-    </row>
-    <row r="146" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H146" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="I146" s="14">
-        <v>17147</v>
-      </c>
-    </row>
-    <row r="147" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H147" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I147" s="14">
-        <v>40264</v>
-      </c>
-    </row>
-    <row r="148" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H148" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="I148" s="14">
-        <v>42366</v>
-      </c>
-    </row>
-    <row r="149" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H149" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="I149" s="14">
-        <v>379401</v>
-      </c>
-    </row>
-    <row r="150" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H150" s="16" t="s">
-        <v>691</v>
-      </c>
-      <c r="I150" s="14">
-        <v>4856</v>
-      </c>
-    </row>
-    <row r="151" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H151" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I151" s="14">
-        <v>15673</v>
-      </c>
-    </row>
-    <row r="152" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H152" s="16" t="s">
-        <v>434</v>
-      </c>
-      <c r="I152" s="14">
-        <v>5925</v>
-      </c>
-    </row>
-    <row r="153" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H153" s="16" t="s">
-        <v>408</v>
-      </c>
-      <c r="I153" s="14">
-        <v>28389</v>
-      </c>
-    </row>
-    <row r="154" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H154" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="I154" s="14">
-        <v>16361</v>
-      </c>
-    </row>
-    <row r="155" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H155" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="I155" s="14">
-        <v>43330</v>
-      </c>
-    </row>
-    <row r="156" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H156" s="16" t="s">
-        <v>542</v>
-      </c>
-      <c r="I156" s="14">
-        <v>71674</v>
-      </c>
-    </row>
-    <row r="157" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H157" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="I157" s="14">
-        <v>420337</v>
-      </c>
-    </row>
-    <row r="158" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H158" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="I158" s="14">
-        <v>335106</v>
-      </c>
-    </row>
-    <row r="159" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H159" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="I159" s="14">
-        <v>101847</v>
-      </c>
-    </row>
-    <row r="160" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H160" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I160" s="14">
-        <v>20021</v>
-      </c>
-    </row>
-    <row r="161" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H161" s="16" t="s">
-        <v>642</v>
-      </c>
-      <c r="I161" s="14">
-        <v>24805</v>
-      </c>
-    </row>
-    <row r="162" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H162" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="I162" s="14">
-        <v>28747</v>
-      </c>
-    </row>
-    <row r="163" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H163" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="I163" s="14">
-        <v>25439</v>
-      </c>
-    </row>
-    <row r="164" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H164" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="I164" s="14">
-        <v>18632</v>
-      </c>
-    </row>
-    <row r="165" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H165" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="I165" s="14">
-        <v>360610</v>
-      </c>
-    </row>
-    <row r="166" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H166" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I166" s="14">
-        <v>8189</v>
-      </c>
-    </row>
-    <row r="167" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H167" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="I167" s="14">
-        <v>7013</v>
-      </c>
-    </row>
-    <row r="168" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H168" s="16" t="s">
-        <v>624</v>
-      </c>
-      <c r="I168" s="14">
-        <v>56188</v>
-      </c>
-    </row>
-    <row r="169" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H169" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="I169" s="14">
-        <v>27336</v>
-      </c>
-    </row>
-    <row r="170" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H170" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="I170" s="14">
-        <v>15883</v>
-      </c>
-    </row>
-    <row r="171" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H171" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="I171" s="14">
-        <v>19731</v>
-      </c>
-    </row>
-    <row r="172" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H172" s="16" t="s">
-        <v>530</v>
-      </c>
-      <c r="I172" s="14">
-        <v>25441</v>
-      </c>
-    </row>
-    <row r="173" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H173" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="I173" s="14">
-        <v>13288</v>
-      </c>
-    </row>
-    <row r="174" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H174" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="I174" s="14">
-        <v>188896</v>
-      </c>
-    </row>
-    <row r="175" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H175" s="16" t="s">
-        <v>699</v>
-      </c>
-      <c r="I175" s="14">
-        <v>33801</v>
-      </c>
-    </row>
-    <row r="176" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H176" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="I176" s="14">
-        <v>19860</v>
-      </c>
-    </row>
-    <row r="177" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H177" s="16" t="s">
-        <v>396</v>
-      </c>
-      <c r="I177" s="14">
-        <v>126928</v>
-      </c>
-    </row>
-    <row r="178" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H178" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="I178" s="14">
-        <v>298017</v>
-      </c>
-    </row>
-    <row r="179" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H179" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="I179" s="14">
-        <v>48329</v>
-      </c>
-    </row>
-    <row r="180" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H180" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I180" s="14">
-        <v>4418497</v>
-      </c>
-    </row>
-    <row r="181" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H181" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="I181" s="14">
-        <v>487770</v>
-      </c>
-    </row>
-    <row r="182" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H182" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="I182" s="14">
-        <v>149289</v>
-      </c>
-    </row>
-    <row r="183" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H183" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="I183" s="14">
-        <v>174650</v>
-      </c>
-    </row>
-    <row r="184" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H184" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="I184" s="14">
-        <v>39119</v>
-      </c>
-    </row>
-    <row r="185" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H185" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="I185" s="14">
-        <v>52119</v>
-      </c>
-    </row>
-    <row r="186" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H186" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I186" s="14">
-        <v>14107</v>
-      </c>
-    </row>
-    <row r="187" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H187" s="16" t="s">
-        <v>473</v>
-      </c>
-      <c r="I187" s="14">
-        <v>3770</v>
-      </c>
-    </row>
-    <row r="188" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H188" s="16" t="s">
-        <v>503</v>
-      </c>
-      <c r="I188" s="14">
-        <v>13165</v>
-      </c>
-    </row>
-    <row r="189" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H189" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I189" s="14">
-        <v>43958</v>
-      </c>
-    </row>
-    <row r="190" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H190" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="I190" s="14">
-        <v>17189</v>
-      </c>
-    </row>
-    <row r="191" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H191" s="16" t="s">
-        <v>507</v>
-      </c>
-      <c r="I191" s="14">
-        <v>28388</v>
-      </c>
-    </row>
-    <row r="192" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H192" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="I192" s="14">
-        <v>34259</v>
-      </c>
-    </row>
-    <row r="193" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H193" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="I193" s="14">
-        <v>12299</v>
-      </c>
-    </row>
-    <row r="194" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H194" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="I194" s="14">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="195" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H195" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="I195" s="14">
-        <v>266948</v>
-      </c>
-    </row>
-    <row r="196" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H196" s="16" t="s">
-        <v>711</v>
-      </c>
-      <c r="I196" s="14">
-        <v>383200</v>
-      </c>
-    </row>
-    <row r="197" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H197" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="I197" s="14">
-        <v>415151</v>
-      </c>
-    </row>
-    <row r="198" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H198" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="I198" s="14">
-        <v>17325</v>
-      </c>
-    </row>
-    <row r="199" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H199" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="I199" s="14">
-        <v>42695</v>
-      </c>
-    </row>
-    <row r="200" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H200" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="I200" s="14">
-        <v>14054</v>
-      </c>
-    </row>
-    <row r="201" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H201" s="16" t="s">
-        <v>479</v>
-      </c>
-      <c r="I201" s="14">
-        <v>7058</v>
-      </c>
-    </row>
-    <row r="202" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H202" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="I202" s="14">
-        <v>354700</v>
-      </c>
-    </row>
-    <row r="203" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H203" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="I203" s="14">
-        <v>69267</v>
-      </c>
-    </row>
-    <row r="204" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H204" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="I204" s="14">
-        <v>14445</v>
-      </c>
-    </row>
-    <row r="205" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H205" s="16" t="s">
-        <v>485</v>
-      </c>
-      <c r="I205" s="14">
-        <v>50320</v>
-      </c>
-    </row>
-    <row r="206" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H206" s="16" t="s">
-        <v>596</v>
-      </c>
-      <c r="I206" s="14">
-        <v>39638</v>
-      </c>
-    </row>
-    <row r="207" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H207" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="I207" s="14">
-        <v>94249</v>
-      </c>
-    </row>
-    <row r="208" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H208" s="16" t="s">
-        <v>654</v>
-      </c>
-      <c r="I208" s="14">
-        <v>17935</v>
-      </c>
-    </row>
-    <row r="209" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H209" s="16" t="s">
-        <v>666</v>
-      </c>
-      <c r="I209" s="14">
-        <v>25548</v>
-      </c>
-    </row>
-    <row r="210" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H210" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="I210" s="14">
-        <v>43428</v>
-      </c>
-    </row>
-    <row r="211" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H211" s="16" t="s">
-        <v>608</v>
-      </c>
-      <c r="I211" s="14">
-        <v>119151</v>
-      </c>
-    </row>
-    <row r="212" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H212" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="I212" s="14">
-        <v>230115</v>
-      </c>
-    </row>
-    <row r="213" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H213" s="16" t="s">
-        <v>559</v>
-      </c>
-      <c r="I213" s="14">
-        <v>50230</v>
-      </c>
-    </row>
-    <row r="214" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H214" s="16" t="s">
-        <v>664</v>
-      </c>
-      <c r="I214" s="14">
-        <v>35045</v>
-      </c>
-    </row>
-    <row r="215" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H215" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="I215" s="14">
-        <v>214342</v>
-      </c>
-    </row>
-    <row r="216" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H216" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="I216" s="14">
-        <v>408091</v>
-      </c>
-    </row>
-    <row r="217" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H217" s="16" t="s">
-        <v>497</v>
-      </c>
-      <c r="I217" s="14">
-        <v>621764</v>
-      </c>
-    </row>
-    <row r="218" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H218" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="I218" s="14">
-        <v>8562</v>
-      </c>
-    </row>
-    <row r="219" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H219" s="16" t="s">
-        <v>544</v>
-      </c>
-      <c r="I219" s="14">
-        <v>152627</v>
-      </c>
-    </row>
-    <row r="220" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H220" s="16" t="s">
-        <v>662</v>
-      </c>
-      <c r="I220" s="14">
-        <v>541824</v>
-      </c>
-    </row>
-    <row r="221" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H221" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="I221" s="14">
-        <v>150717</v>
-      </c>
-    </row>
-    <row r="222" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H222" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="I222" s="14">
-        <v>54114</v>
-      </c>
-    </row>
-    <row r="223" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H223" s="16" t="s">
-        <v>658</v>
-      </c>
-      <c r="I223" s="14">
-        <v>56057</v>
-      </c>
-    </row>
-    <row r="224" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H224" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="I224" s="14">
-        <v>52255</v>
-      </c>
-    </row>
-    <row r="225" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H225" s="16" t="s">
-        <v>505</v>
-      </c>
-      <c r="I225" s="14">
-        <v>44672</v>
-      </c>
-    </row>
-    <row r="226" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H226" s="16" t="s">
-        <v>672</v>
-      </c>
-      <c r="I226" s="14">
-        <v>11959</v>
-      </c>
-    </row>
-    <row r="227" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H227" s="16" t="s">
-        <v>359</v>
-      </c>
-      <c r="I227" s="14">
-        <v>18472</v>
-      </c>
-    </row>
-    <row r="228" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H228" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="I228" s="14">
-        <v>9648</v>
-      </c>
-    </row>
-    <row r="229" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H229" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="I229" s="14">
-        <v>323115</v>
-      </c>
-    </row>
-    <row r="230" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H230" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="I230" s="14">
-        <v>366256</v>
-      </c>
-    </row>
-    <row r="231" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H231" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="I231" s="14">
-        <v>29452</v>
-      </c>
-    </row>
-    <row r="232" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H232" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="I232" s="14">
-        <v>28413</v>
-      </c>
-    </row>
-    <row r="233" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H233" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="I233" s="14">
-        <v>203136</v>
-      </c>
-    </row>
-    <row r="234" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H234" s="16" t="s">
-        <v>523</v>
-      </c>
-      <c r="I234" s="14">
-        <v>3138</v>
-      </c>
-    </row>
-    <row r="235" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H235" s="16" t="s">
-        <v>402</v>
-      </c>
-      <c r="I235" s="14">
-        <v>13704</v>
-      </c>
-    </row>
-    <row r="236" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H236" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="I236" s="14">
-        <v>56938</v>
-      </c>
-    </row>
-    <row r="237" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H237" s="16" t="s">
-        <v>582</v>
-      </c>
-      <c r="I237" s="14">
-        <v>10099</v>
-      </c>
-    </row>
-    <row r="238" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H238" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="I238" s="14">
-        <v>144718</v>
-      </c>
-    </row>
-    <row r="239" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H239" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I239" s="14">
-        <v>270906</v>
-      </c>
-    </row>
-    <row r="240" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H240" s="16" t="s">
-        <v>439</v>
-      </c>
-      <c r="I240" s="14">
-        <v>11709</v>
-      </c>
-    </row>
-    <row r="241" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H241" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="I241" s="14">
-        <v>22946</v>
-      </c>
-    </row>
-    <row r="242" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H242" s="16" t="s">
-        <v>475</v>
-      </c>
-      <c r="I242" s="14">
-        <v>614223</v>
-      </c>
-    </row>
-    <row r="243" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H243" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="I243" s="14">
-        <v>59511</v>
-      </c>
-    </row>
-    <row r="244" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H244" s="16" t="s">
-        <v>682</v>
-      </c>
-      <c r="I244" s="14">
-        <v>11968</v>
-      </c>
-    </row>
-    <row r="245" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H245" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="I245" s="14">
-        <v>355614</v>
-      </c>
-    </row>
-    <row r="246" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H246" s="16" t="s">
-        <v>410</v>
-      </c>
-      <c r="I246" s="14">
-        <v>20374</v>
-      </c>
-    </row>
-    <row r="247" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H247" s="16" t="s">
-        <v>668</v>
-      </c>
-      <c r="I247" s="14">
-        <v>33807</v>
-      </c>
-    </row>
-    <row r="248" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H248" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="I248" s="14">
-        <v>86888</v>
-      </c>
-    </row>
-    <row r="249" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H249" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="I249" s="14">
-        <v>10210</v>
-      </c>
-    </row>
-    <row r="250" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H250" s="16" t="s">
-        <v>563</v>
-      </c>
-      <c r="I250" s="14">
-        <v>27518</v>
-      </c>
-    </row>
-    <row r="251" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H251" s="16" t="s">
-        <v>585</v>
-      </c>
-      <c r="I251" s="14">
-        <v>20748</v>
-      </c>
-    </row>
-    <row r="252" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H252" s="16" t="s">
-        <v>577</v>
-      </c>
-      <c r="I252" s="14">
-        <v>13521</v>
-      </c>
-    </row>
-    <row r="253" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H253" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="I253" s="14">
-        <v>17744</v>
-      </c>
-    </row>
-    <row r="254" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H254" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="I254" s="14">
-        <v>23340</v>
-      </c>
-    </row>
-    <row r="255" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H255" s="16" t="s">
-        <v>353</v>
-      </c>
-      <c r="I255" s="14">
-        <v>212372</v>
-      </c>
-    </row>
-    <row r="256" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H256" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="I256" s="14">
-        <v>559220</v>
-      </c>
-    </row>
-    <row r="257" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H257" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="I257" s="14">
-        <v>225198</v>
-      </c>
-    </row>
-    <row r="258" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H258" s="16" t="s">
-        <v>571</v>
-      </c>
-      <c r="I258" s="14">
-        <v>26761</v>
-      </c>
-    </row>
-    <row r="259" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H259" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="I259" s="14">
-        <v>17403</v>
-      </c>
-    </row>
-    <row r="260" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H260" s="16" t="s">
-        <v>400</v>
-      </c>
-      <c r="I260" s="14">
-        <v>237155</v>
-      </c>
-    </row>
-    <row r="261" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H261" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="I261" s="14">
-        <v>35838</v>
-      </c>
-    </row>
-    <row r="262" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H262" s="16" t="s">
-        <v>510</v>
-      </c>
-      <c r="I262" s="14">
-        <v>55756</v>
-      </c>
-    </row>
-    <row r="263" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H263" s="16" t="s">
-        <v>603</v>
-      </c>
-      <c r="I263" s="14">
-        <v>21783</v>
-      </c>
-    </row>
-    <row r="264" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H264" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I264" s="14">
-        <v>40630</v>
-      </c>
-    </row>
-    <row r="265" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H265" s="16" t="s">
-        <v>423</v>
-      </c>
-      <c r="I265" s="14">
-        <v>73967</v>
-      </c>
-    </row>
-    <row r="266" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H266" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="I266" s="14">
-        <v>5499</v>
-      </c>
-    </row>
-    <row r="267" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H267" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="I267" s="14">
-        <v>6680</v>
-      </c>
-    </row>
-    <row r="268" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H268" s="16" t="s">
-        <v>569</v>
-      </c>
-      <c r="I268" s="14">
-        <v>6040</v>
-      </c>
-    </row>
-    <row r="269" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H269" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="I269" s="14">
-        <v>37575</v>
-      </c>
-    </row>
-    <row r="270" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H270" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="I270" s="14">
-        <v>30213</v>
-      </c>
-    </row>
-    <row r="271" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H271" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="I271" s="14">
-        <v>343514</v>
-      </c>
-    </row>
-    <row r="272" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H272" s="16" t="s">
-        <v>599</v>
-      </c>
-      <c r="I272" s="14">
-        <v>442114</v>
-      </c>
-    </row>
-    <row r="273" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H273" s="16" t="s">
-        <v>646</v>
-      </c>
-      <c r="I273" s="14">
-        <v>70671</v>
-      </c>
-    </row>
-    <row r="274" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H274" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="I274" s="14">
-        <v>38035</v>
-      </c>
-    </row>
-    <row r="275" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H275" s="16" t="s">
-        <v>579</v>
-      </c>
-      <c r="I275" s="14">
-        <v>10481</v>
-      </c>
-    </row>
-    <row r="276" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H276" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="I276" s="14">
-        <v>1675988</v>
-      </c>
-    </row>
-    <row r="277" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H277" s="16" t="s">
-        <v>420</v>
-      </c>
-      <c r="I277" s="14">
-        <v>41019</v>
-      </c>
-    </row>
-    <row r="278" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H278" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="I278" s="14">
-        <v>9339</v>
-      </c>
-    </row>
-    <row r="279" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H279" s="16" t="s">
-        <v>589</v>
-      </c>
-      <c r="I279" s="14">
-        <v>142744</v>
-      </c>
-    </row>
-    <row r="280" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H280" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="I280" s="14">
-        <v>16566</v>
-      </c>
-    </row>
-    <row r="281" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H281" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="I281" s="14">
-        <v>66897</v>
-      </c>
-    </row>
-    <row r="282" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H282" s="16" t="s">
-        <v>627</v>
-      </c>
-      <c r="I282" s="14">
-        <v>18716</v>
-      </c>
-    </row>
-    <row r="283" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H283" s="16" t="s">
-        <v>499</v>
-      </c>
-      <c r="I283" s="14">
-        <v>79181</v>
-      </c>
-    </row>
-    <row r="284" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H284" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="I284" s="14">
-        <v>14406</v>
-      </c>
-    </row>
-    <row r="285" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H285" s="16" t="s">
-        <v>553</v>
-      </c>
-      <c r="I285" s="14">
-        <v>3737</v>
-      </c>
-    </row>
-    <row r="286" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H286" s="16" t="s">
-        <v>708</v>
-      </c>
-      <c r="I286" s="14">
-        <v>246805</v>
-      </c>
-    </row>
-    <row r="287" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H287" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="I287" s="14">
-        <v>6667</v>
-      </c>
-    </row>
-    <row r="288" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H288" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="I288" s="14">
-        <v>1015979</v>
-      </c>
-    </row>
-    <row r="289" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H289" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="I289" s="14">
-        <v>1224740</v>
-      </c>
-    </row>
-    <row r="290" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H290" s="16" t="s">
-        <v>514</v>
-      </c>
-      <c r="I290" s="14">
-        <v>14945</v>
-      </c>
-    </row>
-    <row r="291" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H291" s="16" t="s">
-        <v>686</v>
-      </c>
-      <c r="I291" s="14">
-        <v>118282</v>
-      </c>
-    </row>
-    <row r="292" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H292" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="I292" s="14">
-        <v>21200</v>
-      </c>
-    </row>
-    <row r="293" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H293" s="16" t="s">
-        <v>538</v>
-      </c>
-      <c r="I293" s="14">
-        <v>27049</v>
-      </c>
-    </row>
-    <row r="294" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H294" s="16" t="s">
-        <v>512</v>
-      </c>
-      <c r="I294" s="14">
-        <v>38516</v>
-      </c>
-    </row>
-    <row r="295" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H295" s="16" t="s">
-        <v>606</v>
-      </c>
-      <c r="I295" s="14">
-        <v>20046</v>
-      </c>
-    </row>
-    <row r="296" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H296" s="16" t="s">
-        <v>744</v>
-      </c>
-      <c r="I296" s="14">
+      <c r="I296">
         <v>32568773</v>
       </c>
     </row>
     <row r="297" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H297" s="16" t="s">
-        <v>742</v>
-      </c>
-      <c r="I297" s="14">
+      <c r="H297" s="15" t="s">
+        <v>739</v>
+      </c>
+      <c r="I297">
         <v>65137546</v>
       </c>
     </row>
@@ -19017,8 +19016,8 @@
     <col min="9" max="9" width="9.44140625" style="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -19026,8 +19025,7 @@
     <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20552,38 +20550,38 @@
       <c r="K33" s="2">
         <v>134654</v>
       </c>
-      <c r="M33" s="9" t="s">
-        <v>717</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="O33" s="9" t="s">
+      <c r="M33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="P33" s="9" t="s">
+      <c r="P33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="9" t="s">
+      <c r="Q33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="R33" s="9" t="s">
+      <c r="R33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S33" s="9" t="s">
+      <c r="S33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="T33" s="9" t="s">
+      <c r="T33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="U33" s="9" t="s">
+      <c r="U33" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="V33" s="9" t="s">
+      <c r="V33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="W33" s="9" t="s">
-        <v>719</v>
+      <c r="W33" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
@@ -20624,7 +20622,7 @@
         <v>11</v>
       </c>
       <c r="N34" t="str" cm="1">
-        <f t="array" ref="N34:W34">_xlfn.XLOOKUP(M34,A2:A394,B2:K394,"not found",-1)</f>
+        <f t="array" ref="N34:W34">_xlfn.XLOOKUP(M34,A2:A394,B2:K394,,0)</f>
         <v>None</v>
       </c>
       <c r="O34" t="str">
@@ -20693,7 +20691,7 @@
         <v>18</v>
       </c>
       <c r="N35" t="str" cm="1">
-        <f t="array" ref="N35:W35">_xlfn.XLOOKUP(M35,A3:A395,B3:K395,"not found",-1)</f>
+        <f t="array" ref="N35:W35">_xlfn.XLOOKUP(M35,A3:A395,B3:K395,,0)</f>
         <v>None</v>
       </c>
       <c r="O35" t="str">
@@ -20759,38 +20757,38 @@
         <v>15673</v>
       </c>
       <c r="M36" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="N36" t="str" cm="1">
-        <f t="array" ref="N36:W36">_xlfn.XLOOKUP(M36,A4:A396,B4:K396,"not found",-1)</f>
-        <v>None</v>
+        <f t="array" ref="N36:W36">_xlfn.XLOOKUP(M36,A4:A396,B4:K396,,0)</f>
+        <v>It Manager</v>
       </c>
       <c r="O36" t="str">
-        <v>none</v>
+        <v>5 years</v>
       </c>
       <c r="P36" t="str">
-        <v>Mortgage</v>
+        <v>Rent</v>
       </c>
       <c r="Q36">
-        <v>120000</v>
+        <v>82000</v>
       </c>
       <c r="R36" t="str">
         <v>none</v>
       </c>
       <c r="S36" t="str">
-        <v>Source Verified</v>
+        <v>Not Verified</v>
       </c>
       <c r="T36" t="str">
-        <v>015xx</v>
+        <v>109xx</v>
       </c>
       <c r="U36" t="str">
-        <v>MA</v>
+        <v>NY</v>
       </c>
       <c r="V36">
-        <v>15652</v>
+        <v>851</v>
       </c>
       <c r="W36">
-        <v>281735</v>
+        <v>10215</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
@@ -20827,36 +20825,39 @@
       <c r="K37" s="2">
         <v>20828</v>
       </c>
-      <c r="N37" cm="1">
-        <f t="array" ref="N37:W37">_xlfn.XLOOKUP(M37,A5:A397,B5:K397,"not found",-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
+      <c r="M37" t="s">
+        <v>557</v>
+      </c>
+      <c r="N37" t="str" cm="1">
+        <f t="array" ref="N37:W37">_xlfn.XLOOKUP(M37,A5:A397,B5:K397,,0)</f>
+        <v>Director</v>
+      </c>
+      <c r="O37" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P37" t="str">
+        <v>Rent</v>
       </c>
       <c r="Q37">
-        <v>38335069.949000001</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
+        <v>275000</v>
+      </c>
+      <c r="R37" t="str">
+        <v>none</v>
+      </c>
+      <c r="S37" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="T37" t="str">
+        <v>112xx</v>
+      </c>
+      <c r="U37" t="str">
+        <v>NY</v>
       </c>
       <c r="V37">
-        <v>3202883</v>
+        <v>6379</v>
       </c>
       <c r="W37">
-        <v>32568773</v>
+        <v>70168</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
@@ -20893,36 +20894,39 @@
       <c r="K38" s="2">
         <v>20021</v>
       </c>
-      <c r="N38" cm="1">
-        <f t="array" ref="N38:W38">_xlfn.XLOOKUP(M38,A6:A398,B6:K398,"not found",-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
+      <c r="M38" t="s">
+        <v>98</v>
+      </c>
+      <c r="N38" t="str" cm="1">
+        <f t="array" ref="N38:W38">_xlfn.XLOOKUP(M38,A6:A398,B6:K398,,0)</f>
+        <v>Dental Hygiene</v>
+      </c>
+      <c r="O38" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="P38" t="str">
+        <v>Rent</v>
       </c>
       <c r="Q38">
-        <v>38335069.949000001</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>0</v>
+        <v>96000</v>
+      </c>
+      <c r="R38" t="str">
+        <v>none</v>
+      </c>
+      <c r="S38" t="str">
+        <v>Not Verified</v>
+      </c>
+      <c r="T38" t="str">
+        <v>108xx</v>
+      </c>
+      <c r="U38" t="str">
+        <v>NY</v>
       </c>
       <c r="V38">
-        <v>3202883</v>
+        <v>41983</v>
       </c>
       <c r="W38">
-        <v>32568773</v>
+        <v>251895</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
@@ -20941,8 +20945,8 @@
       <c r="E39" s="2">
         <v>9000</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>720</v>
+      <c r="F39" s="16" t="s">
+        <v>13</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>15</v>
@@ -21367,7 +21371,7 @@
         <v>90000</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>721</v>
+        <v>745</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>20</v>
@@ -22347,7 +22351,7 @@
         <v>62000</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>15</v>
@@ -22487,7 +22491,7 @@
         <v>60000</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>20</v>
@@ -22697,7 +22701,7 @@
         <v>48000</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>20</v>
@@ -23082,7 +23086,7 @@
         <v>55000</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>22</v>
@@ -23257,7 +23261,7 @@
         <v>16000</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>15</v>
@@ -23642,7 +23646,7 @@
         <v>45000</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>22</v>
@@ -24272,7 +24276,7 @@
         <v>55000</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>20</v>
@@ -27387,7 +27391,7 @@
         <v>120000</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>22</v>
@@ -27597,7 +27601,7 @@
         <v>55000</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>730</v>
+        <v>746</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>20</v>
@@ -27877,7 +27881,7 @@
         <v>82000</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>20</v>
@@ -28227,7 +28231,7 @@
         <v>60000</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>22</v>
@@ -28332,7 +28336,7 @@
         <v>33500</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>22</v>
@@ -29487,7 +29491,7 @@
         <v>20000</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="G283" s="4" t="s">
         <v>22</v>
@@ -29802,7 +29806,7 @@
         <v>165000</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="G292" s="4" t="s">
         <v>20</v>
@@ -30642,7 +30646,7 @@
         <v>42000</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="G316" s="4" t="s">
         <v>20</v>
@@ -32217,7 +32221,7 @@
         <v>100000</v>
       </c>
       <c r="F361" s="4" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="G361" s="4" t="s">
         <v>20</v>
@@ -32252,7 +32256,7 @@
         <v>75000</v>
       </c>
       <c r="F362" s="4" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="G362" s="4" t="s">
         <v>20</v>
@@ -32322,7 +32326,7 @@
         <v>90000</v>
       </c>
       <c r="F364" s="4" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="G364" s="4" t="s">
         <v>20</v>

--- a/finance_customer.csv.xlsx
+++ b/finance_customer.csv.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pandas\Finance data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B10C367-71AB-4166-BDFA-B93347D92200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD10826B-74FE-45F1-985F-B20A4F0010F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9802DE5F-B1D8-4319-BDEA-30F1B831059A}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3145" uniqueCount="730">
   <si>
     <t>customer_id</t>
   </si>
@@ -2802,7 +2802,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2841,12 +2841,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -14348,6 +14349,465 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D0CA5600-92BA-45FE-80B4-8C71AE4E87C6}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField multipleItemSelectionAllowed="1" showAll="0">
+      <items count="394">
+        <item x="280"/>
+        <item x="281"/>
+        <item x="286"/>
+        <item x="221"/>
+        <item x="141"/>
+        <item x="364"/>
+        <item x="278"/>
+        <item x="190"/>
+        <item x="353"/>
+        <item x="147"/>
+        <item x="296"/>
+        <item x="130"/>
+        <item x="251"/>
+        <item x="120"/>
+        <item x="136"/>
+        <item x="247"/>
+        <item x="377"/>
+        <item x="87"/>
+        <item x="356"/>
+        <item x="370"/>
+        <item x="216"/>
+        <item x="12"/>
+        <item x="227"/>
+        <item x="9"/>
+        <item x="306"/>
+        <item x="262"/>
+        <item x="270"/>
+        <item x="392"/>
+        <item x="77"/>
+        <item x="135"/>
+        <item x="146"/>
+        <item x="354"/>
+        <item x="18"/>
+        <item x="254"/>
+        <item x="345"/>
+        <item x="350"/>
+        <item x="92"/>
+        <item x="205"/>
+        <item x="260"/>
+        <item x="304"/>
+        <item x="30"/>
+        <item x="131"/>
+        <item x="169"/>
+        <item x="232"/>
+        <item x="29"/>
+        <item x="111"/>
+        <item x="158"/>
+        <item x="145"/>
+        <item x="235"/>
+        <item x="294"/>
+        <item x="358"/>
+        <item x="138"/>
+        <item x="313"/>
+        <item x="359"/>
+        <item x="160"/>
+        <item x="69"/>
+        <item x="171"/>
+        <item x="224"/>
+        <item x="372"/>
+        <item x="311"/>
+        <item x="387"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="316"/>
+        <item x="167"/>
+        <item x="230"/>
+        <item x="123"/>
+        <item x="347"/>
+        <item x="365"/>
+        <item x="175"/>
+        <item x="371"/>
+        <item x="236"/>
+        <item x="162"/>
+        <item x="170"/>
+        <item x="64"/>
+        <item x="322"/>
+        <item x="233"/>
+        <item x="288"/>
+        <item x="211"/>
+        <item x="267"/>
+        <item x="274"/>
+        <item x="127"/>
+        <item x="142"/>
+        <item x="310"/>
+        <item x="196"/>
+        <item x="207"/>
+        <item x="140"/>
+        <item x="301"/>
+        <item x="248"/>
+        <item x="68"/>
+        <item x="38"/>
+        <item x="172"/>
+        <item x="113"/>
+        <item x="86"/>
+        <item x="150"/>
+        <item x="116"/>
+        <item x="240"/>
+        <item x="273"/>
+        <item x="285"/>
+        <item x="250"/>
+        <item x="34"/>
+        <item x="193"/>
+        <item x="253"/>
+        <item x="72"/>
+        <item x="163"/>
+        <item x="129"/>
+        <item x="108"/>
+        <item x="13"/>
+        <item x="70"/>
+        <item x="186"/>
+        <item x="81"/>
+        <item x="128"/>
+        <item x="319"/>
+        <item x="143"/>
+        <item x="85"/>
+        <item x="174"/>
+        <item x="164"/>
+        <item x="183"/>
+        <item x="89"/>
+        <item x="355"/>
+        <item x="219"/>
+        <item x="40"/>
+        <item x="305"/>
+        <item x="182"/>
+        <item x="76"/>
+        <item x="341"/>
+        <item x="318"/>
+        <item x="380"/>
+        <item x="56"/>
+        <item x="239"/>
+        <item x="384"/>
+        <item x="54"/>
+        <item x="106"/>
+        <item x="36"/>
+        <item x="328"/>
+        <item x="212"/>
+        <item x="32"/>
+        <item x="315"/>
+        <item x="26"/>
+        <item x="35"/>
+        <item x="148"/>
+        <item x="330"/>
+        <item x="41"/>
+        <item x="119"/>
+        <item x="132"/>
+        <item x="331"/>
+        <item x="263"/>
+        <item x="65"/>
+        <item x="279"/>
+        <item x="367"/>
+        <item x="326"/>
+        <item x="165"/>
+        <item x="201"/>
+        <item x="179"/>
+        <item x="391"/>
+        <item x="71"/>
+        <item x="109"/>
+        <item x="243"/>
+        <item x="155"/>
+        <item x="139"/>
+        <item x="107"/>
+        <item x="258"/>
+        <item x="7"/>
+        <item x="379"/>
+        <item x="238"/>
+        <item x="166"/>
+        <item x="349"/>
+        <item x="335"/>
+        <item x="95"/>
+        <item x="324"/>
+        <item x="144"/>
+        <item x="283"/>
+        <item x="362"/>
+        <item x="102"/>
+        <item x="276"/>
+        <item x="297"/>
+        <item x="307"/>
+        <item x="287"/>
+        <item x="228"/>
+        <item x="67"/>
+        <item x="302"/>
+        <item x="225"/>
+        <item x="352"/>
+        <item x="93"/>
+        <item x="269"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="168"/>
+        <item x="19"/>
+        <item x="261"/>
+        <item x="55"/>
+        <item x="312"/>
+        <item x="292"/>
+        <item x="159"/>
+        <item x="51"/>
+        <item x="156"/>
+        <item x="118"/>
+        <item x="223"/>
+        <item x="8"/>
+        <item x="94"/>
+        <item x="44"/>
+        <item x="226"/>
+        <item x="244"/>
+        <item x="5"/>
+        <item x="197"/>
+        <item x="275"/>
+        <item x="91"/>
+        <item x="151"/>
+        <item x="382"/>
+        <item x="363"/>
+        <item x="149"/>
+        <item x="0"/>
+        <item x="343"/>
+        <item x="333"/>
+        <item x="361"/>
+        <item x="231"/>
+        <item x="229"/>
+        <item x="134"/>
+        <item x="20"/>
+        <item x="80"/>
+        <item x="137"/>
+        <item x="14"/>
+        <item x="189"/>
+        <item x="101"/>
+        <item x="383"/>
+        <item x="272"/>
+        <item x="63"/>
+        <item x="321"/>
+        <item x="47"/>
+        <item x="28"/>
+        <item x="11"/>
+        <item x="185"/>
+        <item x="23"/>
+        <item x="237"/>
+        <item x="234"/>
+        <item x="218"/>
+        <item x="209"/>
+        <item x="117"/>
+        <item x="194"/>
+        <item x="105"/>
+        <item x="110"/>
+        <item x="308"/>
+        <item x="378"/>
+        <item x="157"/>
+        <item x="213"/>
+        <item x="181"/>
+        <item x="277"/>
+        <item x="268"/>
+        <item x="98"/>
+        <item x="256"/>
+        <item x="368"/>
+        <item x="246"/>
+        <item x="222"/>
+        <item x="369"/>
+        <item x="104"/>
+        <item x="115"/>
+        <item x="52"/>
+        <item x="332"/>
+        <item x="300"/>
+        <item x="257"/>
+        <item x="346"/>
+        <item x="366"/>
+        <item x="291"/>
+        <item x="125"/>
+        <item x="217"/>
+        <item x="210"/>
+        <item x="133"/>
+        <item x="200"/>
+        <item x="271"/>
+        <item x="357"/>
+        <item x="339"/>
+        <item x="161"/>
+        <item x="180"/>
+        <item x="282"/>
+        <item x="342"/>
+        <item x="152"/>
+        <item x="124"/>
+        <item x="176"/>
+        <item x="284"/>
+        <item x="122"/>
+        <item x="17"/>
+        <item x="299"/>
+        <item x="351"/>
+        <item x="289"/>
+        <item x="37"/>
+        <item x="245"/>
+        <item x="220"/>
+        <item x="79"/>
+        <item x="188"/>
+        <item x="16"/>
+        <item x="265"/>
+        <item x="255"/>
+        <item x="295"/>
+        <item x="42"/>
+        <item x="203"/>
+        <item x="215"/>
+        <item x="192"/>
+        <item x="242"/>
+        <item x="338"/>
+        <item x="340"/>
+        <item x="82"/>
+        <item x="10"/>
+        <item x="385"/>
+        <item x="97"/>
+        <item x="184"/>
+        <item x="48"/>
+        <item x="59"/>
+        <item x="202"/>
+        <item x="199"/>
+        <item x="24"/>
+        <item x="298"/>
+        <item x="334"/>
+        <item x="348"/>
+        <item x="374"/>
+        <item x="329"/>
+        <item x="173"/>
+        <item x="204"/>
+        <item x="198"/>
+        <item x="31"/>
+        <item x="303"/>
+        <item x="344"/>
+        <item x="266"/>
+        <item x="15"/>
+        <item x="317"/>
+        <item x="61"/>
+        <item x="177"/>
+        <item x="1"/>
+        <item x="83"/>
+        <item x="290"/>
+        <item x="178"/>
+        <item x="375"/>
+        <item x="126"/>
+        <item x="325"/>
+        <item x="208"/>
+        <item x="381"/>
+        <item x="78"/>
+        <item x="46"/>
+        <item x="121"/>
+        <item x="373"/>
+        <item x="376"/>
+        <item x="389"/>
+        <item x="293"/>
+        <item x="4"/>
+        <item x="386"/>
+        <item x="154"/>
+        <item x="214"/>
+        <item x="53"/>
+        <item x="27"/>
+        <item x="241"/>
+        <item x="100"/>
+        <item x="112"/>
+        <item x="45"/>
+        <item x="43"/>
+        <item x="103"/>
+        <item x="206"/>
+        <item x="388"/>
+        <item x="114"/>
+        <item x="39"/>
+        <item x="320"/>
+        <item x="2"/>
+        <item x="249"/>
+        <item x="60"/>
+        <item x="75"/>
+        <item x="50"/>
+        <item x="314"/>
+        <item x="259"/>
+        <item x="327"/>
+        <item x="33"/>
+        <item x="96"/>
+        <item x="88"/>
+        <item x="73"/>
+        <item x="58"/>
+        <item x="84"/>
+        <item x="3"/>
+        <item x="66"/>
+        <item x="21"/>
+        <item x="390"/>
+        <item x="62"/>
+        <item x="49"/>
+        <item x="6"/>
+        <item x="153"/>
+        <item x="309"/>
+        <item x="323"/>
+        <item x="187"/>
+        <item x="57"/>
+        <item x="360"/>
+        <item x="74"/>
+        <item x="195"/>
+        <item x="90"/>
+        <item x="252"/>
+        <item x="264"/>
+        <item x="99"/>
+        <item x="191"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of annual_inc" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA328EE9-D6A1-4564-A98F-EB239F495583}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A14:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
@@ -14447,7 +14907,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1BEB0EC-1B93-46CD-AF9B-F4264EF3619B}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H11:I297" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
@@ -15644,7 +16104,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4257A7A8-6D2C-4CF7-952A-0B876954193D}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E4:F8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
@@ -15702,465 +16162,6 @@
   </pageFields>
   <dataFields count="1">
     <dataField name="Count of addr_state" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D0CA5600-92BA-45FE-80B4-8C71AE4E87C6}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField multipleItemSelectionAllowed="1" showAll="0">
-      <items count="394">
-        <item x="280"/>
-        <item x="281"/>
-        <item x="286"/>
-        <item x="221"/>
-        <item x="141"/>
-        <item x="364"/>
-        <item x="278"/>
-        <item x="190"/>
-        <item x="353"/>
-        <item x="147"/>
-        <item x="296"/>
-        <item x="130"/>
-        <item x="251"/>
-        <item x="120"/>
-        <item x="136"/>
-        <item x="247"/>
-        <item x="377"/>
-        <item x="87"/>
-        <item x="356"/>
-        <item x="370"/>
-        <item x="216"/>
-        <item x="12"/>
-        <item x="227"/>
-        <item x="9"/>
-        <item x="306"/>
-        <item x="262"/>
-        <item x="270"/>
-        <item x="392"/>
-        <item x="77"/>
-        <item x="135"/>
-        <item x="146"/>
-        <item x="354"/>
-        <item x="18"/>
-        <item x="254"/>
-        <item x="345"/>
-        <item x="350"/>
-        <item x="92"/>
-        <item x="205"/>
-        <item x="260"/>
-        <item x="304"/>
-        <item x="30"/>
-        <item x="131"/>
-        <item x="169"/>
-        <item x="232"/>
-        <item x="29"/>
-        <item x="111"/>
-        <item x="158"/>
-        <item x="145"/>
-        <item x="235"/>
-        <item x="294"/>
-        <item x="358"/>
-        <item x="138"/>
-        <item x="313"/>
-        <item x="359"/>
-        <item x="160"/>
-        <item x="69"/>
-        <item x="171"/>
-        <item x="224"/>
-        <item x="372"/>
-        <item x="311"/>
-        <item x="387"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="316"/>
-        <item x="167"/>
-        <item x="230"/>
-        <item x="123"/>
-        <item x="347"/>
-        <item x="365"/>
-        <item x="175"/>
-        <item x="371"/>
-        <item x="236"/>
-        <item x="162"/>
-        <item x="170"/>
-        <item x="64"/>
-        <item x="322"/>
-        <item x="233"/>
-        <item x="288"/>
-        <item x="211"/>
-        <item x="267"/>
-        <item x="274"/>
-        <item x="127"/>
-        <item x="142"/>
-        <item x="310"/>
-        <item x="196"/>
-        <item x="207"/>
-        <item x="140"/>
-        <item x="301"/>
-        <item x="248"/>
-        <item x="68"/>
-        <item x="38"/>
-        <item x="172"/>
-        <item x="113"/>
-        <item x="86"/>
-        <item x="150"/>
-        <item x="116"/>
-        <item x="240"/>
-        <item x="273"/>
-        <item x="285"/>
-        <item x="250"/>
-        <item x="34"/>
-        <item x="193"/>
-        <item x="253"/>
-        <item x="72"/>
-        <item x="163"/>
-        <item x="129"/>
-        <item x="108"/>
-        <item x="13"/>
-        <item x="70"/>
-        <item x="186"/>
-        <item x="81"/>
-        <item x="128"/>
-        <item x="319"/>
-        <item x="143"/>
-        <item x="85"/>
-        <item x="174"/>
-        <item x="164"/>
-        <item x="183"/>
-        <item x="89"/>
-        <item x="355"/>
-        <item x="219"/>
-        <item x="40"/>
-        <item x="305"/>
-        <item x="182"/>
-        <item x="76"/>
-        <item x="341"/>
-        <item x="318"/>
-        <item x="380"/>
-        <item x="56"/>
-        <item x="239"/>
-        <item x="384"/>
-        <item x="54"/>
-        <item x="106"/>
-        <item x="36"/>
-        <item x="328"/>
-        <item x="212"/>
-        <item x="32"/>
-        <item x="315"/>
-        <item x="26"/>
-        <item x="35"/>
-        <item x="148"/>
-        <item x="330"/>
-        <item x="41"/>
-        <item x="119"/>
-        <item x="132"/>
-        <item x="331"/>
-        <item x="263"/>
-        <item x="65"/>
-        <item x="279"/>
-        <item x="367"/>
-        <item x="326"/>
-        <item x="165"/>
-        <item x="201"/>
-        <item x="179"/>
-        <item x="391"/>
-        <item x="71"/>
-        <item x="109"/>
-        <item x="243"/>
-        <item x="155"/>
-        <item x="139"/>
-        <item x="107"/>
-        <item x="258"/>
-        <item x="7"/>
-        <item x="379"/>
-        <item x="238"/>
-        <item x="166"/>
-        <item x="349"/>
-        <item x="335"/>
-        <item x="95"/>
-        <item x="324"/>
-        <item x="144"/>
-        <item x="283"/>
-        <item x="362"/>
-        <item x="102"/>
-        <item x="276"/>
-        <item x="297"/>
-        <item x="307"/>
-        <item x="287"/>
-        <item x="228"/>
-        <item x="67"/>
-        <item x="302"/>
-        <item x="225"/>
-        <item x="352"/>
-        <item x="93"/>
-        <item x="269"/>
-        <item x="22"/>
-        <item x="25"/>
-        <item x="168"/>
-        <item x="19"/>
-        <item x="261"/>
-        <item x="55"/>
-        <item x="312"/>
-        <item x="292"/>
-        <item x="159"/>
-        <item x="51"/>
-        <item x="156"/>
-        <item x="118"/>
-        <item x="223"/>
-        <item x="8"/>
-        <item x="94"/>
-        <item x="44"/>
-        <item x="226"/>
-        <item x="244"/>
-        <item x="5"/>
-        <item x="197"/>
-        <item x="275"/>
-        <item x="91"/>
-        <item x="151"/>
-        <item x="382"/>
-        <item x="363"/>
-        <item x="149"/>
-        <item x="0"/>
-        <item x="343"/>
-        <item x="333"/>
-        <item x="361"/>
-        <item x="231"/>
-        <item x="229"/>
-        <item x="134"/>
-        <item x="20"/>
-        <item x="80"/>
-        <item x="137"/>
-        <item x="14"/>
-        <item x="189"/>
-        <item x="101"/>
-        <item x="383"/>
-        <item x="272"/>
-        <item x="63"/>
-        <item x="321"/>
-        <item x="47"/>
-        <item x="28"/>
-        <item x="11"/>
-        <item x="185"/>
-        <item x="23"/>
-        <item x="237"/>
-        <item x="234"/>
-        <item x="218"/>
-        <item x="209"/>
-        <item x="117"/>
-        <item x="194"/>
-        <item x="105"/>
-        <item x="110"/>
-        <item x="308"/>
-        <item x="378"/>
-        <item x="157"/>
-        <item x="213"/>
-        <item x="181"/>
-        <item x="277"/>
-        <item x="268"/>
-        <item x="98"/>
-        <item x="256"/>
-        <item x="368"/>
-        <item x="246"/>
-        <item x="222"/>
-        <item x="369"/>
-        <item x="104"/>
-        <item x="115"/>
-        <item x="52"/>
-        <item x="332"/>
-        <item x="300"/>
-        <item x="257"/>
-        <item x="346"/>
-        <item x="366"/>
-        <item x="291"/>
-        <item x="125"/>
-        <item x="217"/>
-        <item x="210"/>
-        <item x="133"/>
-        <item x="200"/>
-        <item x="271"/>
-        <item x="357"/>
-        <item x="339"/>
-        <item x="161"/>
-        <item x="180"/>
-        <item x="282"/>
-        <item x="342"/>
-        <item x="152"/>
-        <item x="124"/>
-        <item x="176"/>
-        <item x="284"/>
-        <item x="122"/>
-        <item x="17"/>
-        <item x="299"/>
-        <item x="351"/>
-        <item x="289"/>
-        <item x="37"/>
-        <item x="245"/>
-        <item x="220"/>
-        <item x="79"/>
-        <item x="188"/>
-        <item x="16"/>
-        <item x="265"/>
-        <item x="255"/>
-        <item x="295"/>
-        <item x="42"/>
-        <item x="203"/>
-        <item x="215"/>
-        <item x="192"/>
-        <item x="242"/>
-        <item x="338"/>
-        <item x="340"/>
-        <item x="82"/>
-        <item x="10"/>
-        <item x="385"/>
-        <item x="97"/>
-        <item x="184"/>
-        <item x="48"/>
-        <item x="59"/>
-        <item x="202"/>
-        <item x="199"/>
-        <item x="24"/>
-        <item x="298"/>
-        <item x="334"/>
-        <item x="348"/>
-        <item x="374"/>
-        <item x="329"/>
-        <item x="173"/>
-        <item x="204"/>
-        <item x="198"/>
-        <item x="31"/>
-        <item x="303"/>
-        <item x="344"/>
-        <item x="266"/>
-        <item x="15"/>
-        <item x="317"/>
-        <item x="61"/>
-        <item x="177"/>
-        <item x="1"/>
-        <item x="83"/>
-        <item x="290"/>
-        <item x="178"/>
-        <item x="375"/>
-        <item x="126"/>
-        <item x="325"/>
-        <item x="208"/>
-        <item x="381"/>
-        <item x="78"/>
-        <item x="46"/>
-        <item x="121"/>
-        <item x="373"/>
-        <item x="376"/>
-        <item x="389"/>
-        <item x="293"/>
-        <item x="4"/>
-        <item x="386"/>
-        <item x="154"/>
-        <item x="214"/>
-        <item x="53"/>
-        <item x="27"/>
-        <item x="241"/>
-        <item x="100"/>
-        <item x="112"/>
-        <item x="45"/>
-        <item x="43"/>
-        <item x="103"/>
-        <item x="206"/>
-        <item x="388"/>
-        <item x="114"/>
-        <item x="39"/>
-        <item x="320"/>
-        <item x="2"/>
-        <item x="249"/>
-        <item x="60"/>
-        <item x="75"/>
-        <item x="50"/>
-        <item x="314"/>
-        <item x="259"/>
-        <item x="327"/>
-        <item x="33"/>
-        <item x="96"/>
-        <item x="88"/>
-        <item x="73"/>
-        <item x="58"/>
-        <item x="84"/>
-        <item x="3"/>
-        <item x="66"/>
-        <item x="21"/>
-        <item x="390"/>
-        <item x="62"/>
-        <item x="49"/>
-        <item x="6"/>
-        <item x="153"/>
-        <item x="309"/>
-        <item x="323"/>
-        <item x="187"/>
-        <item x="57"/>
-        <item x="360"/>
-        <item x="74"/>
-        <item x="195"/>
-        <item x="90"/>
-        <item x="252"/>
-        <item x="264"/>
-        <item x="99"/>
-        <item x="191"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of annual_inc" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -16612,7 +16613,7 @@
       <c r="J3" s="2">
         <v>150674</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="3" t="s">
         <v>729</v>
       </c>
     </row>
@@ -16647,7 +16648,7 @@
       <c r="J4" s="2">
         <v>281735</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="17">
         <f>SUM(E2:E395)</f>
         <v>76670139.898000002</v>
       </c>
@@ -16875,12 +16876,12 @@
       <c r="J10" s="2">
         <v>30491</v>
       </c>
-      <c r="N10" s="20" t="s">
+      <c r="N10" s="21" t="s">
         <v>728</v>
       </c>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -18035,34 +18036,35 @@
       <c r="L34" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M34" t="str" cm="1">
+      <c r="M34" s="22" t="str" cm="1">
         <f t="array" ref="M34:U34">_xlfn.XLOOKUP(L34,A2:A394,B2:J394,,0)</f>
         <v>None</v>
       </c>
-      <c r="N34" t="str">
+      <c r="N34" s="22" t="str">
         <v>none</v>
       </c>
-      <c r="O34" t="str">
+      <c r="O34" s="22" t="str">
         <v>Rent</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="22">
         <v>25000</v>
       </c>
-      <c r="Q34" t="str">
+      <c r="Q34" s="22" t="str">
         <v>Verified</v>
       </c>
-      <c r="R34" t="str">
+      <c r="R34" s="22" t="str">
         <v>010xx</v>
       </c>
-      <c r="S34" t="str">
+      <c r="S34" s="22" t="str">
         <v>MA</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="22">
         <v>6864</v>
       </c>
-      <c r="U34">
+      <c r="U34" s="22">
         <v>34322</v>
       </c>
+      <c r="V34" s="22"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
@@ -18095,37 +18097,38 @@
       <c r="J35" s="2">
         <v>335106</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L35" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="M35" t="str" cm="1">
+      <c r="M35" s="22" t="str" cm="1">
         <f t="array" ref="M35:U35">_xlfn.XLOOKUP(L35,A3:A395,B3:J395,,0)</f>
         <v>None</v>
       </c>
-      <c r="N35" t="str">
+      <c r="N35" s="22" t="str">
         <v>none</v>
       </c>
-      <c r="O35" t="str">
+      <c r="O35" s="22" t="str">
         <v>Mortgage</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="22">
         <v>185000</v>
       </c>
-      <c r="Q35" t="str">
+      <c r="Q35" s="22" t="str">
         <v>Not Verified</v>
       </c>
-      <c r="R35" t="str">
+      <c r="R35" s="22" t="str">
         <v>010xx</v>
       </c>
-      <c r="S35" t="str">
+      <c r="S35" s="22" t="str">
         <v>MA</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="22">
         <v>7930</v>
       </c>
-      <c r="U35">
+      <c r="U35" s="22">
         <v>150674</v>
       </c>
+      <c r="V35" s="22"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
@@ -18158,37 +18161,38 @@
       <c r="J36" s="2">
         <v>15673</v>
       </c>
-      <c r="L36" t="s">
+      <c r="L36" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="M36" t="str" cm="1">
+      <c r="M36" s="22" t="str" cm="1">
         <f t="array" ref="M36:U36">_xlfn.XLOOKUP(L36,A4:A396,B4:J396,,0)</f>
         <v>It Manager</v>
       </c>
-      <c r="N36" t="str">
+      <c r="N36" s="22" t="str">
         <v>5 years</v>
       </c>
-      <c r="O36" t="str">
+      <c r="O36" s="22" t="str">
         <v>Rent</v>
       </c>
-      <c r="P36">
+      <c r="P36" s="22">
         <v>82000</v>
       </c>
-      <c r="Q36" t="str">
+      <c r="Q36" s="22" t="str">
         <v>Not Verified</v>
       </c>
-      <c r="R36" t="str">
+      <c r="R36" s="22" t="str">
         <v>109xx</v>
       </c>
-      <c r="S36" t="str">
+      <c r="S36" s="22" t="str">
         <v>NY</v>
       </c>
-      <c r="T36">
+      <c r="T36" s="22">
         <v>851</v>
       </c>
-      <c r="U36">
+      <c r="U36" s="22">
         <v>10215</v>
       </c>
+      <c r="V36" s="22"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
@@ -18221,37 +18225,38 @@
       <c r="J37" s="2">
         <v>20828</v>
       </c>
-      <c r="L37" t="s">
+      <c r="L37" s="22" t="s">
         <v>557</v>
       </c>
-      <c r="M37" t="str" cm="1">
+      <c r="M37" s="22" t="str" cm="1">
         <f t="array" ref="M37:U37">_xlfn.XLOOKUP(L37,A5:A397,B5:J397,,0)</f>
         <v>Director</v>
       </c>
-      <c r="N37" t="str">
+      <c r="N37" s="22" t="str">
         <v>5 years</v>
       </c>
-      <c r="O37" t="str">
+      <c r="O37" s="22" t="str">
         <v>Rent</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="22">
         <v>275000</v>
       </c>
-      <c r="Q37" t="str">
+      <c r="Q37" s="22" t="str">
         <v>Verified</v>
       </c>
-      <c r="R37" t="str">
+      <c r="R37" s="22" t="str">
         <v>112xx</v>
       </c>
-      <c r="S37" t="str">
+      <c r="S37" s="22" t="str">
         <v>NY</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="22">
         <v>6379</v>
       </c>
-      <c r="U37">
+      <c r="U37" s="22">
         <v>70168</v>
       </c>
+      <c r="V37" s="22"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
@@ -18284,37 +18289,38 @@
       <c r="J38" s="2">
         <v>20021</v>
       </c>
-      <c r="L38" t="s">
+      <c r="L38" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="M38" t="str" cm="1">
+      <c r="M38" s="22" t="str" cm="1">
         <f t="array" ref="M38:U38">_xlfn.XLOOKUP(L38,A6:A398,B6:J398,,0)</f>
         <v>Dental Hygiene</v>
       </c>
-      <c r="N38" t="str">
+      <c r="N38" s="22" t="str">
         <v>5 years</v>
       </c>
-      <c r="O38" t="str">
+      <c r="O38" s="22" t="str">
         <v>Rent</v>
       </c>
-      <c r="P38">
+      <c r="P38" s="22">
         <v>96000</v>
       </c>
-      <c r="Q38" t="str">
+      <c r="Q38" s="22" t="str">
         <v>Not Verified</v>
       </c>
-      <c r="R38" t="str">
+      <c r="R38" s="22" t="str">
         <v>108xx</v>
       </c>
-      <c r="S38" t="str">
+      <c r="S38" s="22" t="str">
         <v>NY</v>
       </c>
-      <c r="T38">
+      <c r="T38" s="22">
         <v>41983</v>
       </c>
-      <c r="U38">
+      <c r="U38" s="22">
         <v>251895</v>
       </c>
+      <c r="V38" s="22"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
@@ -18723,19 +18729,19 @@
       <c r="J50" s="2">
         <v>103172</v>
       </c>
-      <c r="M50" s="21" t="s">
+      <c r="M50" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="N50" s="21" t="s">
+      <c r="N50" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="O50" s="21" t="s">
+      <c r="O50" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="P50" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q50" s="21" t="s">
+      <c r="P50" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q50" s="20" t="s">
         <v>109</v>
       </c>
     </row>
@@ -18946,6 +18952,18 @@
       <c r="J56" s="2">
         <v>19731</v>
       </c>
+      <c r="L56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
@@ -18978,6 +18996,19 @@
       <c r="J57" s="2">
         <v>29277</v>
       </c>
+      <c r="L57" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M57" s="17" t="str" cm="1">
+        <f t="array" ref="M57:O57">VLOOKUP(L57,A2:J394,{2,5,10},FALSE)</f>
+        <v>None</v>
+      </c>
+      <c r="N57" s="17">
+        <v>25000</v>
+      </c>
+      <c r="O57" s="17">
+        <v>34322</v>
+      </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
@@ -19010,6 +19041,19 @@
       <c r="J58" s="2">
         <v>19340</v>
       </c>
+      <c r="L58" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="M58" s="17" t="str" cm="1">
+        <f t="array" ref="M58:O58">VLOOKUP(L58,A3:J395,{2,5,10},FALSE)</f>
+        <v>Sales</v>
+      </c>
+      <c r="N58" s="17">
+        <v>175000</v>
+      </c>
+      <c r="O58" s="17">
+        <v>323115</v>
+      </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
@@ -19042,6 +19086,19 @@
       <c r="J59" s="2">
         <v>448449</v>
       </c>
+      <c r="L59" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="M59" s="17" t="str" cm="1">
+        <f t="array" ref="M59:O59">VLOOKUP(L59,A4:J396,{2,5,10},FALSE)</f>
+        <v>None</v>
+      </c>
+      <c r="N59" s="17">
+        <v>44000</v>
+      </c>
+      <c r="O59" s="17">
+        <v>44446</v>
+      </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
@@ -19074,6 +19131,19 @@
       <c r="J60" s="2">
         <v>355619</v>
       </c>
+      <c r="L60" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M60" s="17" t="str" cm="1">
+        <f t="array" ref="M60:O60">VLOOKUP(L60,A5:J397,{2,5,10},FALSE)</f>
+        <v>Personal Care Assissstant</v>
+      </c>
+      <c r="N60" s="17">
+        <v>25000</v>
+      </c>
+      <c r="O60" s="17">
+        <v>12299</v>
+      </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
@@ -19106,6 +19176,19 @@
       <c r="J61" s="2">
         <v>105146</v>
       </c>
+      <c r="L61" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="M61" s="17" t="str" cm="1">
+        <f t="array" ref="M61:O61">VLOOKUP(L61,A6:J398,{2,5,10},FALSE)</f>
+        <v>Senior Director Of Strategy And Planning</v>
+      </c>
+      <c r="N61" s="17">
+        <v>150000</v>
+      </c>
+      <c r="O61" s="17">
+        <v>20374</v>
+      </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
@@ -19137,6 +19220,19 @@
       </c>
       <c r="J62" s="2">
         <v>298017</v>
+      </c>
+      <c r="L62" s="17" t="s">
+        <v>712</v>
+      </c>
+      <c r="M62" s="17" t="str" cm="1">
+        <f t="array" ref="M62:O62">VLOOKUP(L62,A7:J399,{2,5,10},FALSE)</f>
+        <v>Field Supervisor</v>
+      </c>
+      <c r="N62" s="17">
+        <v>39000</v>
+      </c>
+      <c r="O62" s="17">
+        <v>22971</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">

--- a/finance_customer.csv.xlsx
+++ b/finance_customer.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pandas\Finance data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD10826B-74FE-45F1-985F-B20A4F0010F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413594EE-6A91-4D9F-89EB-E30AB5C43CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9802DE5F-B1D8-4319-BDEA-30F1B831059A}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3145" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="730">
   <si>
     <t>customer_id</t>
   </si>
@@ -16495,16 +16495,15 @@
   <dimension ref="A1:V395"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="8" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -17983,24 +17982,22 @@
       <c r="P33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="1" t="s">
+      <c r="Q33" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="R33" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="S33" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="T33" s="10" t="s">
         <v>8</v>
       </c>
+      <c r="T33" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="U33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="V33" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="V33" s="1"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
